--- a/outputs/penalty_catalog/penalty_catalog.xlsx
+++ b/outputs/penalty_catalog/penalty_catalog.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Nguyên tắc chung" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Checklist mức phạt'!$A$1:$S$159</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Checklist mức phạt'!$A$1:$S$164</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -470,7 +470,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Cột 'cá nhân*' = 1/2 mức tổ chức, chỉ để THAM KHẢO (dựa Luật XLVPHC, ngoài nguồn đã cung cấp, chưa xác nhận).</t>
+          <t>Cột 'cá nhân*' = 1/2 mức tổ chức (Điều 5.5 NĐ125: tổ chức gấp 2 lần cá nhân, trừ Điều 16, 17, 18); xem sheet Nguyên tắc chung.</t>
         </is>
       </c>
     </row>
@@ -506,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S159"/>
+  <dimension ref="A1:S164"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -2541,67 +2541,75 @@
       <c r="S30" s="2" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+      <c r="A31" s="4" t="inlineStr">
         <is>
           <t>P030</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B31" s="4" t="inlineStr">
         <is>
           <t>Thủ tục thuế</t>
         </is>
       </c>
-      <c r="C31" s="2" t="n">
+      <c r="C31" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="D31" s="2" t="n">
+      <c r="D31" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="E31" s="2" t="inlineStr"/>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="E31" s="4" t="inlineStr"/>
+      <c r="F31" s="4" t="inlineStr">
         <is>
           <t>Nộp hồ sơ khai thuế quá hạn trên 90 ngày, có phát sinh thuế phải nộp, đã nộp đủ thuế + tiền chậm nộp trước khi có quyết định kiểm tra/thanh tra hoặc biên bản chậm nộp</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>Phạt tiền (khung)</t>
-        </is>
-      </c>
-      <c r="H31" s="3" t="n">
+      <c r="G31" s="4" t="inlineStr">
+        <is>
+          <t>Phạt tiền (khung)</t>
+        </is>
+      </c>
+      <c r="H31" s="5" t="n">
         <v>15000000</v>
       </c>
-      <c r="I31" s="3" t="n">
+      <c r="I31" s="5" t="n">
         <v>25000000</v>
       </c>
-      <c r="J31" s="3" t="n">
+      <c r="J31" s="5" t="n">
         <v>7500000</v>
       </c>
-      <c r="K31" s="3" t="n">
+      <c r="K31" s="5" t="n">
         <v>12500000</v>
       </c>
-      <c r="L31" s="2" t="inlineStr"/>
-      <c r="M31" s="2" t="inlineStr"/>
-      <c r="N31" s="2" t="inlineStr"/>
-      <c r="O31" s="2" t="inlineStr">
-        <is>
-          <t>2020-12-05</t>
-        </is>
-      </c>
-      <c r="P31" s="2" t="inlineStr"/>
-      <c r="Q31" s="2" t="inlineStr">
-        <is>
-          <t>Còn hiệu lực</t>
-        </is>
-      </c>
-      <c r="R31" s="2" t="inlineStr">
-        <is>
-          <t>NĐ 125/2020+310/2025</t>
-        </is>
-      </c>
-      <c r="S31" s="2" t="inlineStr">
-        <is>
-          <t>NĐ310 (từ 16/01/2026) bổ sung: nếu tiền phạt &gt; số thuế phát sinh trên hồ sơ (hoặc tổng thuế các hồ sơ nộp cùng ngày cùng sắc thuế) thì mức phạt tối đa = số thuế phát sinh, nhưng không thấp hơn mức trung bình khung khoản 4 (11,5 triệu). Trường hợp nộp trên 90 ngày KHÔNG thuộc khoản 5 bị xử lý như trốn thuế (Điều 17.1.a).</t>
+      <c r="L31" s="4" t="inlineStr"/>
+      <c r="M31" s="4" t="inlineStr"/>
+      <c r="N31" s="4" t="inlineStr">
+        <is>
+          <t>Buộc nộp tiền chậm nộp (khoản 6.a Điều 13 gốc có bao gồm khoản 5)</t>
+        </is>
+      </c>
+      <c r="O31" s="4" t="inlineStr">
+        <is>
+          <t>2020-12-05</t>
+        </is>
+      </c>
+      <c r="P31" s="4" t="inlineStr">
+        <is>
+          <t>2026-01-15</t>
+        </is>
+      </c>
+      <c r="Q31" s="4" t="inlineStr">
+        <is>
+          <t>Đã được thay bằng quy định mới từ 16/01/2026 (chỉ áp dụng hành vi đã kết thúc trước ngày này)</t>
+        </is>
+      </c>
+      <c r="R31" s="4" t="inlineStr">
+        <is>
+          <t>NĐ 125/2020</t>
+        </is>
+      </c>
+      <c r="S31" s="4" t="inlineStr">
+        <is>
+          <t>Trường hợp nộp trên 90 ngày KHÔNG thuộc khoản 5 bị xử lý như trốn thuế (Điều 17.1.a).</t>
         </is>
       </c>
     </row>
@@ -2617,19 +2625,15 @@
         </is>
       </c>
       <c r="C32" s="2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D32" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="E32" s="2" t="inlineStr"/>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>Cung cấp thông tin, hồ sơ pháp lý đăng ký thuế theo thông báo của cơ quan thuế quá hạn từ 05 ngày làm việc</t>
+          <t>Nộp hồ sơ khai thuế quá hạn trên 90 ngày, có phát sinh thuế phải nộp, đã nộp đủ thuế + tiền chậm nộp trước khi có quyết định kiểm tra/thanh tra hoặc biên bản chậm nộp</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -2638,23 +2642,27 @@
         </is>
       </c>
       <c r="H32" s="3" t="n">
-        <v>2000000</v>
+        <v>15000000</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>3000000</v>
+        <v>25000000</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>1000000</v>
+        <v>7500000</v>
       </c>
       <c r="K32" s="3" t="n">
-        <v>1500000</v>
+        <v>12500000</v>
       </c>
       <c r="L32" s="2" t="inlineStr"/>
       <c r="M32" s="2" t="inlineStr"/>
-      <c r="N32" s="2" t="inlineStr"/>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>Khoản 6.a Điều 13 mới chỉ buộc nộp tiền chậm nộp đối với khoản 1, 2, 3, 4 (không còn khoản 5)</t>
+        </is>
+      </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>2020-12-05</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr"/>
@@ -2665,10 +2673,14 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>NĐ 125/2020</t>
-        </is>
-      </c>
-      <c r="S32" s="2" t="inlineStr"/>
+          <t>NĐ 310/2025</t>
+        </is>
+      </c>
+      <c r="S32" s="2" t="inlineStr">
+        <is>
+          <t>Từ 16/01/2026: nếu tiền phạt &gt; số thuế phát sinh trên hồ sơ (hoặc tổng thuế các hồ sơ nộp cùng ngày cùng sắc thuế) thì mức phạt tối đa = số thuế phát sinh, nhưng không thấp hơn mức trung bình khung khoản 4 (11,5 triệu). Trigger đổi thành 'cơ quan khác công bố quyết định thanh tra, kiểm tra'.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -2689,12 +2701,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>a</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>Cung cấp thông tin, tài liệu, sổ kế toán xác định nghĩa vụ thuế theo thông báo quá hạn từ 05 ngày làm việc</t>
+          <t>Cung cấp thông tin, hồ sơ pháp lý đăng ký thuế theo thông báo của cơ quan thuế quá hạn từ 05 ngày làm việc</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -2750,16 +2762,16 @@
         <v>14</v>
       </c>
       <c r="D34" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>b</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>Không cung cấp / cung cấp không đầy đủ, không chính xác thông tin, chứng từ, hóa đơn, sổ kế toán xác định nghĩa vụ thuế; số hiệu, số dư tài khoản</t>
+          <t>Cung cấp thông tin, tài liệu, sổ kế toán xác định nghĩa vụ thuế theo thông báo quá hạn từ 05 ngày làm việc</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -2768,24 +2780,20 @@
         </is>
       </c>
       <c r="H34" s="3" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="I34" s="3" t="n">
         <v>3000000</v>
       </c>
-      <c r="I34" s="3" t="n">
-        <v>5000000</v>
-      </c>
       <c r="J34" s="3" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="K34" s="3" t="n">
         <v>1500000</v>
-      </c>
-      <c r="K34" s="3" t="n">
-        <v>2500000</v>
       </c>
       <c r="L34" s="2" t="inlineStr"/>
       <c r="M34" s="2" t="inlineStr"/>
-      <c r="N34" s="2" t="inlineStr">
-        <is>
-          <t>Buộc cung cấp thông tin</t>
-        </is>
-      </c>
+      <c r="N34" s="2" t="inlineStr"/>
       <c r="O34" s="2" t="inlineStr">
         <is>
           <t>2020-12-05</t>
@@ -2823,12 +2831,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>a</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>Không cung cấp / cung cấp không đầy đủ, không đúng chỉ tiêu nghĩa vụ thuế phải đăng ký, không làm giảm nghĩa vụ thuế</t>
+          <t>Không cung cấp / cung cấp không đầy đủ, không chính xác thông tin, chứng từ, hóa đơn, sổ kế toán xác định nghĩa vụ thuế; số hiệu, số dư tài khoản</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -2892,12 +2900,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>b</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>Không cung cấp / cung cấp không đầy đủ thông tin tài khoản tại TCTD, KBNN, công nợ bên thứ ba khi cơ quan thuế yêu cầu</t>
+          <t>Không cung cấp / cung cấp không đầy đủ, không đúng chỉ tiêu nghĩa vụ thuế phải đăng ký, không làm giảm nghĩa vụ thuế</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -2954,19 +2962,19 @@
         </is>
       </c>
       <c r="C37" s="2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D37" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>c</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>Không nhận quyết định thanh tra, kiểm tra thuế, quyết định cưỡng chế khi cơ quan thuế giao, gửi</t>
+          <t>Không cung cấp / cung cấp không đầy đủ thông tin tài khoản tại TCTD, KBNN, công nợ bên thứ ba khi cơ quan thuế yêu cầu</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -2975,20 +2983,24 @@
         </is>
       </c>
       <c r="H37" s="3" t="n">
-        <v>2000000</v>
+        <v>3000000</v>
       </c>
       <c r="I37" s="3" t="n">
         <v>5000000</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>1000000</v>
+        <v>1500000</v>
       </c>
       <c r="K37" s="3" t="n">
         <v>2500000</v>
       </c>
       <c r="L37" s="2" t="inlineStr"/>
       <c r="M37" s="2" t="inlineStr"/>
-      <c r="N37" s="2" t="inlineStr"/>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>Buộc cung cấp thông tin</t>
+        </is>
+      </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
           <t>2020-12-05</t>
@@ -3026,12 +3038,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>a</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>Không chấp hành quyết định thanh tra, kiểm tra thuế quá 03 ngày làm việc</t>
+          <t>Không nhận quyết định thanh tra, kiểm tra thuế, quyết định cưỡng chế khi cơ quan thuế giao, gửi</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -3091,12 +3103,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>b</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>Cung cấp hồ sơ, tài liệu, hóa đơn, sổ kế toán quá 06 giờ làm việc khi kiểm tra tại trụ sở</t>
+          <t>Không chấp hành quyết định thanh tra, kiểm tra thuế quá thời hạn 03 ngày làm việc trở lên</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -3156,12 +3168,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>d</t>
+          <t>c</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>Cung cấp không đầy đủ, chính xác thông tin, tài liệu, sổ kế toán khi kiểm tra tại trụ sở</t>
+          <t>Cung cấp hồ sơ, tài liệu, hóa đơn, sổ kế toán quá 06 giờ làm việc khi kiểm tra tại trụ sở</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -3183,11 +3195,7 @@
       </c>
       <c r="L40" s="2" t="inlineStr"/>
       <c r="M40" s="2" t="inlineStr"/>
-      <c r="N40" s="2" t="inlineStr">
-        <is>
-          <t>Buộc cung cấp thông tin, tài liệu, sổ kế toán</t>
-        </is>
-      </c>
+      <c r="N40" s="2" t="inlineStr"/>
       <c r="O40" s="2" t="inlineStr">
         <is>
           <t>2020-12-05</t>
@@ -3225,12 +3233,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>đ</t>
+          <t>d</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>Không ký biên bản kiểm tra, thanh tra thuế trong 05 ngày làm việc</t>
+          <t>Cung cấp không đầy đủ, chính xác thông tin, tài liệu, sổ kế toán khi kiểm tra tại trụ sở</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -3252,7 +3260,11 @@
       </c>
       <c r="L41" s="2" t="inlineStr"/>
       <c r="M41" s="2" t="inlineStr"/>
-      <c r="N41" s="2" t="inlineStr"/>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>Buộc cung cấp thông tin, tài liệu, sổ kế toán</t>
+        </is>
+      </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
           <t>2020-12-05</t>
@@ -3286,16 +3298,16 @@
         <v>15</v>
       </c>
       <c r="D42" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>đ</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>Không cung cấp số liệu, tài liệu, sổ kế toán khi cơ quan có thẩm quyền yêu cầu trong kiểm tra/thanh tra tại trụ sở</t>
+          <t>Không ký biên bản kiểm tra, thanh tra thuế trong 05 ngày làm việc</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -3304,24 +3316,20 @@
         </is>
       </c>
       <c r="H42" s="3" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="I42" s="3" t="n">
         <v>5000000</v>
       </c>
-      <c r="I42" s="3" t="n">
-        <v>10000000</v>
-      </c>
       <c r="J42" s="3" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="K42" s="3" t="n">
         <v>2500000</v>
-      </c>
-      <c r="K42" s="3" t="n">
-        <v>5000000</v>
       </c>
       <c r="L42" s="2" t="inlineStr"/>
       <c r="M42" s="2" t="inlineStr"/>
-      <c r="N42" s="2" t="inlineStr">
-        <is>
-          <t>Buộc cung cấp thông tin, tài liệu, sổ kế toán</t>
-        </is>
-      </c>
+      <c r="N42" s="2" t="inlineStr"/>
       <c r="O42" s="2" t="inlineStr">
         <is>
           <t>2020-12-05</t>
@@ -3359,12 +3367,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>a</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>Không thực hiện / thực hiện không đúng quyết định niêm phong hồ sơ, két quỹ, kho hàng...</t>
+          <t>Không cung cấp số liệu, tài liệu, sổ kế toán khi cơ quan có thẩm quyền yêu cầu trong kiểm tra/thanh tra tại trụ sở</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -3386,7 +3394,11 @@
       </c>
       <c r="L43" s="2" t="inlineStr"/>
       <c r="M43" s="2" t="inlineStr"/>
-      <c r="N43" s="2" t="inlineStr"/>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>Buộc cung cấp thông tin, tài liệu, sổ kế toán</t>
+        </is>
+      </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
           <t>2020-12-05</t>
@@ -3424,12 +3436,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>b</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>Tự ý tháo bỏ, thay đổi dấu hiệu niêm phong hợp pháp</t>
+          <t>Không thực hiện / thực hiện không đúng quyết định niêm phong hồ sơ, két quỹ, kho hàng...</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -3478,45 +3490,45 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Khai sai / trốn thuế</t>
+          <t>Thủ tục thuế</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D45" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>c</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>Khai sai căn cứ tính thuế / số thuế được khấu trừ / sai trường hợp miễn giảm hoàn - nghiệp vụ đã phản ánh đầy đủ trong sổ sách, hóa đơn, chứng từ hợp pháp</t>
+          <t>Tự ý tháo bỏ, thay đổi dấu hiệu niêm phong hợp pháp</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>Phạt theo tỷ lệ</t>
-        </is>
-      </c>
-      <c r="H45" s="3" t="n"/>
-      <c r="I45" s="3" t="n"/>
-      <c r="J45" s="3" t="n"/>
-      <c r="K45" s="3" t="n"/>
-      <c r="L45" s="2" t="inlineStr">
-        <is>
-          <t>20% số thuế khai thiếu / số thuế miễn, giảm, hoàn cao hơn quy định</t>
-        </is>
-      </c>
+          <t>Phạt tiền (khung)</t>
+        </is>
+      </c>
+      <c r="H45" s="3" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="I45" s="3" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="J45" s="3" t="n">
+        <v>2500000</v>
+      </c>
+      <c r="K45" s="3" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="L45" s="2" t="inlineStr"/>
       <c r="M45" s="2" t="inlineStr"/>
-      <c r="N45" s="2" t="inlineStr">
-        <is>
-          <t>Buộc nộp đủ thuế thiếu + tiền chậm nộp; điều chỉnh lỗ, thuế GTGT đầu vào chuyển kỳ sau</t>
-        </is>
-      </c>
+      <c r="N45" s="2" t="inlineStr"/>
       <c r="O45" s="2" t="inlineStr">
         <is>
           <t>2020-12-05</t>
@@ -3536,211 +3548,211 @@
       <c r="S45" s="2" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="4" t="inlineStr">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>P045</t>
         </is>
       </c>
-      <c r="B46" s="4" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>Khai sai / trốn thuế</t>
         </is>
       </c>
-      <c r="C46" s="4" t="n">
+      <c r="C46" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="D46" s="4" t="n">
+      <c r="D46" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E46" s="4" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>Khai sai căn cứ tính thuế / số thuế được khấu trừ / sai trường hợp miễn giảm hoàn - nghiệp vụ đã phản ánh đầy đủ trong sổ sách, hóa đơn, chứng từ hợp pháp</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>Phạt theo tỷ lệ</t>
+        </is>
+      </c>
+      <c r="H46" s="3" t="n"/>
+      <c r="I46" s="3" t="n"/>
+      <c r="J46" s="3" t="n"/>
+      <c r="K46" s="3" t="n"/>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>20% số thuế khai thiếu / số thuế miễn, giảm, hoàn cao hơn quy định</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr"/>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>Buộc nộp đủ thuế thiếu + tiền chậm nộp; điều chỉnh lỗ, thuế GTGT đầu vào chuyển kỳ sau</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>2020-12-05</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr"/>
+      <c r="Q46" s="2" t="inlineStr">
+        <is>
+          <t>Còn hiệu lực</t>
+        </is>
+      </c>
+      <c r="R46" s="2" t="inlineStr">
+        <is>
+          <t>NĐ 125/2020</t>
+        </is>
+      </c>
+      <c r="S46" s="2" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>P046</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>Khai sai / trốn thuế</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="D47" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E47" s="4" t="inlineStr">
         <is>
           <t>b</t>
         </is>
       </c>
-      <c r="F46" s="4" t="inlineStr">
+      <c r="F47" s="4" t="inlineStr">
         <is>
           <t>Khai sai làm giảm thuế phải nộp (không thuộc điểm a), đã tự khai bổ sung và nộp đủ thuế trước khi cơ quan thuế kết thúc thanh tra, kiểm tra tại trụ sở</t>
         </is>
       </c>
-      <c r="G46" s="4" t="inlineStr">
+      <c r="G47" s="4" t="inlineStr">
         <is>
           <t>Phạt theo tỷ lệ</t>
         </is>
       </c>
-      <c r="H46" s="5" t="n"/>
-      <c r="I46" s="5" t="n"/>
-      <c r="J46" s="5" t="n"/>
-      <c r="K46" s="5" t="n"/>
-      <c r="L46" s="4" t="inlineStr">
+      <c r="H47" s="5" t="n"/>
+      <c r="I47" s="5" t="n"/>
+      <c r="J47" s="5" t="n"/>
+      <c r="K47" s="5" t="n"/>
+      <c r="L47" s="4" t="inlineStr">
         <is>
           <t>20% số thuế khai thiếu / số thuế miễn, giảm, hoàn cao hơn quy định</t>
         </is>
       </c>
-      <c r="M46" s="4" t="inlineStr"/>
-      <c r="N46" s="4" t="inlineStr">
+      <c r="M47" s="4" t="inlineStr"/>
+      <c r="N47" s="4" t="inlineStr">
         <is>
           <t>Buộc nộp đủ thuế thiếu + tiền chậm nộp; điều chỉnh lỗ, thuế GTGT đầu vào chuyển kỳ sau</t>
         </is>
       </c>
-      <c r="O46" s="4" t="inlineStr">
-        <is>
-          <t>2020-12-05</t>
-        </is>
-      </c>
-      <c r="P46" s="4" t="inlineStr">
+      <c r="O47" s="4" t="inlineStr">
+        <is>
+          <t>2020-12-05</t>
+        </is>
+      </c>
+      <c r="P47" s="4" t="inlineStr">
         <is>
           <t>2026-01-15</t>
         </is>
       </c>
-      <c r="Q46" s="4" t="inlineStr">
+      <c r="Q47" s="4" t="inlineStr">
         <is>
           <t>Đã bãi bỏ từ 16/01/2026 (chỉ áp dụng hành vi đã kết thúc trước ngày này)</t>
         </is>
       </c>
-      <c r="R46" s="4" t="inlineStr">
-        <is>
-          <t>NĐ 125/2020</t>
-        </is>
-      </c>
-      <c r="S46" s="4" t="inlineStr">
+      <c r="R47" s="4" t="inlineStr">
+        <is>
+          <t>NĐ 125/2020</t>
+        </is>
+      </c>
+      <c r="S47" s="4" t="inlineStr">
         <is>
           <t>Điểm này bị NĐ310 bãi bỏ; thay bằng Điều 9.3: khai bổ sung + nộp đủ thuế TRƯỚC khi có quyết định kiểm tra/thanh tra hoặc trước khi cơ quan thuế phát hiện thì KHÔNG bị xử phạt.</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>P046</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>P047</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
         <is>
           <t>Khai sai / trốn thuế</t>
         </is>
       </c>
-      <c r="C47" s="2" t="n">
+      <c r="C48" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="D47" s="2" t="n">
+      <c r="D48" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E48" s="4" t="inlineStr">
         <is>
           <t>c</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>Khai sai bị xác định là trốn thuế nhưng vi phạm lần đầu về trốn thuế, đã khai bổ sung và nộp đủ thuế trước khi có quyết định xử phạt, cơ quan thuế đã lập biên bản ghi nhận là khai sai</t>
-        </is>
-      </c>
-      <c r="G47" s="2" t="inlineStr">
+      <c r="F48" s="4" t="inlineStr">
+        <is>
+          <t>Khai sai bị xác định là trốn thuế nhưng vi phạm lần đầu về trốn thuế, đã khai bổ sung và nộp đủ thuế trước khi có quyết định xử phạt, cơ quan thuế đã lập biên bản ghi nhận là khai sai (biên bản thanh tra, kiểm tra thuế hoặc biên bản vi phạm hành chính)</t>
+        </is>
+      </c>
+      <c r="G48" s="4" t="inlineStr">
         <is>
           <t>Phạt theo tỷ lệ</t>
         </is>
       </c>
-      <c r="H47" s="3" t="n"/>
-      <c r="I47" s="3" t="n"/>
-      <c r="J47" s="3" t="n"/>
-      <c r="K47" s="3" t="n"/>
-      <c r="L47" s="2" t="inlineStr">
+      <c r="H48" s="5" t="n"/>
+      <c r="I48" s="5" t="n"/>
+      <c r="J48" s="5" t="n"/>
+      <c r="K48" s="5" t="n"/>
+      <c r="L48" s="4" t="inlineStr">
         <is>
           <t>20% số thuế khai thiếu / số thuế miễn, giảm, hoàn cao hơn quy định</t>
         </is>
       </c>
-      <c r="M47" s="2" t="inlineStr"/>
-      <c r="N47" s="2" t="inlineStr">
+      <c r="M48" s="4" t="inlineStr"/>
+      <c r="N48" s="4" t="inlineStr">
         <is>
           <t>Buộc nộp đủ thuế thiếu + tiền chậm nộp; điều chỉnh lỗ, thuế GTGT đầu vào chuyển kỳ sau</t>
         </is>
       </c>
-      <c r="O47" s="2" t="inlineStr">
-        <is>
-          <t>2020-12-05</t>
-        </is>
-      </c>
-      <c r="P47" s="2" t="inlineStr"/>
-      <c r="Q47" s="2" t="inlineStr">
-        <is>
-          <t>Còn hiệu lực</t>
-        </is>
-      </c>
-      <c r="R47" s="2" t="inlineStr">
-        <is>
-          <t>NĐ 125/2020+310/2025</t>
-        </is>
-      </c>
-      <c r="S47" s="2" t="inlineStr">
-        <is>
-          <t>NĐ310 sửa điểm này (bỏ cụm 'thanh tra, kiểm tra thuế' ở biên bản).</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>P047</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>Khai sai / trốn thuế</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="D48" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>d</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>Khai sai dẫn đến thiếu thuế với giao dịch liên kết nhưng đã lập hồ sơ xác định giá thị trường / gửi phụ lục giao dịch liên kết</t>
-        </is>
-      </c>
-      <c r="G48" s="2" t="inlineStr">
-        <is>
-          <t>Phạt theo tỷ lệ</t>
-        </is>
-      </c>
-      <c r="H48" s="3" t="n"/>
-      <c r="I48" s="3" t="n"/>
-      <c r="J48" s="3" t="n"/>
-      <c r="K48" s="3" t="n"/>
-      <c r="L48" s="2" t="inlineStr">
-        <is>
-          <t>20% số thuế khai thiếu / số thuế miễn, giảm, hoàn cao hơn quy định</t>
-        </is>
-      </c>
-      <c r="M48" s="2" t="inlineStr"/>
-      <c r="N48" s="2" t="inlineStr">
-        <is>
-          <t>Buộc nộp đủ thuế thiếu + tiền chậm nộp; điều chỉnh lỗ, thuế GTGT đầu vào chuyển kỳ sau</t>
-        </is>
-      </c>
-      <c r="O48" s="2" t="inlineStr">
-        <is>
-          <t>2020-12-05</t>
-        </is>
-      </c>
-      <c r="P48" s="2" t="inlineStr"/>
-      <c r="Q48" s="2" t="inlineStr">
-        <is>
-          <t>Còn hiệu lực</t>
-        </is>
-      </c>
-      <c r="R48" s="2" t="inlineStr">
-        <is>
-          <t>NĐ 125/2020</t>
-        </is>
-      </c>
-      <c r="S48" s="2" t="inlineStr"/>
+      <c r="O48" s="4" t="inlineStr">
+        <is>
+          <t>2020-12-05</t>
+        </is>
+      </c>
+      <c r="P48" s="4" t="inlineStr">
+        <is>
+          <t>2026-01-15</t>
+        </is>
+      </c>
+      <c r="Q48" s="4" t="inlineStr">
+        <is>
+          <t>Đã được thay bằng quy định mới từ 16/01/2026 (chỉ áp dụng hành vi đã kết thúc trước ngày này)</t>
+        </is>
+      </c>
+      <c r="R48" s="4" t="inlineStr">
+        <is>
+          <t>NĐ 125/2020</t>
+        </is>
+      </c>
+      <c r="S48" s="4" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -3761,12 +3773,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>đ</t>
+          <t>c</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>Sử dụng hóa đơn, chứng từ không hợp pháp để hạch toán đầu vào, nhưng người mua chứng minh được lỗi thuộc bên bán và đã hạch toán đầy đủ</t>
+          <t>Khai sai bị xác định là trốn thuế nhưng vi phạm lần đầu về trốn thuế, đã khai bổ sung và nộp đủ thuế trước khi có quyết định xử phạt, cơ quan thuế đã lập biên bản ghi nhận là khai sai (chỉ còn: biên bản vi phạm hành chính)</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -3791,7 +3803,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>2020-12-05</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr"/>
@@ -3802,10 +3814,14 @@
       </c>
       <c r="R49" s="2" t="inlineStr">
         <is>
-          <t>NĐ 125/2020</t>
-        </is>
-      </c>
-      <c r="S49" s="2" t="inlineStr"/>
+          <t>NĐ 310/2025</t>
+        </is>
+      </c>
+      <c r="S49" s="2" t="inlineStr">
+        <is>
+          <t>Bản OCR NĐ310 ghi tiêu đề 'điểm e'; nội dung trích khớp điểm c khoản 1 Điều 16 gốc (khoản 1 không có điểm e).</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -3819,19 +3835,19 @@
         </is>
       </c>
       <c r="C50" s="2" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D50" s="2" t="n">
         <v>1</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>d</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>Không nộp hồ sơ đăng ký thuế; không nộp hồ sơ khai thuế hoặc nộp sau 90 ngày kể từ ngày hết hạn</t>
+          <t>Khai sai dẫn đến thiếu thuế với giao dịch liên kết nhưng đã lập hồ sơ xác định giá thị trường / gửi phụ lục giao dịch liên kết</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -3845,13 +3861,13 @@
       <c r="K50" s="3" t="n"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>Phạt 1-3 lần số thuế trốn (mức cụ thể theo tình tiết - xem sheet Nguyên tắc chung)</t>
+          <t>20% số thuế khai thiếu / số thuế miễn, giảm, hoàn cao hơn quy định</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr"/>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>Buộc nộp đủ thuế trốn (+ tiền chậm nộp); điều chỉnh lỗ, thuế GTGT đầu vào</t>
+          <t>Buộc nộp đủ thuế thiếu + tiền chậm nộp; điều chỉnh lỗ, thuế GTGT đầu vào chuyển kỳ sau</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
@@ -3884,19 +3900,19 @@
         </is>
       </c>
       <c r="C51" s="2" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D51" s="2" t="n">
         <v>1</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>đ</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>Không ghi sổ kế toán các khoản thu; không khai, khai sai dẫn đến thiếu thuế (trừ Điều 16)</t>
+          <t>Sử dụng hóa đơn, chứng từ không hợp pháp để hạch toán đầu vào, nhưng người mua chứng minh được lỗi thuộc bên bán và đã hạch toán đầy đủ</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -3910,13 +3926,13 @@
       <c r="K51" s="3" t="n"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>Phạt 1-3 lần số thuế trốn (mức cụ thể theo tình tiết - xem sheet Nguyên tắc chung)</t>
+          <t>20% số thuế khai thiếu / số thuế miễn, giảm, hoàn cao hơn quy định</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr"/>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>Buộc nộp đủ thuế trốn (+ tiền chậm nộp); điều chỉnh lỗ, thuế GTGT đầu vào</t>
+          <t>Buộc nộp đủ thuế thiếu + tiền chậm nộp; điều chỉnh lỗ, thuế GTGT đầu vào chuyển kỳ sau</t>
         </is>
       </c>
       <c r="O51" s="2" t="inlineStr">
@@ -3935,11 +3951,7 @@
           <t>NĐ 125/2020</t>
         </is>
       </c>
-      <c r="S51" s="2" t="inlineStr">
-        <is>
-          <t>Nếu bị phát hiện sau hạn nộp hồ sơ khai thuế nhưng KHÔNG làm giảm thuế phải nộp: xử phạt theo Điều 12.3 (5-8 triệu) - khoản 7 Điều 17.</t>
-        </is>
-      </c>
+      <c r="S51" s="2" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -3960,12 +3972,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>a</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>Không lập hóa đơn khi bán hàng hóa, dịch vụ (trừ trường hợp đã khai thuế); lập hóa đơn sai số lượng, giá trị để khai thuế thấp hơn thực tế và bị phát hiện sau hạn nộp hồ sơ khai thuế</t>
+          <t>Không nộp hồ sơ đăng ký thuế; không nộp hồ sơ khai thuế hoặc nộp sau 90 ngày kể từ ngày hết hạn</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -3982,7 +3994,11 @@
           <t>Phạt 1-3 lần số thuế trốn (mức cụ thể theo tình tiết - xem sheet Nguyên tắc chung)</t>
         </is>
       </c>
-      <c r="M52" s="2" t="inlineStr"/>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>Trừ trường hợp điểm b, c khoản 4 và khoản 5 Điều 13</t>
+        </is>
+      </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
           <t>Buộc nộp đủ thuế trốn (+ tiền chậm nộp); điều chỉnh lỗ, thuế GTGT đầu vào</t>
@@ -4025,12 +4041,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>d</t>
+          <t>b</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>Sử dụng hóa đơn không hợp pháp; sử dụng không hợp pháp hóa đơn để khai thuế làm giảm thuế phải nộp / tăng thuế được hoàn, miễn, giảm</t>
+          <t>Không ghi sổ kế toán các khoản thu; không khai, khai sai dẫn đến thiếu thuế (trừ Điều 16)</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -4069,7 +4085,11 @@
           <t>NĐ 125/2020</t>
         </is>
       </c>
-      <c r="S53" s="2" t="inlineStr"/>
+      <c r="S53" s="2" t="inlineStr">
+        <is>
+          <t>Nếu bị phát hiện sau hạn nộp hồ sơ khai thuế nhưng KHÔNG làm giảm thuế phải nộp: xử phạt theo Điều 12.3 (5-8 triệu) - khoản 7 Điều 17.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -4090,12 +4110,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>đ</t>
+          <t>c</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>Sử dụng chứng từ không hợp pháp; chứng từ, tài liệu không phản ánh đúng bản chất/giá trị giao dịch; hủy vật tư, hàng hóa không đúng thực tế để giảm thuế</t>
+          <t>Không lập hóa đơn khi bán hàng hóa, dịch vụ (trừ trường hợp đã khai thuế); lập hóa đơn sai số lượng, giá trị để khai thuế thấp hơn thực tế và bị phát hiện sau hạn nộp hồ sơ khai thuế</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -4134,11 +4154,7 @@
           <t>NĐ 125/2020</t>
         </is>
       </c>
-      <c r="S54" s="2" t="inlineStr">
-        <is>
-          <t>Nếu bị phát hiện sau hạn nộp hồ sơ khai thuế nhưng KHÔNG làm giảm thuế phải nộp: xử phạt theo Điều 12.3 (5-8 triệu) - khoản 7 Điều 17.</t>
-        </is>
-      </c>
+      <c r="S54" s="2" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -4159,12 +4175,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>e</t>
+          <t>d</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>Sử dụng hàng hóa không chịu thuế/miễn thuế sai mục đích mà không khai báo chuyển đổi mục đích</t>
+          <t>Sử dụng hóa đơn không hợp pháp; sử dụng không hợp pháp hóa đơn để khai thuế làm giảm thuế phải nộp / tăng thuế được hoàn, miễn, giảm</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -4203,11 +4219,7 @@
           <t>NĐ 125/2020</t>
         </is>
       </c>
-      <c r="S55" s="2" t="inlineStr">
-        <is>
-          <t>Nếu bị phát hiện sau hạn nộp hồ sơ khai thuế nhưng KHÔNG làm giảm thuế phải nộp: xử phạt theo Điều 12.3 (5-8 triệu) - khoản 7 Điều 17.</t>
-        </is>
-      </c>
+      <c r="S55" s="2" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -4228,12 +4240,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>đ</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>Có hoạt động KD trong thời gian xin ngừng/tạm ngừng mà không thông báo cơ quan thuế</t>
+          <t>Sử dụng chứng từ không hợp pháp; chứng từ, tài liệu không phản ánh đúng bản chất/giá trị giao dịch; hủy vật tư, hàng hóa không đúng thực tế để giảm thuế</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -4272,7 +4284,11 @@
           <t>NĐ 125/2020</t>
         </is>
       </c>
-      <c r="S56" s="2" t="inlineStr"/>
+      <c r="S56" s="2" t="inlineStr">
+        <is>
+          <t>Nếu bị phát hiện sau hạn nộp hồ sơ khai thuế nhưng KHÔNG làm giảm thuế phải nộp: xử phạt theo Điều 12.3 (5-8 triệu) - khoản 7 Điều 17.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -4286,15 +4302,19 @@
         </is>
       </c>
       <c r="C57" s="2" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D57" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E57" s="2" t="inlineStr"/>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>Ngân hàng thương mại không trích chuyển tiền từ tài khoản người nộp thuế vào NSNN theo yêu cầu của cơ quan thuế</t>
+          <t>Sử dụng hàng hóa không chịu thuế/miễn thuế sai mục đích mà không khai báo chuyển đổi mục đích</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -4308,11 +4328,15 @@
       <c r="K57" s="3" t="n"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>Phạt bằng số thuế + tiền chậm nộp + tiền phạt không trích chuyển (trừ số dư tối thiểu)</t>
+          <t>Phạt 1-3 lần số thuế trốn (mức cụ thể theo tình tiết - xem sheet Nguyên tắc chung)</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr"/>
-      <c r="N57" s="2" t="inlineStr"/>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>Buộc nộp đủ thuế trốn (+ tiền chậm nộp); điều chỉnh lỗ, thuế GTGT đầu vào</t>
+        </is>
+      </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
           <t>2020-12-05</t>
@@ -4331,7 +4355,7 @@
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>Đối tượng: ngân hàng thương mại, không phải người nộp thuế.</t>
+          <t>Nếu bị phát hiện sau hạn nộp hồ sơ khai thuế nhưng KHÔNG làm giảm thuế phải nộp: xử phạt theo Điều 12.3 (5-8 triệu) - khoản 7 Điều 17.</t>
         </is>
       </c>
     </row>
@@ -4343,41 +4367,49 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Thủ tục thuế</t>
+          <t>Khai sai / trốn thuế</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D58" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E58" s="2" t="inlineStr"/>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>Cung cấp thông tin, tài liệu xác định nghĩa vụ thuế / tài khoản của người nộp thuế theo yêu cầu cơ quan thuế quá hạn từ 05 ngày</t>
+          <t>Có hoạt động KD trong thời gian xin ngừng/tạm ngừng mà không thông báo cơ quan thuế</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>Phạt tiền (khung)</t>
-        </is>
-      </c>
-      <c r="H58" s="3" t="n">
-        <v>2000000</v>
-      </c>
-      <c r="I58" s="3" t="n">
-        <v>6000000</v>
-      </c>
-      <c r="J58" s="3" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="K58" s="3" t="n">
-        <v>3000000</v>
-      </c>
-      <c r="L58" s="2" t="inlineStr"/>
-      <c r="M58" s="2" t="inlineStr"/>
-      <c r="N58" s="2" t="inlineStr"/>
+          <t>Phạt theo tỷ lệ</t>
+        </is>
+      </c>
+      <c r="H58" s="3" t="n"/>
+      <c r="I58" s="3" t="n"/>
+      <c r="J58" s="3" t="n"/>
+      <c r="K58" s="3" t="n"/>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>Phạt 1-3 lần số thuế trốn (mức cụ thể theo tình tiết - xem sheet Nguyên tắc chung)</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>Trừ trường hợp điểm b khoản 4 Điều 10</t>
+        </is>
+      </c>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>Buộc nộp đủ thuế trốn (+ tiền chậm nộp); điều chỉnh lỗ, thuế GTGT đầu vào</t>
+        </is>
+      </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
           <t>2020-12-05</t>
@@ -4391,294 +4423,282 @@
       </c>
       <c r="R58" s="2" t="inlineStr">
         <is>
+          <t>NĐ 125/2020</t>
+        </is>
+      </c>
+      <c r="S58" s="2" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>P058</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>Khai sai / trốn thuế</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="D59" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E59" s="2" t="inlineStr"/>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>Ngân hàng thương mại không trích chuyển tiền từ tài khoản người nộp thuế vào NSNN theo yêu cầu của cơ quan thuế</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>Phạt theo tỷ lệ</t>
+        </is>
+      </c>
+      <c r="H59" s="3" t="n"/>
+      <c r="I59" s="3" t="n"/>
+      <c r="J59" s="3" t="n"/>
+      <c r="K59" s="3" t="n"/>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>Phạt bằng số thuế + tiền chậm nộp + tiền phạt không trích chuyển (trừ số dư tối thiểu)</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>Trừ trường hợp tài khoản không còn số dư hoặc đã trích chuyển toàn bộ số dư mà vẫn không đủ số tiền phải nộp</t>
+        </is>
+      </c>
+      <c r="N59" s="2" t="inlineStr"/>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>2020-12-05</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr"/>
+      <c r="Q59" s="2" t="inlineStr">
+        <is>
+          <t>Còn hiệu lực</t>
+        </is>
+      </c>
+      <c r="R59" s="2" t="inlineStr">
+        <is>
+          <t>NĐ 125/2020</t>
+        </is>
+      </c>
+      <c r="S59" s="2" t="inlineStr">
+        <is>
+          <t>Đối tượng: ngân hàng thương mại, không phải người nộp thuế.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>P059</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>Thủ tục thuế</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="D60" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E60" s="2" t="inlineStr"/>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>Cung cấp thông tin, tài liệu xác định nghĩa vụ thuế / tài khoản của người nộp thuế theo yêu cầu cơ quan thuế quá hạn từ 05 ngày</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>Phạt tiền (khung)</t>
+        </is>
+      </c>
+      <c r="H60" s="3" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="I60" s="3" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="J60" s="3" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="K60" s="3" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="L60" s="2" t="inlineStr"/>
+      <c r="M60" s="2" t="inlineStr"/>
+      <c r="N60" s="2" t="inlineStr"/>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>2020-12-05</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr"/>
+      <c r="Q60" s="2" t="inlineStr">
+        <is>
+          <t>Còn hiệu lực</t>
+        </is>
+      </c>
+      <c r="R60" s="2" t="inlineStr">
+        <is>
           <t>NĐ 125/2020+310/2025</t>
         </is>
       </c>
-      <c r="S58" s="2" t="inlineStr">
+      <c r="S60" s="2" t="inlineStr">
         <is>
           <t>Giữ nguyên khung ở bản cũ và bản mới.</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="4" t="inlineStr">
-        <is>
-          <t>P058</t>
-        </is>
-      </c>
-      <c r="B59" s="4" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="4" t="inlineStr">
+        <is>
+          <t>P060</t>
+        </is>
+      </c>
+      <c r="B61" s="4" t="inlineStr">
         <is>
           <t>Thủ tục thuế</t>
         </is>
       </c>
-      <c r="C59" s="4" t="n">
+      <c r="C61" s="4" t="n">
         <v>19</v>
       </c>
-      <c r="D59" s="4" t="n">
+      <c r="D61" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="E59" s="4" t="inlineStr">
+      <c r="E61" s="4" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="F59" s="4" t="inlineStr">
+      <c r="F61" s="4" t="inlineStr">
         <is>
           <t>Thông đồng, bao che người nộp thuế trốn thuế; không thực hiện quyết định cưỡng chế hành chính thuế (trừ Điều 18)</t>
         </is>
       </c>
-      <c r="G59" s="4" t="inlineStr">
-        <is>
-          <t>Phạt tiền (khung)</t>
-        </is>
-      </c>
-      <c r="H59" s="5" t="n">
+      <c r="G61" s="4" t="inlineStr">
+        <is>
+          <t>Phạt tiền (khung)</t>
+        </is>
+      </c>
+      <c r="H61" s="5" t="n">
         <v>6000000</v>
       </c>
-      <c r="I59" s="5" t="n">
+      <c r="I61" s="5" t="n">
         <v>16000000</v>
       </c>
-      <c r="J59" s="5" t="n">
+      <c r="J61" s="5" t="n">
         <v>3000000</v>
       </c>
-      <c r="K59" s="5" t="n">
+      <c r="K61" s="5" t="n">
         <v>8000000</v>
       </c>
-      <c r="L59" s="4" t="inlineStr"/>
-      <c r="M59" s="4" t="inlineStr"/>
-      <c r="N59" s="4" t="inlineStr"/>
-      <c r="O59" s="4" t="inlineStr">
-        <is>
-          <t>2020-12-05</t>
-        </is>
-      </c>
-      <c r="P59" s="4" t="inlineStr">
+      <c r="L61" s="4" t="inlineStr"/>
+      <c r="M61" s="4" t="inlineStr"/>
+      <c r="N61" s="4" t="inlineStr"/>
+      <c r="O61" s="4" t="inlineStr">
+        <is>
+          <t>2020-12-05</t>
+        </is>
+      </c>
+      <c r="P61" s="4" t="inlineStr">
         <is>
           <t>2026-01-15</t>
         </is>
       </c>
-      <c r="Q59" s="4" t="inlineStr">
+      <c r="Q61" s="4" t="inlineStr">
         <is>
           <t>Đã được thay bằng quy định mới từ 16/01/2026 (chỉ áp dụng hành vi đã kết thúc trước ngày này)</t>
         </is>
       </c>
-      <c r="R59" s="4" t="inlineStr">
-        <is>
-          <t>NĐ 125/2020</t>
-        </is>
-      </c>
-      <c r="S59" s="4" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="4" t="inlineStr">
-        <is>
-          <t>P059</t>
-        </is>
-      </c>
-      <c r="B60" s="4" t="inlineStr">
+      <c r="R61" s="4" t="inlineStr">
+        <is>
+          <t>NĐ 125/2020</t>
+        </is>
+      </c>
+      <c r="S61" s="4" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="4" t="inlineStr">
+        <is>
+          <t>P061</t>
+        </is>
+      </c>
+      <c r="B62" s="4" t="inlineStr">
         <is>
           <t>Thủ tục thuế</t>
         </is>
       </c>
-      <c r="C60" s="4" t="n">
+      <c r="C62" s="4" t="n">
         <v>19</v>
       </c>
-      <c r="D60" s="4" t="n">
+      <c r="D62" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="E60" s="4" t="inlineStr">
+      <c r="E62" s="4" t="inlineStr">
         <is>
           <t>b</t>
         </is>
       </c>
-      <c r="F60" s="4" t="inlineStr">
+      <c r="F62" s="4" t="inlineStr">
         <is>
           <t>Không cung cấp / cung cấp không chính xác thông tin tài sản, quyền, nghĩa vụ tài sản của người nộp thuế; tài khoản tại TCTD, KBNN</t>
         </is>
       </c>
-      <c r="G60" s="4" t="inlineStr">
-        <is>
-          <t>Phạt tiền (khung)</t>
-        </is>
-      </c>
-      <c r="H60" s="5" t="n">
+      <c r="G62" s="4" t="inlineStr">
+        <is>
+          <t>Phạt tiền (khung)</t>
+        </is>
+      </c>
+      <c r="H62" s="5" t="n">
         <v>6000000</v>
       </c>
-      <c r="I60" s="5" t="n">
+      <c r="I62" s="5" t="n">
         <v>16000000</v>
       </c>
-      <c r="J60" s="5" t="n">
+      <c r="J62" s="5" t="n">
         <v>3000000</v>
       </c>
-      <c r="K60" s="5" t="n">
+      <c r="K62" s="5" t="n">
         <v>8000000</v>
       </c>
-      <c r="L60" s="4" t="inlineStr"/>
-      <c r="M60" s="4" t="inlineStr"/>
-      <c r="N60" s="4" t="inlineStr">
+      <c r="L62" s="4" t="inlineStr"/>
+      <c r="M62" s="4" t="inlineStr"/>
+      <c r="N62" s="4" t="inlineStr">
         <is>
           <t>Buộc cung cấp thông tin</t>
         </is>
       </c>
-      <c r="O60" s="4" t="inlineStr">
-        <is>
-          <t>2020-12-05</t>
-        </is>
-      </c>
-      <c r="P60" s="4" t="inlineStr">
+      <c r="O62" s="4" t="inlineStr">
+        <is>
+          <t>2020-12-05</t>
+        </is>
+      </c>
+      <c r="P62" s="4" t="inlineStr">
         <is>
           <t>2026-01-15</t>
         </is>
       </c>
-      <c r="Q60" s="4" t="inlineStr">
+      <c r="Q62" s="4" t="inlineStr">
         <is>
           <t>Đã được thay bằng quy định mới từ 16/01/2026 (chỉ áp dụng hành vi đã kết thúc trước ngày này)</t>
         </is>
       </c>
-      <c r="R60" s="4" t="inlineStr">
-        <is>
-          <t>NĐ 125/2020</t>
-        </is>
-      </c>
-      <c r="S60" s="4" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>P060</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>Thủ tục thuế</t>
-        </is>
-      </c>
-      <c r="C61" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="D61" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E61" s="2" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="F61" s="2" t="inlineStr">
-        <is>
-          <t>Cung cấp KHÔNG CHÍNH XÁC thông tin tài sản, quyền, nghĩa vụ tài sản của người nộp thuế hoặc thông tin xác định nghĩa vụ thuế</t>
-        </is>
-      </c>
-      <c r="G61" s="2" t="inlineStr">
-        <is>
-          <t>Phạt tiền (khung)</t>
-        </is>
-      </c>
-      <c r="H61" s="3" t="n">
-        <v>6000000</v>
-      </c>
-      <c r="I61" s="3" t="n">
-        <v>10000000</v>
-      </c>
-      <c r="J61" s="3" t="n">
-        <v>3000000</v>
-      </c>
-      <c r="K61" s="3" t="n">
-        <v>5000000</v>
-      </c>
-      <c r="L61" s="2" t="inlineStr"/>
-      <c r="M61" s="2" t="inlineStr"/>
-      <c r="N61" s="2" t="inlineStr">
-        <is>
-          <t>Buộc cung cấp thông tin đầy đủ, chính xác</t>
-        </is>
-      </c>
-      <c r="O61" s="2" t="inlineStr">
-        <is>
-          <t>2026-01-16</t>
-        </is>
-      </c>
-      <c r="P61" s="2" t="inlineStr"/>
-      <c r="Q61" s="2" t="inlineStr">
-        <is>
-          <t>Còn hiệu lực</t>
-        </is>
-      </c>
-      <c r="R61" s="2" t="inlineStr">
-        <is>
-          <t>NĐ 310/2025</t>
-        </is>
-      </c>
-      <c r="S61" s="2" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t>P061</t>
-        </is>
-      </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>Thủ tục thuế</t>
-        </is>
-      </c>
-      <c r="C62" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="D62" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E62" s="2" t="inlineStr">
-        <is>
-          <t>b</t>
-        </is>
-      </c>
-      <c r="F62" s="2" t="inlineStr">
-        <is>
-          <t>Cung cấp KHÔNG CHÍNH XÁC thông tin tài khoản của người nộp thuế tại TCTD, KBNN, chi nhánh ngân hàng nước ngoài</t>
-        </is>
-      </c>
-      <c r="G62" s="2" t="inlineStr">
-        <is>
-          <t>Phạt tiền (khung)</t>
-        </is>
-      </c>
-      <c r="H62" s="3" t="n">
-        <v>6000000</v>
-      </c>
-      <c r="I62" s="3" t="n">
-        <v>10000000</v>
-      </c>
-      <c r="J62" s="3" t="n">
-        <v>3000000</v>
-      </c>
-      <c r="K62" s="3" t="n">
-        <v>5000000</v>
-      </c>
-      <c r="L62" s="2" t="inlineStr"/>
-      <c r="M62" s="2" t="inlineStr"/>
-      <c r="N62" s="2" t="inlineStr">
-        <is>
-          <t>Buộc cung cấp thông tin đầy đủ, chính xác</t>
-        </is>
-      </c>
-      <c r="O62" s="2" t="inlineStr">
-        <is>
-          <t>2026-01-16</t>
-        </is>
-      </c>
-      <c r="P62" s="2" t="inlineStr"/>
-      <c r="Q62" s="2" t="inlineStr">
-        <is>
-          <t>Còn hiệu lực</t>
-        </is>
-      </c>
-      <c r="R62" s="2" t="inlineStr">
-        <is>
-          <t>NĐ 310/2025</t>
-        </is>
-      </c>
-      <c r="S62" s="2" t="inlineStr"/>
+      <c r="R62" s="4" t="inlineStr">
+        <is>
+          <t>NĐ 125/2020</t>
+        </is>
+      </c>
+      <c r="S62" s="4" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -4699,12 +4719,12 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>a</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>Cung cấp KHÔNG CHÍNH XÁC thông tin tiền lương, tiền công, thu nhập của người nộp thuế</t>
+          <t>Cung cấp KHÔNG CHÍNH XÁC thông tin tài sản, quyền, nghĩa vụ tài sản của người nộp thuế hoặc thông tin xác định nghĩa vụ thuế</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -4764,16 +4784,16 @@
         <v>19</v>
       </c>
       <c r="D64" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>b</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>KHÔNG cung cấp thông tin tài sản, quyền, nghĩa vụ tài sản của người nộp thuế hoặc thông tin xác định nghĩa vụ thuế</t>
+          <t>Cung cấp KHÔNG CHÍNH XÁC thông tin tài khoản của người nộp thuế tại TCTD, KBNN, chi nhánh ngân hàng nước ngoài</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -4782,16 +4802,16 @@
         </is>
       </c>
       <c r="H64" s="3" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="I64" s="3" t="n">
         <v>10000000</v>
       </c>
-      <c r="I64" s="3" t="n">
-        <v>16000000</v>
-      </c>
       <c r="J64" s="3" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="K64" s="3" t="n">
         <v>5000000</v>
-      </c>
-      <c r="K64" s="3" t="n">
-        <v>8000000</v>
       </c>
       <c r="L64" s="2" t="inlineStr"/>
       <c r="M64" s="2" t="inlineStr"/>
@@ -4833,16 +4853,16 @@
         <v>19</v>
       </c>
       <c r="D65" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>c</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>KHÔNG cung cấp thông tin tài khoản của người nộp thuế tại TCTD, KBNN, chi nhánh ngân hàng nước ngoài</t>
+          <t>Cung cấp KHÔNG CHÍNH XÁC thông tin tiền lương, tiền công, thu nhập của người nộp thuế</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -4851,16 +4871,16 @@
         </is>
       </c>
       <c r="H65" s="3" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="I65" s="3" t="n">
         <v>10000000</v>
       </c>
-      <c r="I65" s="3" t="n">
-        <v>16000000</v>
-      </c>
       <c r="J65" s="3" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="K65" s="3" t="n">
         <v>5000000</v>
-      </c>
-      <c r="K65" s="3" t="n">
-        <v>8000000</v>
       </c>
       <c r="L65" s="2" t="inlineStr"/>
       <c r="M65" s="2" t="inlineStr"/>
@@ -4906,12 +4926,12 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>a</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>KHÔNG cung cấp thông tin tiền lương, tiền công, thu nhập của người nộp thuế</t>
+          <t>KHÔNG cung cấp thông tin tài sản, quyền, nghĩa vụ tài sản của người nộp thuế hoặc thông tin xác định nghĩa vụ thuế</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -4975,12 +4995,12 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>đ</t>
+          <t>b</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>Thông đồng, bao che người nộp thuế trốn thuế; không thực hiện quyết định cưỡng chế hành chính thuế (trừ Điều 18)</t>
+          <t>KHÔNG cung cấp thông tin tài khoản của người nộp thuế tại TCTD, KBNN, chi nhánh ngân hàng nước ngoài</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -5002,7 +5022,11 @@
       </c>
       <c r="L67" s="2" t="inlineStr"/>
       <c r="M67" s="2" t="inlineStr"/>
-      <c r="N67" s="2" t="inlineStr"/>
+      <c r="N67" s="2" t="inlineStr">
+        <is>
+          <t>Buộc cung cấp thông tin đầy đủ, chính xác</t>
+        </is>
+      </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
           <t>2026-01-16</t>
@@ -5022,142 +5046,138 @@
       <c r="S67" s="2" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" s="4" t="inlineStr">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>P067</t>
         </is>
       </c>
-      <c r="B68" s="4" t="inlineStr">
-        <is>
-          <t>Hóa đơn</t>
-        </is>
-      </c>
-      <c r="C68" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="D68" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E68" s="4" t="inlineStr"/>
-      <c r="F68" s="4" t="inlineStr">
-        <is>
-          <t>Không ký hợp đồng in bằng văn bản / tổ chức in in hóa đơn đặt in không có quyết định in</t>
-        </is>
-      </c>
-      <c r="G68" s="4" t="inlineStr">
-        <is>
-          <t>Phạt tiền (khung)</t>
-        </is>
-      </c>
-      <c r="H68" s="5" t="n">
-        <v>500000</v>
-      </c>
-      <c r="I68" s="5" t="n">
-        <v>1500000</v>
-      </c>
-      <c r="J68" s="5" t="n">
-        <v>250000</v>
-      </c>
-      <c r="K68" s="5" t="n">
-        <v>750000</v>
-      </c>
-      <c r="L68" s="4" t="inlineStr"/>
-      <c r="M68" s="4" t="inlineStr"/>
-      <c r="N68" s="4" t="inlineStr"/>
-      <c r="O68" s="4" t="inlineStr">
-        <is>
-          <t>2020-12-05</t>
-        </is>
-      </c>
-      <c r="P68" s="4" t="inlineStr">
-        <is>
-          <t>2026-01-15</t>
-        </is>
-      </c>
-      <c r="Q68" s="4" t="inlineStr">
-        <is>
-          <t>Đã bãi bỏ từ 16/01/2026 (chỉ áp dụng hành vi đã kết thúc trước ngày này)</t>
-        </is>
-      </c>
-      <c r="R68" s="4" t="inlineStr">
-        <is>
-          <t>NĐ 125/2020</t>
-        </is>
-      </c>
-      <c r="S68" s="4" t="inlineStr">
-        <is>
-          <t>Điều 20 NĐ125 bị bãi bỏ (một phần) bởi Điều 2 NĐ310.</t>
-        </is>
-      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>Thủ tục thuế</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="D68" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>KHÔNG cung cấp thông tin tiền lương, tiền công, thu nhập của người nộp thuế</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>Phạt tiền (khung)</t>
+        </is>
+      </c>
+      <c r="H68" s="3" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="I68" s="3" t="n">
+        <v>16000000</v>
+      </c>
+      <c r="J68" s="3" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="K68" s="3" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="L68" s="2" t="inlineStr"/>
+      <c r="M68" s="2" t="inlineStr"/>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>Buộc cung cấp thông tin đầy đủ, chính xác</t>
+        </is>
+      </c>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr"/>
+      <c r="Q68" s="2" t="inlineStr">
+        <is>
+          <t>Còn hiệu lực</t>
+        </is>
+      </c>
+      <c r="R68" s="2" t="inlineStr">
+        <is>
+          <t>NĐ 310/2025</t>
+        </is>
+      </c>
+      <c r="S68" s="2" t="inlineStr"/>
     </row>
     <row r="69">
-      <c r="A69" s="4" t="inlineStr">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>P068</t>
         </is>
       </c>
-      <c r="B69" s="4" t="inlineStr">
-        <is>
-          <t>Hóa đơn</t>
-        </is>
-      </c>
-      <c r="C69" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="D69" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="E69" s="4" t="inlineStr"/>
-      <c r="F69" s="4" t="inlineStr">
-        <is>
-          <t>Đặt in hóa đơn khi cơ quan thuế đã có văn bản thông báo không đủ điều kiện đặt in</t>
-        </is>
-      </c>
-      <c r="G69" s="4" t="inlineStr">
-        <is>
-          <t>Phạt tiền (khung)</t>
-        </is>
-      </c>
-      <c r="H69" s="5" t="n">
-        <v>2000000</v>
-      </c>
-      <c r="I69" s="5" t="n">
-        <v>4000000</v>
-      </c>
-      <c r="J69" s="5" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="K69" s="5" t="n">
-        <v>2000000</v>
-      </c>
-      <c r="L69" s="4" t="inlineStr"/>
-      <c r="M69" s="4" t="inlineStr"/>
-      <c r="N69" s="4" t="inlineStr"/>
-      <c r="O69" s="4" t="inlineStr">
-        <is>
-          <t>2020-12-05</t>
-        </is>
-      </c>
-      <c r="P69" s="4" t="inlineStr">
-        <is>
-          <t>2026-01-15</t>
-        </is>
-      </c>
-      <c r="Q69" s="4" t="inlineStr">
-        <is>
-          <t>Đã bãi bỏ từ 16/01/2026 (chỉ áp dụng hành vi đã kết thúc trước ngày này)</t>
-        </is>
-      </c>
-      <c r="R69" s="4" t="inlineStr">
-        <is>
-          <t>NĐ 125/2020</t>
-        </is>
-      </c>
-      <c r="S69" s="4" t="inlineStr">
-        <is>
-          <t>Điều 20 NĐ125 bị bãi bỏ (một phần) bởi Điều 2 NĐ310.</t>
-        </is>
-      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>Thủ tục thuế</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="D69" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>đ</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>Thông đồng, bao che người nộp thuế trốn thuế; không thực hiện quyết định cưỡng chế hành chính thuế (trừ Điều 18)</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>Phạt tiền (khung)</t>
+        </is>
+      </c>
+      <c r="H69" s="3" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="I69" s="3" t="n">
+        <v>16000000</v>
+      </c>
+      <c r="J69" s="3" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="K69" s="3" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="L69" s="2" t="inlineStr"/>
+      <c r="M69" s="2" t="inlineStr"/>
+      <c r="N69" s="2" t="inlineStr"/>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr"/>
+      <c r="Q69" s="2" t="inlineStr">
+        <is>
+          <t>Còn hiệu lực</t>
+        </is>
+      </c>
+      <c r="R69" s="2" t="inlineStr">
+        <is>
+          <t>NĐ 310/2025</t>
+        </is>
+      </c>
+      <c r="S69" s="2" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
@@ -5174,12 +5194,12 @@
         <v>20</v>
       </c>
       <c r="D70" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E70" s="4" t="inlineStr"/>
       <c r="F70" s="4" t="inlineStr">
         <is>
-          <t>Đặt in hóa đơn theo mẫu đã phát hành của tổ chức/cá nhân khác hoặc đặt in trùng số cùng ký hiệu</t>
+          <t>Không ký hợp đồng in bằng văn bản / tổ chức in in hóa đơn đặt in không có quyết định in</t>
         </is>
       </c>
       <c r="G70" s="4" t="inlineStr">
@@ -5188,16 +5208,16 @@
         </is>
       </c>
       <c r="H70" s="5" t="n">
-        <v>20000000</v>
+        <v>500000</v>
       </c>
       <c r="I70" s="5" t="n">
-        <v>50000000</v>
+        <v>1500000</v>
       </c>
       <c r="J70" s="5" t="n">
-        <v>10000000</v>
+        <v>250000</v>
       </c>
       <c r="K70" s="5" t="n">
-        <v>25000000</v>
+        <v>750000</v>
       </c>
       <c r="L70" s="4" t="inlineStr"/>
       <c r="M70" s="4" t="inlineStr"/>
@@ -5224,7 +5244,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>Điều 20 NĐ125 bị bãi bỏ (một phần) bởi Điều 2 NĐ310.</t>
+          <t>Điều 20 NĐ125 bị bãi bỏ hoàn toàn bởi Điều 2 NĐ310.</t>
         </is>
       </c>
     </row>
@@ -5240,7 +5260,7 @@
         </is>
       </c>
       <c r="C71" s="4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D71" s="4" t="n">
         <v>2</v>
@@ -5248,7 +5268,7 @@
       <c r="E71" s="4" t="inlineStr"/>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>In hóa đơn đặt in mà không ký hợp đồng in bằng văn bản</t>
+          <t>Đặt in hóa đơn khi cơ quan thuế đã có văn bản thông báo không đủ điều kiện đặt in (trừ trường hợp cơ quan thuế không có ý kiến bằng văn bản khi nhận đề nghị sử dụng hóa đơn đặt in)</t>
         </is>
       </c>
       <c r="G71" s="4" t="inlineStr">
@@ -5257,16 +5277,16 @@
         </is>
       </c>
       <c r="H71" s="5" t="n">
-        <v>500000</v>
+        <v>2000000</v>
       </c>
       <c r="I71" s="5" t="n">
-        <v>1500000</v>
+        <v>4000000</v>
       </c>
       <c r="J71" s="5" t="n">
-        <v>250000</v>
+        <v>1000000</v>
       </c>
       <c r="K71" s="5" t="n">
-        <v>750000</v>
+        <v>2000000</v>
       </c>
       <c r="L71" s="4" t="inlineStr"/>
       <c r="M71" s="4" t="inlineStr"/>
@@ -5293,7 +5313,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>Điều 21 NĐ125 bị bãi bỏ (một phần) bởi Điều 2 NĐ310.</t>
+          <t>Điều 20 NĐ125 bị bãi bỏ hoàn toàn bởi Điều 2 NĐ310.</t>
         </is>
       </c>
     </row>
@@ -5309,7 +5329,7 @@
         </is>
       </c>
       <c r="C72" s="4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D72" s="4" t="n">
         <v>3</v>
@@ -5317,7 +5337,7 @@
       <c r="E72" s="4" t="inlineStr"/>
       <c r="F72" s="4" t="inlineStr">
         <is>
-          <t>Báo cáo về việc in hóa đơn quá hạn từ 06 ngày trở lên</t>
+          <t>Đặt in hóa đơn theo mẫu đã phát hành của tổ chức/cá nhân khác hoặc đặt in trùng số cùng ký hiệu</t>
         </is>
       </c>
       <c r="G72" s="4" t="inlineStr">
@@ -5326,16 +5346,16 @@
         </is>
       </c>
       <c r="H72" s="5" t="n">
-        <v>2000000</v>
+        <v>20000000</v>
       </c>
       <c r="I72" s="5" t="n">
-        <v>4000000</v>
+        <v>50000000</v>
       </c>
       <c r="J72" s="5" t="n">
-        <v>1000000</v>
+        <v>10000000</v>
       </c>
       <c r="K72" s="5" t="n">
-        <v>2000000</v>
+        <v>25000000</v>
       </c>
       <c r="L72" s="4" t="inlineStr"/>
       <c r="M72" s="4" t="inlineStr"/>
@@ -5362,7 +5382,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>Điều 21 NĐ125 bị bãi bỏ (một phần) bởi Điều 2 NĐ310.</t>
+          <t>Điều 20 NĐ125 bị bãi bỏ hoàn toàn bởi Điều 2 NĐ310.</t>
         </is>
       </c>
     </row>
@@ -5381,12 +5401,12 @@
         <v>21</v>
       </c>
       <c r="D73" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E73" s="4" t="inlineStr"/>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>Không hủy sản phẩm in hỏng, in thừa khi thanh lý hợp đồng in</t>
+          <t>In hóa đơn đặt in mà không ký hợp đồng in bằng văn bản</t>
         </is>
       </c>
       <c r="G73" s="4" t="inlineStr">
@@ -5395,16 +5415,16 @@
         </is>
       </c>
       <c r="H73" s="5" t="n">
-        <v>4000000</v>
+        <v>500000</v>
       </c>
       <c r="I73" s="5" t="n">
-        <v>8000000</v>
+        <v>1500000</v>
       </c>
       <c r="J73" s="5" t="n">
-        <v>2000000</v>
+        <v>250000</v>
       </c>
       <c r="K73" s="5" t="n">
-        <v>4000000</v>
+        <v>750000</v>
       </c>
       <c r="L73" s="4" t="inlineStr"/>
       <c r="M73" s="4" t="inlineStr"/>
@@ -5431,7 +5451,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>Điều 21 NĐ125 bị bãi bỏ (một phần) bởi Điều 2 NĐ310.</t>
+          <t>Điều 21 NĐ125 bị bãi bỏ hoàn toàn bởi Điều 2 NĐ310.</t>
         </is>
       </c>
     </row>
@@ -5450,16 +5470,12 @@
         <v>21</v>
       </c>
       <c r="D74" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="E74" s="4" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="E74" s="4" t="inlineStr"/>
       <c r="F74" s="4" t="inlineStr">
         <is>
-          <t>Nhận in hóa đơn đặt in khi không đủ điều kiện in hóa đơn</t>
+          <t>Báo cáo về việc in hóa đơn quá hạn từ 06 ngày trở lên (trừ trường hợp cảnh cáo điểm b khoản 1)</t>
         </is>
       </c>
       <c r="G74" s="4" t="inlineStr">
@@ -5468,16 +5484,16 @@
         </is>
       </c>
       <c r="H74" s="5" t="n">
-        <v>6000000</v>
+        <v>2000000</v>
       </c>
       <c r="I74" s="5" t="n">
-        <v>18000000</v>
+        <v>4000000</v>
       </c>
       <c r="J74" s="5" t="n">
-        <v>3000000</v>
+        <v>1000000</v>
       </c>
       <c r="K74" s="5" t="n">
-        <v>9000000</v>
+        <v>2000000</v>
       </c>
       <c r="L74" s="4" t="inlineStr"/>
       <c r="M74" s="4" t="inlineStr"/>
@@ -5504,7 +5520,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>Điều 21 NĐ125 bị bãi bỏ (một phần) bởi Điều 2 NĐ310.</t>
+          <t>Điều 21 NĐ125 bị bãi bỏ hoàn toàn bởi Điều 2 NĐ310.</t>
         </is>
       </c>
     </row>
@@ -5523,16 +5539,12 @@
         <v>21</v>
       </c>
       <c r="D75" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="E75" s="4" t="inlineStr">
-        <is>
-          <t>b</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="E75" s="4" t="inlineStr"/>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>Không khai báo việc làm mất hóa đơn trước khi giao cho khách hàng</t>
+          <t>Không hủy sản phẩm in hỏng, in thừa khi thanh lý hợp đồng in</t>
         </is>
       </c>
       <c r="G75" s="4" t="inlineStr">
@@ -5541,16 +5553,16 @@
         </is>
       </c>
       <c r="H75" s="5" t="n">
-        <v>6000000</v>
+        <v>4000000</v>
       </c>
       <c r="I75" s="5" t="n">
-        <v>18000000</v>
+        <v>8000000</v>
       </c>
       <c r="J75" s="5" t="n">
-        <v>3000000</v>
+        <v>2000000</v>
       </c>
       <c r="K75" s="5" t="n">
-        <v>9000000</v>
+        <v>4000000</v>
       </c>
       <c r="L75" s="4" t="inlineStr"/>
       <c r="M75" s="4" t="inlineStr"/>
@@ -5577,7 +5589,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>Điều 21 NĐ125 bị bãi bỏ (một phần) bởi Điều 2 NĐ310.</t>
+          <t>Điều 21 NĐ125 bị bãi bỏ hoàn toàn bởi Điều 2 NĐ310.</t>
         </is>
       </c>
     </row>
@@ -5596,12 +5608,16 @@
         <v>21</v>
       </c>
       <c r="D76" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="E76" s="4" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="E76" s="4" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
       <c r="F76" s="4" t="inlineStr">
         <is>
-          <t>Chuyển nhượng toàn bộ hoặc một khâu trong hợp đồng in hóa đơn cho cơ sở in khác</t>
+          <t>Nhận in hóa đơn đặt in khi không đủ điều kiện in hóa đơn</t>
         </is>
       </c>
       <c r="G76" s="4" t="inlineStr">
@@ -5610,16 +5626,16 @@
         </is>
       </c>
       <c r="H76" s="5" t="n">
-        <v>10000000</v>
+        <v>6000000</v>
       </c>
       <c r="I76" s="5" t="n">
-        <v>20000000</v>
+        <v>18000000</v>
       </c>
       <c r="J76" s="5" t="n">
-        <v>5000000</v>
+        <v>3000000</v>
       </c>
       <c r="K76" s="5" t="n">
-        <v>10000000</v>
+        <v>9000000</v>
       </c>
       <c r="L76" s="4" t="inlineStr"/>
       <c r="M76" s="4" t="inlineStr"/>
@@ -5646,7 +5662,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>Điều 21 NĐ125 bị bãi bỏ (một phần) bởi Điều 2 NĐ310.</t>
+          <t>Điều 21 NĐ125 bị bãi bỏ hoàn toàn bởi Điều 2 NĐ310.</t>
         </is>
       </c>
     </row>
@@ -5665,12 +5681,16 @@
         <v>21</v>
       </c>
       <c r="D77" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="E77" s="4" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="E77" s="4" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>In hóa đơn theo mẫu đã phát hành của tổ chức/cá nhân khác hoặc in trùng số cùng ký hiệu</t>
+          <t>Không khai báo việc làm mất hóa đơn trước khi giao cho khách hàng</t>
         </is>
       </c>
       <c r="G77" s="4" t="inlineStr">
@@ -5679,16 +5699,16 @@
         </is>
       </c>
       <c r="H77" s="5" t="n">
-        <v>20000000</v>
+        <v>6000000</v>
       </c>
       <c r="I77" s="5" t="n">
-        <v>50000000</v>
+        <v>18000000</v>
       </c>
       <c r="J77" s="5" t="n">
-        <v>10000000</v>
+        <v>3000000</v>
       </c>
       <c r="K77" s="5" t="n">
-        <v>25000000</v>
+        <v>9000000</v>
       </c>
       <c r="L77" s="4" t="inlineStr"/>
       <c r="M77" s="4" t="inlineStr"/>
@@ -5715,7 +5735,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>Điều 21 NĐ125 bị bãi bỏ (một phần) bởi Điều 2 NĐ310.</t>
+          <t>Điều 21 NĐ125 bị bãi bỏ hoàn toàn bởi Điều 2 NĐ310.</t>
         </is>
       </c>
     </row>
@@ -5731,19 +5751,15 @@
         </is>
       </c>
       <c r="C78" s="4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D78" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E78" s="4" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="E78" s="4" t="inlineStr"/>
       <c r="F78" s="4" t="inlineStr">
         <is>
-          <t>Cho, bán hóa đơn đặt in chưa phát hành</t>
+          <t>Chuyển nhượng toàn bộ hoặc một khâu trong hợp đồng in hóa đơn cho cơ sở in khác</t>
         </is>
       </c>
       <c r="G78" s="4" t="inlineStr">
@@ -5752,16 +5768,16 @@
         </is>
       </c>
       <c r="H78" s="5" t="n">
-        <v>15000000</v>
+        <v>10000000</v>
       </c>
       <c r="I78" s="5" t="n">
-        <v>45000000</v>
+        <v>20000000</v>
       </c>
       <c r="J78" s="5" t="n">
-        <v>7500000</v>
+        <v>5000000</v>
       </c>
       <c r="K78" s="5" t="n">
-        <v>22500000</v>
+        <v>10000000</v>
       </c>
       <c r="L78" s="4" t="inlineStr"/>
       <c r="M78" s="4" t="inlineStr"/>
@@ -5788,7 +5804,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>Khoản 1 Điều 22 bị bãi bỏ bởi NĐ310.</t>
+          <t>Điều 21 NĐ125 bị bãi bỏ hoàn toàn bởi Điều 2 NĐ310.</t>
         </is>
       </c>
     </row>
@@ -5804,19 +5820,15 @@
         </is>
       </c>
       <c r="C79" s="4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D79" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E79" s="4" t="inlineStr">
-        <is>
-          <t>b</t>
-        </is>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="E79" s="4" t="inlineStr"/>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>Cho, bán hóa đơn đặt in của khách hàng đặt in hóa đơn cho tổ chức, cá nhân khác</t>
+          <t>In hóa đơn theo mẫu đã phát hành của tổ chức/cá nhân khác hoặc in trùng số cùng ký hiệu</t>
         </is>
       </c>
       <c r="G79" s="4" t="inlineStr">
@@ -5825,16 +5837,16 @@
         </is>
       </c>
       <c r="H79" s="5" t="n">
-        <v>15000000</v>
+        <v>20000000</v>
       </c>
       <c r="I79" s="5" t="n">
-        <v>45000000</v>
+        <v>50000000</v>
       </c>
       <c r="J79" s="5" t="n">
-        <v>7500000</v>
+        <v>10000000</v>
       </c>
       <c r="K79" s="5" t="n">
-        <v>22500000</v>
+        <v>25000000</v>
       </c>
       <c r="L79" s="4" t="inlineStr"/>
       <c r="M79" s="4" t="inlineStr"/>
@@ -5861,7 +5873,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>Khoản 1 Điều 22 bị bãi bỏ bởi NĐ310.</t>
+          <t>Điều 21 NĐ125 bị bãi bỏ hoàn toàn bởi Điều 2 NĐ310.</t>
         </is>
       </c>
     </row>
@@ -5877,7 +5889,7 @@
         </is>
       </c>
       <c r="C80" s="4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D80" s="4" t="n">
         <v>1</v>
@@ -5889,7 +5901,7 @@
       </c>
       <c r="F80" s="4" t="inlineStr">
         <is>
-          <t>Nộp thông báo điều chỉnh thông tin phát hành hóa đơn (đổi địa chỉ/tên) quá hạn 10-20 ngày</t>
+          <t>Cho, bán hóa đơn đặt in chưa phát hành</t>
         </is>
       </c>
       <c r="G80" s="4" t="inlineStr">
@@ -5898,16 +5910,16 @@
         </is>
       </c>
       <c r="H80" s="5" t="n">
-        <v>500000</v>
+        <v>15000000</v>
       </c>
       <c r="I80" s="5" t="n">
-        <v>1500000</v>
+        <v>45000000</v>
       </c>
       <c r="J80" s="5" t="n">
-        <v>250000</v>
+        <v>7500000</v>
       </c>
       <c r="K80" s="5" t="n">
-        <v>750000</v>
+        <v>22500000</v>
       </c>
       <c r="L80" s="4" t="inlineStr"/>
       <c r="M80" s="4" t="inlineStr"/>
@@ -5934,7 +5946,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>Điều 23 NĐ125 bị bãi bỏ (một phần) bởi Điều 2 NĐ310.</t>
+          <t>Khoản 1 Điều 22 bị bãi bỏ bởi NĐ310.</t>
         </is>
       </c>
     </row>
@@ -5950,7 +5962,7 @@
         </is>
       </c>
       <c r="C81" s="4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D81" s="4" t="n">
         <v>1</v>
@@ -5962,7 +5974,7 @@
       </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
-          <t>Nộp bảng kê hóa đơn chưa sử dụng khi đổi địa chỉ quá hạn 10-20 ngày</t>
+          <t>Cho, bán hóa đơn đặt in của khách hàng đặt in hóa đơn cho tổ chức, cá nhân khác</t>
         </is>
       </c>
       <c r="G81" s="4" t="inlineStr">
@@ -5971,16 +5983,16 @@
         </is>
       </c>
       <c r="H81" s="5" t="n">
-        <v>500000</v>
+        <v>15000000</v>
       </c>
       <c r="I81" s="5" t="n">
-        <v>1500000</v>
+        <v>45000000</v>
       </c>
       <c r="J81" s="5" t="n">
-        <v>250000</v>
+        <v>7500000</v>
       </c>
       <c r="K81" s="5" t="n">
-        <v>750000</v>
+        <v>22500000</v>
       </c>
       <c r="L81" s="4" t="inlineStr"/>
       <c r="M81" s="4" t="inlineStr"/>
@@ -6007,7 +6019,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>Điều 23 NĐ125 bị bãi bỏ (một phần) bởi Điều 2 NĐ310.</t>
+          <t>Khoản 1 Điều 22 bị bãi bỏ bởi NĐ310.</t>
         </is>
       </c>
     </row>
@@ -6030,12 +6042,12 @@
       </c>
       <c r="E82" s="4" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>a</t>
         </is>
       </c>
       <c r="F82" s="4" t="inlineStr">
         <is>
-          <t>Sử dụng hóa đơn đã thông báo phát hành nhưng chưa đến hạn sử dụng</t>
+          <t>Nộp thông báo điều chỉnh thông tin phát hành hóa đơn (đổi địa chỉ/tên) quá hạn 10-20 ngày</t>
         </is>
       </c>
       <c r="G82" s="4" t="inlineStr">
@@ -6080,7 +6092,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>Điều 23 NĐ125 bị bãi bỏ (một phần) bởi Điều 2 NĐ310.</t>
+          <t>Điều 23 NĐ125 bị bãi bỏ hoàn toàn bởi Điều 2 NĐ310.</t>
         </is>
       </c>
     </row>
@@ -6099,16 +6111,16 @@
         <v>23</v>
       </c>
       <c r="D83" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E83" s="4" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>b</t>
         </is>
       </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
-          <t>Lập thông báo phát hành không đầy đủ nội dung, đã bị cơ quan thuế thông báo điều chỉnh nhưng vẫn lập hóa đơn</t>
+          <t>Nộp bảng kê hóa đơn chưa sử dụng khi đổi địa chỉ quá hạn 10-20 ngày</t>
         </is>
       </c>
       <c r="G83" s="4" t="inlineStr">
@@ -6117,16 +6129,16 @@
         </is>
       </c>
       <c r="H83" s="5" t="n">
-        <v>2000000</v>
+        <v>500000</v>
       </c>
       <c r="I83" s="5" t="n">
-        <v>4000000</v>
+        <v>1500000</v>
       </c>
       <c r="J83" s="5" t="n">
-        <v>1000000</v>
+        <v>250000</v>
       </c>
       <c r="K83" s="5" t="n">
-        <v>2000000</v>
+        <v>750000</v>
       </c>
       <c r="L83" s="4" t="inlineStr"/>
       <c r="M83" s="4" t="inlineStr"/>
@@ -6153,7 +6165,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>Điều 23 NĐ125 bị bãi bỏ (một phần) bởi Điều 2 NĐ310.</t>
+          <t>Điều 23 NĐ125 bị bãi bỏ hoàn toàn bởi Điều 2 NĐ310.</t>
         </is>
       </c>
     </row>
@@ -6172,16 +6184,16 @@
         <v>23</v>
       </c>
       <c r="D84" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E84" s="4" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>c</t>
         </is>
       </c>
       <c r="F84" s="4" t="inlineStr">
         <is>
-          <t>Không niêm yết thông báo phát hành hóa đơn đúng quy định</t>
+          <t>Sử dụng hóa đơn đã thông báo phát hành nhưng chưa đến hạn sử dụng</t>
         </is>
       </c>
       <c r="G84" s="4" t="inlineStr">
@@ -6190,16 +6202,16 @@
         </is>
       </c>
       <c r="H84" s="5" t="n">
-        <v>2000000</v>
+        <v>500000</v>
       </c>
       <c r="I84" s="5" t="n">
-        <v>4000000</v>
+        <v>1500000</v>
       </c>
       <c r="J84" s="5" t="n">
-        <v>1000000</v>
+        <v>250000</v>
       </c>
       <c r="K84" s="5" t="n">
-        <v>2000000</v>
+        <v>750000</v>
       </c>
       <c r="L84" s="4" t="inlineStr"/>
       <c r="M84" s="4" t="inlineStr"/>
@@ -6226,7 +6238,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>Điều 23 NĐ125 bị bãi bỏ (một phần) bởi Điều 2 NĐ310.</t>
+          <t>Điều 23 NĐ125 bị bãi bỏ hoàn toàn bởi Điều 2 NĐ310.</t>
         </is>
       </c>
     </row>
@@ -6249,12 +6261,12 @@
       </c>
       <c r="E85" s="4" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>a</t>
         </is>
       </c>
       <c r="F85" s="4" t="inlineStr">
         <is>
-          <t>Nộp thông báo điều chỉnh thông tin phát hành hóa đơn (đổi địa chỉ/tên) quá hạn từ 21 ngày</t>
+          <t>Lập thông báo phát hành không đầy đủ nội dung, đã bị cơ quan thuế thông báo điều chỉnh nhưng vẫn lập hóa đơn</t>
         </is>
       </c>
       <c r="G85" s="4" t="inlineStr">
@@ -6299,7 +6311,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>Điều 23 NĐ125 bị bãi bỏ (một phần) bởi Điều 2 NĐ310.</t>
+          <t>Điều 23 NĐ125 bị bãi bỏ hoàn toàn bởi Điều 2 NĐ310.</t>
         </is>
       </c>
     </row>
@@ -6322,12 +6334,12 @@
       </c>
       <c r="E86" s="4" t="inlineStr">
         <is>
-          <t>d</t>
+          <t>b</t>
         </is>
       </c>
       <c r="F86" s="4" t="inlineStr">
         <is>
-          <t>Nộp bảng kê hóa đơn chưa sử dụng khi đổi địa chỉ quá hạn từ 21 ngày</t>
+          <t>Không niêm yết thông báo phát hành hóa đơn đúng quy định</t>
         </is>
       </c>
       <c r="G86" s="4" t="inlineStr">
@@ -6372,7 +6384,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>Điều 23 NĐ125 bị bãi bỏ (một phần) bởi Điều 2 NĐ310.</t>
+          <t>Điều 23 NĐ125 bị bãi bỏ hoàn toàn bởi Điều 2 NĐ310.</t>
         </is>
       </c>
     </row>
@@ -6391,12 +6403,16 @@
         <v>23</v>
       </c>
       <c r="D87" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="E87" s="4" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="E87" s="4" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
-          <t>Không lập thông báo phát hành hóa đơn trước khi đưa vào sử dụng (hóa đơn gắn nghiệp vụ đã khai, nộp thuế)</t>
+          <t>Nộp thông báo điều chỉnh thông tin phát hành hóa đơn (đổi địa chỉ/tên) quá hạn từ 21 ngày</t>
         </is>
       </c>
       <c r="G87" s="4" t="inlineStr">
@@ -6405,16 +6421,16 @@
         </is>
       </c>
       <c r="H87" s="5" t="n">
-        <v>6000000</v>
+        <v>2000000</v>
       </c>
       <c r="I87" s="5" t="n">
-        <v>18000000</v>
+        <v>4000000</v>
       </c>
       <c r="J87" s="5" t="n">
-        <v>3000000</v>
+        <v>1000000</v>
       </c>
       <c r="K87" s="5" t="n">
-        <v>9000000</v>
+        <v>2000000</v>
       </c>
       <c r="L87" s="4" t="inlineStr"/>
       <c r="M87" s="4" t="inlineStr"/>
@@ -6441,7 +6457,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>Điều 23 NĐ125 bị bãi bỏ (một phần) bởi Điều 2 NĐ310.</t>
+          <t>Điều 23 NĐ125 bị bãi bỏ hoàn toàn bởi Điều 2 NĐ310.</t>
         </is>
       </c>
     </row>
@@ -6457,26 +6473,38 @@
         </is>
       </c>
       <c r="C88" s="4" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D88" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E88" s="4" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="E88" s="4" t="inlineStr">
+        <is>
+          <t>d</t>
+        </is>
+      </c>
       <c r="F88" s="4" t="inlineStr">
         <is>
-          <t>Báo cáo về việc nhận in hóa đơn quá hạn 01-05 ngày (và 06-10 ngày nếu có tình tiết giảm nhẹ)</t>
+          <t>Nộp bảng kê hóa đơn chưa sử dụng khi đổi địa chỉ quá hạn từ 21 ngày</t>
         </is>
       </c>
       <c r="G88" s="4" t="inlineStr">
         <is>
-          <t>Cảnh cáo</t>
-        </is>
-      </c>
-      <c r="H88" s="5" t="n"/>
-      <c r="I88" s="5" t="n"/>
-      <c r="J88" s="5" t="n"/>
-      <c r="K88" s="5" t="n"/>
+          <t>Phạt tiền (khung)</t>
+        </is>
+      </c>
+      <c r="H88" s="5" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="I88" s="5" t="n">
+        <v>4000000</v>
+      </c>
+      <c r="J88" s="5" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="K88" s="5" t="n">
+        <v>2000000</v>
+      </c>
       <c r="L88" s="4" t="inlineStr"/>
       <c r="M88" s="4" t="inlineStr"/>
       <c r="N88" s="4" t="inlineStr"/>
@@ -6502,7 +6530,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>Điều 21 NĐ125 bị bãi bỏ bởi Điều 2 NĐ310.</t>
+          <t>Điều 23 NĐ125 bị bãi bỏ hoàn toàn bởi Điều 2 NĐ310.</t>
         </is>
       </c>
     </row>
@@ -6518,15 +6546,15 @@
         </is>
       </c>
       <c r="C89" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D89" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E89" s="4" t="inlineStr"/>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>Cho, bán hóa đơn mua của cơ quan thuế nhưng chưa lập</t>
+          <t>Không lập thông báo phát hành hóa đơn trước khi đưa vào sử dụng (hóa đơn gắn nghiệp vụ đã khai, nộp thuế hoặc chưa đến kỳ kê khai, nộp thuế)</t>
         </is>
       </c>
       <c r="G89" s="4" t="inlineStr">
@@ -6535,24 +6563,20 @@
         </is>
       </c>
       <c r="H89" s="5" t="n">
-        <v>20000000</v>
+        <v>6000000</v>
       </c>
       <c r="I89" s="5" t="n">
-        <v>50000000</v>
+        <v>18000000</v>
       </c>
       <c r="J89" s="5" t="n">
-        <v>10000000</v>
+        <v>3000000</v>
       </c>
       <c r="K89" s="5" t="n">
-        <v>25000000</v>
+        <v>9000000</v>
       </c>
       <c r="L89" s="4" t="inlineStr"/>
       <c r="M89" s="4" t="inlineStr"/>
-      <c r="N89" s="4" t="inlineStr">
-        <is>
-          <t>Buộc hủy hóa đơn; buộc nộp lại số lợi bất hợp pháp</t>
-        </is>
-      </c>
+      <c r="N89" s="4" t="inlineStr"/>
       <c r="O89" s="4" t="inlineStr">
         <is>
           <t>2020-12-05</t>
@@ -6565,7 +6589,7 @@
       </c>
       <c r="Q89" s="4" t="inlineStr">
         <is>
-          <t>Đã được thay bằng quy định mới từ 16/01/2026 (chỉ áp dụng hành vi đã kết thúc trước ngày này)</t>
+          <t>Đã bãi bỏ từ 16/01/2026 (chỉ áp dụng hành vi đã kết thúc trước ngày này)</t>
         </is>
       </c>
       <c r="R89" s="4" t="inlineStr">
@@ -6573,72 +6597,72 @@
           <t>NĐ 125/2020</t>
         </is>
       </c>
-      <c r="S89" s="4" t="inlineStr"/>
+      <c r="S89" s="4" t="inlineStr">
+        <is>
+          <t>Điều 23 NĐ125 bị bãi bỏ hoàn toàn bởi Điều 2 NĐ310.</t>
+        </is>
+      </c>
     </row>
     <row r="90">
-      <c r="A90" s="2" t="inlineStr">
+      <c r="A90" s="4" t="inlineStr">
         <is>
           <t>P089</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
+      <c r="B90" s="4" t="inlineStr">
         <is>
           <t>Hóa đơn</t>
         </is>
       </c>
-      <c r="C90" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="D90" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E90" s="2" t="inlineStr"/>
-      <c r="F90" s="2" t="inlineStr">
-        <is>
-          <t>Cho, bán hóa đơn</t>
-        </is>
-      </c>
-      <c r="G90" s="2" t="inlineStr">
-        <is>
-          <t>Phạt tiền (khung)</t>
-        </is>
-      </c>
-      <c r="H90" s="3" t="n">
-        <v>20000000</v>
-      </c>
-      <c r="I90" s="3" t="n">
-        <v>50000000</v>
-      </c>
-      <c r="J90" s="3" t="n">
-        <v>10000000</v>
-      </c>
-      <c r="K90" s="3" t="n">
-        <v>25000000</v>
-      </c>
-      <c r="L90" s="2" t="inlineStr"/>
-      <c r="M90" s="2" t="inlineStr"/>
-      <c r="N90" s="2" t="inlineStr">
-        <is>
-          <t>Buộc nộp lại số lợi bất hợp pháp (điểm b khoản 3 Điều 22 NĐ125)</t>
-        </is>
-      </c>
-      <c r="O90" s="2" t="inlineStr">
-        <is>
-          <t>2026-01-16</t>
-        </is>
-      </c>
-      <c r="P90" s="2" t="inlineStr"/>
-      <c r="Q90" s="2" t="inlineStr">
-        <is>
-          <t>Còn hiệu lực</t>
-        </is>
-      </c>
-      <c r="R90" s="2" t="inlineStr">
-        <is>
-          <t>NĐ 310/2025</t>
-        </is>
-      </c>
-      <c r="S90" s="2" t="inlineStr"/>
+      <c r="C90" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="D90" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E90" s="4" t="inlineStr"/>
+      <c r="F90" s="4" t="inlineStr">
+        <is>
+          <t>Báo cáo về việc nhận in hóa đơn quá hạn 01-05 ngày (và 06-10 ngày nếu có tình tiết giảm nhẹ)</t>
+        </is>
+      </c>
+      <c r="G90" s="4" t="inlineStr">
+        <is>
+          <t>Cảnh cáo</t>
+        </is>
+      </c>
+      <c r="H90" s="5" t="n"/>
+      <c r="I90" s="5" t="n"/>
+      <c r="J90" s="5" t="n"/>
+      <c r="K90" s="5" t="n"/>
+      <c r="L90" s="4" t="inlineStr"/>
+      <c r="M90" s="4" t="inlineStr"/>
+      <c r="N90" s="4" t="inlineStr"/>
+      <c r="O90" s="4" t="inlineStr">
+        <is>
+          <t>2020-12-05</t>
+        </is>
+      </c>
+      <c r="P90" s="4" t="inlineStr">
+        <is>
+          <t>2026-01-15</t>
+        </is>
+      </c>
+      <c r="Q90" s="4" t="inlineStr">
+        <is>
+          <t>Đã bãi bỏ từ 16/01/2026 (chỉ áp dụng hành vi đã kết thúc trước ngày này)</t>
+        </is>
+      </c>
+      <c r="R90" s="4" t="inlineStr">
+        <is>
+          <t>NĐ 125/2020</t>
+        </is>
+      </c>
+      <c r="S90" s="4" t="inlineStr">
+        <is>
+          <t>Điều 21 NĐ125 bị bãi bỏ bởi Điều 2 NĐ310.</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
@@ -6652,37 +6676,41 @@
         </is>
       </c>
       <c r="C91" s="4" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D91" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E91" s="4" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="E91" s="4" t="inlineStr"/>
       <c r="F91" s="4" t="inlineStr">
         <is>
-          <t>Lập hóa đơn không đúng thời điểm nhưng không dẫn đến chậm nghĩa vụ thuế</t>
+          <t>Cho, bán hóa đơn mua của cơ quan thuế nhưng chưa lập</t>
         </is>
       </c>
       <c r="G91" s="4" t="inlineStr">
         <is>
-          <t>Cảnh cáo</t>
-        </is>
-      </c>
-      <c r="H91" s="5" t="n"/>
-      <c r="I91" s="5" t="n"/>
-      <c r="J91" s="5" t="n"/>
-      <c r="K91" s="5" t="n"/>
+          <t>Phạt tiền (khung)</t>
+        </is>
+      </c>
+      <c r="H91" s="5" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="I91" s="5" t="n">
+        <v>50000000</v>
+      </c>
+      <c r="J91" s="5" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="K91" s="5" t="n">
+        <v>25000000</v>
+      </c>
       <c r="L91" s="4" t="inlineStr"/>
-      <c r="M91" s="4" t="inlineStr">
-        <is>
-          <t>Có tình tiết giảm nhẹ</t>
-        </is>
-      </c>
-      <c r="N91" s="4" t="inlineStr"/>
+      <c r="M91" s="4" t="inlineStr"/>
+      <c r="N91" s="4" t="inlineStr">
+        <is>
+          <t>Buộc hủy hóa đơn; buộc nộp lại số lợi bất hợp pháp</t>
+        </is>
+      </c>
       <c r="O91" s="4" t="inlineStr">
         <is>
           <t>2020-12-05</t>
@@ -6695,7 +6723,7 @@
       </c>
       <c r="Q91" s="4" t="inlineStr">
         <is>
-          <t>Đã bãi bỏ từ 16/01/2026 (chỉ áp dụng hành vi đã kết thúc trước ngày này)</t>
+          <t>Đã được thay bằng quy định mới từ 16/01/2026 (chỉ áp dụng hành vi đã kết thúc trước ngày này)</t>
         </is>
       </c>
       <c r="R91" s="4" t="inlineStr">
@@ -6717,36 +6745,44 @@
         </is>
       </c>
       <c r="C92" s="2" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D92" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E92" s="2" t="inlineStr">
-        <is>
-          <t>b</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="E92" s="2" t="inlineStr"/>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>Lập hóa đơn liên tục từ số nhỏ đến lớn nhưng khác quyển; đã hủy quyển số nhỏ sau khi phát hiện</t>
+          <t>Cho, bán hóa đơn</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>Cảnh cáo</t>
-        </is>
-      </c>
-      <c r="H92" s="3" t="n"/>
-      <c r="I92" s="3" t="n"/>
-      <c r="J92" s="3" t="n"/>
-      <c r="K92" s="3" t="n"/>
+          <t>Phạt tiền (khung)</t>
+        </is>
+      </c>
+      <c r="H92" s="3" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="I92" s="3" t="n">
+        <v>50000000</v>
+      </c>
+      <c r="J92" s="3" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="K92" s="3" t="n">
+        <v>25000000</v>
+      </c>
       <c r="L92" s="2" t="inlineStr"/>
       <c r="M92" s="2" t="inlineStr"/>
-      <c r="N92" s="2" t="inlineStr"/>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>Buộc nộp lại số lợi bất hợp pháp (điểm b khoản 3 Điều 22 NĐ125)</t>
+        </is>
+      </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>2020-12-05</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr"/>
@@ -6757,209 +6793,189 @@
       </c>
       <c r="R92" s="2" t="inlineStr">
         <is>
-          <t>NĐ 125/2020</t>
+          <t>NĐ 310/2025</t>
         </is>
       </c>
       <c r="S92" s="2" t="inlineStr"/>
     </row>
     <row r="93">
-      <c r="A93" s="2" t="inlineStr">
+      <c r="A93" s="4" t="inlineStr">
         <is>
           <t>P092</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
+      <c r="B93" s="4" t="inlineStr">
         <is>
           <t>Hóa đơn</t>
         </is>
       </c>
-      <c r="C93" s="2" t="n">
+      <c r="C93" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="D93" s="2" t="n">
+      <c r="D93" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="E93" s="2" t="inlineStr">
+      <c r="E93" s="4" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="F93" s="4" t="inlineStr">
+        <is>
+          <t>Lập hóa đơn không đúng thời điểm nhưng không dẫn đến chậm nghĩa vụ thuế</t>
+        </is>
+      </c>
+      <c r="G93" s="4" t="inlineStr">
+        <is>
+          <t>Cảnh cáo</t>
+        </is>
+      </c>
+      <c r="H93" s="5" t="n"/>
+      <c r="I93" s="5" t="n"/>
+      <c r="J93" s="5" t="n"/>
+      <c r="K93" s="5" t="n"/>
+      <c r="L93" s="4" t="inlineStr"/>
+      <c r="M93" s="4" t="inlineStr">
+        <is>
+          <t>Có tình tiết giảm nhẹ</t>
+        </is>
+      </c>
+      <c r="N93" s="4" t="inlineStr"/>
+      <c r="O93" s="4" t="inlineStr">
+        <is>
+          <t>2020-12-05</t>
+        </is>
+      </c>
+      <c r="P93" s="4" t="inlineStr">
+        <is>
+          <t>2026-01-15</t>
+        </is>
+      </c>
+      <c r="Q93" s="4" t="inlineStr">
+        <is>
+          <t>Đã bãi bỏ từ 16/01/2026 (chỉ áp dụng hành vi đã kết thúc trước ngày này)</t>
+        </is>
+      </c>
+      <c r="R93" s="4" t="inlineStr">
+        <is>
+          <t>NĐ 125/2020</t>
+        </is>
+      </c>
+      <c r="S93" s="4" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>P093</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>Hóa đơn</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="D94" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>Lập hóa đơn liên tục từ số nhỏ đến lớn nhưng khác quyển; đã hủy quyển số nhỏ sau khi phát hiện</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>Cảnh cáo</t>
+        </is>
+      </c>
+      <c r="H94" s="3" t="n"/>
+      <c r="I94" s="3" t="n"/>
+      <c r="J94" s="3" t="n"/>
+      <c r="K94" s="3" t="n"/>
+      <c r="L94" s="2" t="inlineStr"/>
+      <c r="M94" s="2" t="inlineStr"/>
+      <c r="N94" s="2" t="inlineStr"/>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>2020-12-05</t>
+        </is>
+      </c>
+      <c r="P94" s="2" t="inlineStr"/>
+      <c r="Q94" s="2" t="inlineStr">
+        <is>
+          <t>Còn hiệu lực</t>
+        </is>
+      </c>
+      <c r="R94" s="2" t="inlineStr">
+        <is>
+          <t>NĐ 125/2020</t>
+        </is>
+      </c>
+      <c r="S94" s="2" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>P094</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>Hóa đơn</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="D95" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
         <is>
           <t>c</t>
         </is>
       </c>
-      <c r="F93" s="2" t="inlineStr">
+      <c r="F95" s="2" t="inlineStr">
         <is>
           <t>Lập sai loại hóa đơn nhưng đã lập lại đúng trước khi có quyết định thanh tra/kiểm tra, không ảnh hưởng nghĩa vụ thuế</t>
         </is>
       </c>
-      <c r="G93" s="2" t="inlineStr">
+      <c r="G95" s="2" t="inlineStr">
         <is>
           <t>Cảnh cáo</t>
         </is>
       </c>
-      <c r="H93" s="3" t="n"/>
-      <c r="I93" s="3" t="n"/>
-      <c r="J93" s="3" t="n"/>
-      <c r="K93" s="3" t="n"/>
-      <c r="L93" s="2" t="inlineStr"/>
-      <c r="M93" s="2" t="inlineStr"/>
-      <c r="N93" s="2" t="inlineStr"/>
-      <c r="O93" s="2" t="inlineStr">
-        <is>
-          <t>2020-12-05</t>
-        </is>
-      </c>
-      <c r="P93" s="2" t="inlineStr"/>
-      <c r="Q93" s="2" t="inlineStr">
+      <c r="H95" s="3" t="n"/>
+      <c r="I95" s="3" t="n"/>
+      <c r="J95" s="3" t="n"/>
+      <c r="K95" s="3" t="n"/>
+      <c r="L95" s="2" t="inlineStr"/>
+      <c r="M95" s="2" t="inlineStr"/>
+      <c r="N95" s="2" t="inlineStr"/>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>2020-12-05</t>
+        </is>
+      </c>
+      <c r="P95" s="2" t="inlineStr"/>
+      <c r="Q95" s="2" t="inlineStr">
         <is>
           <t>Còn hiệu lực</t>
         </is>
       </c>
-      <c r="R93" s="2" t="inlineStr">
-        <is>
-          <t>NĐ 125/2020</t>
-        </is>
-      </c>
-      <c r="S93" s="2" t="inlineStr"/>
-    </row>
-    <row r="94">
-      <c r="A94" s="4" t="inlineStr">
-        <is>
-          <t>P093</t>
-        </is>
-      </c>
-      <c r="B94" s="4" t="inlineStr">
-        <is>
-          <t>Hóa đơn</t>
-        </is>
-      </c>
-      <c r="C94" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="D94" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="E94" s="4" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="F94" s="4" t="inlineStr">
-        <is>
-          <t>Không lập hóa đơn tổng hợp theo quy định</t>
-        </is>
-      </c>
-      <c r="G94" s="4" t="inlineStr">
-        <is>
-          <t>Phạt tiền (khung)</t>
-        </is>
-      </c>
-      <c r="H94" s="5" t="n">
-        <v>500000</v>
-      </c>
-      <c r="I94" s="5" t="n">
-        <v>1500000</v>
-      </c>
-      <c r="J94" s="5" t="n">
-        <v>250000</v>
-      </c>
-      <c r="K94" s="5" t="n">
-        <v>750000</v>
-      </c>
-      <c r="L94" s="4" t="inlineStr"/>
-      <c r="M94" s="4" t="inlineStr"/>
-      <c r="N94" s="4" t="inlineStr"/>
-      <c r="O94" s="4" t="inlineStr">
-        <is>
-          <t>2020-12-05</t>
-        </is>
-      </c>
-      <c r="P94" s="4" t="inlineStr">
-        <is>
-          <t>2026-01-15</t>
-        </is>
-      </c>
-      <c r="Q94" s="4" t="inlineStr">
-        <is>
-          <t>Đã được thay bằng quy định mới từ 16/01/2026 (chỉ áp dụng hành vi đã kết thúc trước ngày này)</t>
-        </is>
-      </c>
-      <c r="R94" s="4" t="inlineStr">
-        <is>
-          <t>NĐ 125/2020</t>
-        </is>
-      </c>
-      <c r="S94" s="4" t="inlineStr">
-        <is>
-          <t>Khoản 2 cũ bị thay hoàn toàn bởi NĐ310; hành vi 'không lập hóa đơn tổng hợp' không còn nêu riêng.</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="4" t="inlineStr">
-        <is>
-          <t>P094</t>
-        </is>
-      </c>
-      <c r="B95" s="4" t="inlineStr">
-        <is>
-          <t>Hóa đơn</t>
-        </is>
-      </c>
-      <c r="C95" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="D95" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="E95" s="4" t="inlineStr">
-        <is>
-          <t>b</t>
-        </is>
-      </c>
-      <c r="F95" s="4" t="inlineStr">
-        <is>
-          <t>Không lập hóa đơn cho hàng khuyến mại, quảng cáo, hàng mẫu, cho biếu tặng, trả lương</t>
-        </is>
-      </c>
-      <c r="G95" s="4" t="inlineStr">
-        <is>
-          <t>Phạt tiền (khung)</t>
-        </is>
-      </c>
-      <c r="H95" s="5" t="n">
-        <v>500000</v>
-      </c>
-      <c r="I95" s="5" t="n">
-        <v>1500000</v>
-      </c>
-      <c r="J95" s="5" t="n">
-        <v>250000</v>
-      </c>
-      <c r="K95" s="5" t="n">
-        <v>750000</v>
-      </c>
-      <c r="L95" s="4" t="inlineStr"/>
-      <c r="M95" s="4" t="inlineStr"/>
-      <c r="N95" s="4" t="inlineStr"/>
-      <c r="O95" s="4" t="inlineStr">
-        <is>
-          <t>2020-12-05</t>
-        </is>
-      </c>
-      <c r="P95" s="4" t="inlineStr">
-        <is>
-          <t>2026-01-15</t>
-        </is>
-      </c>
-      <c r="Q95" s="4" t="inlineStr">
-        <is>
-          <t>Đã được thay bằng quy định mới từ 16/01/2026 (chỉ áp dụng hành vi đã kết thúc trước ngày này)</t>
-        </is>
-      </c>
-      <c r="R95" s="4" t="inlineStr">
-        <is>
-          <t>NĐ 125/2020</t>
-        </is>
-      </c>
-      <c r="S95" s="4" t="inlineStr"/>
+      <c r="R95" s="2" t="inlineStr">
+        <is>
+          <t>NĐ 125/2020</t>
+        </is>
+      </c>
+      <c r="S95" s="2" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="4" t="inlineStr">
@@ -6976,12 +6992,16 @@
         <v>24</v>
       </c>
       <c r="D96" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="E96" s="4" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="E96" s="4" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
       <c r="F96" s="4" t="inlineStr">
         <is>
-          <t>Lập hóa đơn không đúng thời điểm nhưng không dẫn đến chậm nghĩa vụ thuế</t>
+          <t>Không lập hóa đơn tổng hợp theo quy định</t>
         </is>
       </c>
       <c r="G96" s="4" t="inlineStr">
@@ -6990,16 +7010,16 @@
         </is>
       </c>
       <c r="H96" s="5" t="n">
-        <v>3000000</v>
+        <v>500000</v>
       </c>
       <c r="I96" s="5" t="n">
-        <v>5000000</v>
+        <v>1500000</v>
       </c>
       <c r="J96" s="5" t="n">
-        <v>1500000</v>
+        <v>250000</v>
       </c>
       <c r="K96" s="5" t="n">
-        <v>2500000</v>
+        <v>750000</v>
       </c>
       <c r="L96" s="4" t="inlineStr"/>
       <c r="M96" s="4" t="inlineStr"/>
@@ -7024,7 +7044,11 @@
           <t>NĐ 125/2020</t>
         </is>
       </c>
-      <c r="S96" s="4" t="inlineStr"/>
+      <c r="S96" s="4" t="inlineStr">
+        <is>
+          <t>Khoản 2 cũ bị thay hoàn toàn bởi NĐ310; hành vi 'không lập hóa đơn tổng hợp' không còn nêu riêng.</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="4" t="inlineStr">
@@ -7041,16 +7065,16 @@
         <v>24</v>
       </c>
       <c r="D97" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E97" s="4" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>b</t>
         </is>
       </c>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t>Lập hóa đơn không đúng thời điểm theo quy định (trừ điểm a khoản 1, khoản 3)</t>
+          <t>Không lập hóa đơn cho hàng khuyến mại, quảng cáo, hàng mẫu, cho biếu tặng, trả lương</t>
         </is>
       </c>
       <c r="G97" s="4" t="inlineStr">
@@ -7059,16 +7083,16 @@
         </is>
       </c>
       <c r="H97" s="5" t="n">
-        <v>4000000</v>
+        <v>500000</v>
       </c>
       <c r="I97" s="5" t="n">
-        <v>8000000</v>
+        <v>1500000</v>
       </c>
       <c r="J97" s="5" t="n">
-        <v>2000000</v>
+        <v>250000</v>
       </c>
       <c r="K97" s="5" t="n">
-        <v>4000000</v>
+        <v>750000</v>
       </c>
       <c r="L97" s="4" t="inlineStr"/>
       <c r="M97" s="4" t="inlineStr"/>
@@ -7085,149 +7109,149 @@
       </c>
       <c r="Q97" s="4" t="inlineStr">
         <is>
+          <t>Đã được thay bằng quy định mới từ 16/01/2026 (chỉ áp dụng hành vi đã kết thúc trước ngày này)</t>
+        </is>
+      </c>
+      <c r="R97" s="4" t="inlineStr">
+        <is>
+          <t>NĐ 125/2020</t>
+        </is>
+      </c>
+      <c r="S97" s="4" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="4" t="inlineStr">
+        <is>
+          <t>P097</t>
+        </is>
+      </c>
+      <c r="B98" s="4" t="inlineStr">
+        <is>
+          <t>Hóa đơn</t>
+        </is>
+      </c>
+      <c r="C98" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="D98" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E98" s="4" t="inlineStr"/>
+      <c r="F98" s="4" t="inlineStr">
+        <is>
+          <t>Lập hóa đơn không đúng thời điểm nhưng không dẫn đến chậm nghĩa vụ thuế</t>
+        </is>
+      </c>
+      <c r="G98" s="4" t="inlineStr">
+        <is>
+          <t>Phạt tiền (khung)</t>
+        </is>
+      </c>
+      <c r="H98" s="5" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="I98" s="5" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="J98" s="5" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="K98" s="5" t="n">
+        <v>2500000</v>
+      </c>
+      <c r="L98" s="4" t="inlineStr"/>
+      <c r="M98" s="4" t="inlineStr"/>
+      <c r="N98" s="4" t="inlineStr"/>
+      <c r="O98" s="4" t="inlineStr">
+        <is>
+          <t>2020-12-05</t>
+        </is>
+      </c>
+      <c r="P98" s="4" t="inlineStr">
+        <is>
+          <t>2026-01-15</t>
+        </is>
+      </c>
+      <c r="Q98" s="4" t="inlineStr">
+        <is>
+          <t>Đã được thay bằng quy định mới từ 16/01/2026 (chỉ áp dụng hành vi đã kết thúc trước ngày này)</t>
+        </is>
+      </c>
+      <c r="R98" s="4" t="inlineStr">
+        <is>
+          <t>NĐ 125/2020</t>
+        </is>
+      </c>
+      <c r="S98" s="4" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="4" t="inlineStr">
+        <is>
+          <t>P098</t>
+        </is>
+      </c>
+      <c r="B99" s="4" t="inlineStr">
+        <is>
+          <t>Hóa đơn</t>
+        </is>
+      </c>
+      <c r="C99" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="D99" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="E99" s="4" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="F99" s="4" t="inlineStr">
+        <is>
+          <t>Lập hóa đơn không đúng thời điểm theo quy định (trừ điểm a khoản 1, khoản 3)</t>
+        </is>
+      </c>
+      <c r="G99" s="4" t="inlineStr">
+        <is>
+          <t>Phạt tiền (khung)</t>
+        </is>
+      </c>
+      <c r="H99" s="5" t="n">
+        <v>4000000</v>
+      </c>
+      <c r="I99" s="5" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="J99" s="5" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="K99" s="5" t="n">
+        <v>4000000</v>
+      </c>
+      <c r="L99" s="4" t="inlineStr"/>
+      <c r="M99" s="4" t="inlineStr"/>
+      <c r="N99" s="4" t="inlineStr"/>
+      <c r="O99" s="4" t="inlineStr">
+        <is>
+          <t>2020-12-05</t>
+        </is>
+      </c>
+      <c r="P99" s="4" t="inlineStr">
+        <is>
+          <t>2026-01-15</t>
+        </is>
+      </c>
+      <c r="Q99" s="4" t="inlineStr">
+        <is>
           <t>Đã bãi bỏ từ 16/01/2026 (chỉ áp dụng hành vi đã kết thúc trước ngày này)</t>
         </is>
       </c>
-      <c r="R97" s="4" t="inlineStr">
-        <is>
-          <t>NĐ 125/2020</t>
-        </is>
-      </c>
-      <c r="S97" s="4" t="inlineStr"/>
-    </row>
-    <row r="98">
-      <c r="A98" s="2" t="inlineStr">
-        <is>
-          <t>P097</t>
-        </is>
-      </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>Hóa đơn</t>
-        </is>
-      </c>
-      <c r="C98" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="D98" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="E98" s="2" t="inlineStr">
-        <is>
-          <t>b</t>
-        </is>
-      </c>
-      <c r="F98" s="2" t="inlineStr">
-        <is>
-          <t>Lập hóa đơn không theo thứ tự từ số nhỏ đến số lớn</t>
-        </is>
-      </c>
-      <c r="G98" s="2" t="inlineStr">
-        <is>
-          <t>Phạt tiền (khung)</t>
-        </is>
-      </c>
-      <c r="H98" s="3" t="n">
-        <v>4000000</v>
-      </c>
-      <c r="I98" s="3" t="n">
-        <v>8000000</v>
-      </c>
-      <c r="J98" s="3" t="n">
-        <v>2000000</v>
-      </c>
-      <c r="K98" s="3" t="n">
-        <v>4000000</v>
-      </c>
-      <c r="L98" s="2" t="inlineStr"/>
-      <c r="M98" s="2" t="inlineStr">
-        <is>
-          <t>Trừ trường hợp cảnh cáo điểm b khoản 1</t>
-        </is>
-      </c>
-      <c r="N98" s="2" t="inlineStr"/>
-      <c r="O98" s="2" t="inlineStr">
-        <is>
-          <t>2020-12-05</t>
-        </is>
-      </c>
-      <c r="P98" s="2" t="inlineStr"/>
-      <c r="Q98" s="2" t="inlineStr">
-        <is>
-          <t>Còn hiệu lực</t>
-        </is>
-      </c>
-      <c r="R98" s="2" t="inlineStr">
-        <is>
-          <t>NĐ 125/2020</t>
-        </is>
-      </c>
-      <c r="S98" s="2" t="inlineStr"/>
-    </row>
-    <row r="99">
-      <c r="A99" s="2" t="inlineStr">
-        <is>
-          <t>P098</t>
-        </is>
-      </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>Hóa đơn</t>
-        </is>
-      </c>
-      <c r="C99" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="D99" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="E99" s="2" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
-      <c r="F99" s="2" t="inlineStr">
-        <is>
-          <t>Lập hóa đơn ghi ngày trước ngày mua hóa đơn của cơ quan thuế</t>
-        </is>
-      </c>
-      <c r="G99" s="2" t="inlineStr">
-        <is>
-          <t>Phạt tiền (khung)</t>
-        </is>
-      </c>
-      <c r="H99" s="3" t="n">
-        <v>4000000</v>
-      </c>
-      <c r="I99" s="3" t="n">
-        <v>8000000</v>
-      </c>
-      <c r="J99" s="3" t="n">
-        <v>2000000</v>
-      </c>
-      <c r="K99" s="3" t="n">
-        <v>4000000</v>
-      </c>
-      <c r="L99" s="2" t="inlineStr"/>
-      <c r="M99" s="2" t="inlineStr"/>
-      <c r="N99" s="2" t="inlineStr"/>
-      <c r="O99" s="2" t="inlineStr">
-        <is>
-          <t>2020-12-05</t>
-        </is>
-      </c>
-      <c r="P99" s="2" t="inlineStr"/>
-      <c r="Q99" s="2" t="inlineStr">
-        <is>
-          <t>Còn hiệu lực</t>
-        </is>
-      </c>
-      <c r="R99" s="2" t="inlineStr">
-        <is>
-          <t>NĐ 125/2020</t>
-        </is>
-      </c>
-      <c r="S99" s="2" t="inlineStr"/>
+      <c r="R99" s="4" t="inlineStr">
+        <is>
+          <t>NĐ 125/2020</t>
+        </is>
+      </c>
+      <c r="S99" s="4" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
@@ -7248,12 +7272,12 @@
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>d</t>
+          <t>b</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>Lập sai loại hóa đơn đã giao cho người mua hoặc đã kê khai thuế</t>
+          <t>Lập hóa đơn không theo thứ tự từ số nhỏ đến số lớn</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
@@ -7276,14 +7300,10 @@
       <c r="L100" s="2" t="inlineStr"/>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>Trừ trường hợp cảnh cáo điểm c khoản 1</t>
-        </is>
-      </c>
-      <c r="N100" s="2" t="inlineStr">
-        <is>
-          <t>Buộc lập hóa đơn theo quy định khi người mua yêu cầu</t>
-        </is>
-      </c>
+          <t>Trừ trường hợp cảnh cáo điểm b khoản 1</t>
+        </is>
+      </c>
+      <c r="N100" s="2" t="inlineStr"/>
       <c r="O100" s="2" t="inlineStr">
         <is>
           <t>2020-12-05</t>
@@ -7321,12 +7341,12 @@
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>đ</t>
+          <t>c</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>Lập hóa đơn điện tử khi chưa có thông báo chấp thuận của cơ quan thuế</t>
+          <t>Lập hóa đơn ghi ngày trước ngày mua hóa đơn của cơ quan thuế</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
@@ -7386,12 +7406,12 @@
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>e</t>
+          <t>d</t>
         </is>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>Lập hóa đơn trong thời gian tạm ngừng hoạt động kinh doanh (trừ hợp đồng ký trước)</t>
+          <t>Lập sai loại hóa đơn đã giao cho người mua hoặc đã kê khai thuế</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
@@ -7412,8 +7432,16 @@
         <v>4000000</v>
       </c>
       <c r="L102" s="2" t="inlineStr"/>
-      <c r="M102" s="2" t="inlineStr"/>
-      <c r="N102" s="2" t="inlineStr"/>
+      <c r="M102" s="2" t="inlineStr">
+        <is>
+          <t>Trừ trường hợp cảnh cáo điểm c khoản 1</t>
+        </is>
+      </c>
+      <c r="N102" s="2" t="inlineStr">
+        <is>
+          <t>Buộc lập hóa đơn theo quy định (đến 15/01/2026: khi người mua yêu cầu; từ 16/01/2026 không còn điều kiện này)</t>
+        </is>
+      </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
           <t>2020-12-05</t>
@@ -7451,12 +7479,12 @@
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>đ</t>
         </is>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>Lập hóa đơn điện tử từ máy tính tiền không kết nối, chuyển dữ liệu điện tử với cơ quan thuế</t>
+          <t>Lập hóa đơn điện tử khi chưa có thông báo chấp thuận của cơ quan thuế</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
@@ -7498,73 +7526,69 @@
       <c r="S103" s="2" t="inlineStr"/>
     </row>
     <row r="104">
-      <c r="A104" s="4" t="inlineStr">
+      <c r="A104" s="2" t="inlineStr">
         <is>
           <t>P103</t>
         </is>
       </c>
-      <c r="B104" s="4" t="inlineStr">
+      <c r="B104" s="2" t="inlineStr">
         <is>
           <t>Hóa đơn</t>
         </is>
       </c>
-      <c r="C104" s="4" t="n">
+      <c r="C104" s="2" t="n">
         <v>24</v>
       </c>
-      <c r="D104" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="E104" s="4" t="inlineStr"/>
-      <c r="F104" s="4" t="inlineStr">
-        <is>
-          <t>Không lập hóa đơn khi bán hàng hóa, cung cấp dịch vụ cho người mua theo quy định</t>
-        </is>
-      </c>
-      <c r="G104" s="4" t="inlineStr">
-        <is>
-          <t>Phạt tiền (khung)</t>
-        </is>
-      </c>
-      <c r="H104" s="5" t="n">
-        <v>10000000</v>
-      </c>
-      <c r="I104" s="5" t="n">
-        <v>20000000</v>
-      </c>
-      <c r="J104" s="5" t="n">
-        <v>5000000</v>
-      </c>
-      <c r="K104" s="5" t="n">
-        <v>10000000</v>
-      </c>
-      <c r="L104" s="4" t="inlineStr"/>
-      <c r="M104" s="4" t="inlineStr"/>
-      <c r="N104" s="4" t="inlineStr">
-        <is>
-          <t>Buộc lập hóa đơn khi người mua yêu cầu</t>
-        </is>
-      </c>
-      <c r="O104" s="4" t="inlineStr">
-        <is>
-          <t>2020-12-05</t>
-        </is>
-      </c>
-      <c r="P104" s="4" t="inlineStr">
-        <is>
-          <t>2026-01-15</t>
-        </is>
-      </c>
-      <c r="Q104" s="4" t="inlineStr">
-        <is>
-          <t>Đã được thay bằng quy định mới từ 16/01/2026 (chỉ áp dụng hành vi đã kết thúc trước ngày này)</t>
-        </is>
-      </c>
-      <c r="R104" s="4" t="inlineStr">
-        <is>
-          <t>NĐ 125/2020</t>
-        </is>
-      </c>
-      <c r="S104" s="4" t="inlineStr"/>
+      <c r="D104" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>Lập hóa đơn trong thời gian tạm ngừng hoạt động kinh doanh (trừ hợp đồng ký trước)</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>Phạt tiền (khung)</t>
+        </is>
+      </c>
+      <c r="H104" s="3" t="n">
+        <v>4000000</v>
+      </c>
+      <c r="I104" s="3" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="J104" s="3" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="K104" s="3" t="n">
+        <v>4000000</v>
+      </c>
+      <c r="L104" s="2" t="inlineStr"/>
+      <c r="M104" s="2" t="inlineStr"/>
+      <c r="N104" s="2" t="inlineStr"/>
+      <c r="O104" s="2" t="inlineStr">
+        <is>
+          <t>2020-12-05</t>
+        </is>
+      </c>
+      <c r="P104" s="2" t="inlineStr"/>
+      <c r="Q104" s="2" t="inlineStr">
+        <is>
+          <t>Còn hiệu lực</t>
+        </is>
+      </c>
+      <c r="R104" s="2" t="inlineStr">
+        <is>
+          <t>NĐ 125/2020</t>
+        </is>
+      </c>
+      <c r="S104" s="2" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
@@ -7581,37 +7605,41 @@
         <v>24</v>
       </c>
       <c r="D105" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>g</t>
         </is>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>Lập hóa đơn KHÔNG ĐÚNG THỜI ĐIỂM theo quy định</t>
+          <t>Lập hóa đơn điện tử từ máy tính tiền không kết nối, chuyển dữ liệu điện tử với cơ quan thuế</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>Cảnh cáo</t>
-        </is>
-      </c>
-      <c r="H105" s="3" t="n"/>
-      <c r="I105" s="3" t="n"/>
-      <c r="J105" s="3" t="n"/>
-      <c r="K105" s="3" t="n"/>
+          <t>Phạt tiền (khung)</t>
+        </is>
+      </c>
+      <c r="H105" s="3" t="n">
+        <v>4000000</v>
+      </c>
+      <c r="I105" s="3" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="J105" s="3" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="K105" s="3" t="n">
+        <v>4000000</v>
+      </c>
       <c r="L105" s="2" t="inlineStr"/>
-      <c r="M105" s="2" t="inlineStr">
-        <is>
-          <t>Nhóm A: hàng KM/quảng cáo/mẫu, cho biếu tặng, trả lương, tiêu dùng nội bộ, cho vay mượn/hoàn trả: 01 số hóa đơn</t>
-        </is>
-      </c>
+      <c r="M105" s="2" t="inlineStr"/>
       <c r="N105" s="2" t="inlineStr"/>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2020-12-05</t>
         </is>
       </c>
       <c r="P105" s="2" t="inlineStr"/>
@@ -7622,85 +7650,81 @@
       </c>
       <c r="R105" s="2" t="inlineStr">
         <is>
-          <t>NĐ 310/2025</t>
-        </is>
-      </c>
-      <c r="S105" s="2" t="inlineStr">
-        <is>
-          <t>Nhiều hành vi trong cùng một vụ việc chỉ bị xử phạt một hành vi theo khung tương ứng tổng số hóa đơn (điểm đ khoản 3 Điều 5 NĐ125 mới).</t>
-        </is>
-      </c>
+          <t>NĐ 125/2020</t>
+        </is>
+      </c>
+      <c r="S105" s="2" t="inlineStr"/>
     </row>
     <row r="106">
-      <c r="A106" s="2" t="inlineStr">
+      <c r="A106" s="4" t="inlineStr">
         <is>
           <t>P105</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
+      <c r="B106" s="4" t="inlineStr">
         <is>
           <t>Hóa đơn</t>
         </is>
       </c>
-      <c r="C106" s="2" t="n">
+      <c r="C106" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="D106" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E106" s="2" t="inlineStr">
-        <is>
-          <t>b</t>
-        </is>
-      </c>
-      <c r="F106" s="2" t="inlineStr">
-        <is>
-          <t>Lập hóa đơn KHÔNG ĐÚNG THỜI ĐIỂM theo quy định</t>
-        </is>
-      </c>
-      <c r="G106" s="2" t="inlineStr">
-        <is>
-          <t>Phạt tiền (khung)</t>
-        </is>
-      </c>
-      <c r="H106" s="3" t="n">
-        <v>500000</v>
-      </c>
-      <c r="I106" s="3" t="n">
-        <v>1500000</v>
-      </c>
-      <c r="J106" s="3" t="n">
-        <v>250000</v>
-      </c>
-      <c r="K106" s="3" t="n">
-        <v>750000</v>
-      </c>
-      <c r="L106" s="2" t="inlineStr"/>
-      <c r="M106" s="2" t="inlineStr">
-        <is>
-          <t>Nhóm A: hàng KM/quảng cáo/mẫu, cho biếu tặng, trả lương, tiêu dùng nội bộ, cho vay mượn/hoàn trả: 02 đến dưới 10 số; Nhóm B: bán hàng hóa, cung cấp dịch vụ: 01 số</t>
-        </is>
-      </c>
-      <c r="N106" s="2" t="inlineStr"/>
-      <c r="O106" s="2" t="inlineStr">
-        <is>
-          <t>2026-01-16</t>
-        </is>
-      </c>
-      <c r="P106" s="2" t="inlineStr"/>
-      <c r="Q106" s="2" t="inlineStr">
-        <is>
-          <t>Còn hiệu lực</t>
-        </is>
-      </c>
-      <c r="R106" s="2" t="inlineStr">
-        <is>
-          <t>NĐ 310/2025</t>
-        </is>
-      </c>
-      <c r="S106" s="2" t="inlineStr">
-        <is>
-          <t>Nhiều hành vi trong cùng một vụ việc chỉ bị xử phạt một hành vi theo khung tương ứng tổng số hóa đơn (điểm đ khoản 3 Điều 5 NĐ125 mới).</t>
+      <c r="D106" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="E106" s="4" t="inlineStr"/>
+      <c r="F106" s="4" t="inlineStr">
+        <is>
+          <t>Không lập hóa đơn khi bán hàng hóa, cung cấp dịch vụ cho người mua theo quy định</t>
+        </is>
+      </c>
+      <c r="G106" s="4" t="inlineStr">
+        <is>
+          <t>Phạt tiền (khung)</t>
+        </is>
+      </c>
+      <c r="H106" s="5" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="I106" s="5" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="J106" s="5" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="K106" s="5" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="L106" s="4" t="inlineStr"/>
+      <c r="M106" s="4" t="inlineStr"/>
+      <c r="N106" s="4" t="inlineStr">
+        <is>
+          <t>Buộc lập hóa đơn khi người mua yêu cầu</t>
+        </is>
+      </c>
+      <c r="O106" s="4" t="inlineStr">
+        <is>
+          <t>2020-12-05</t>
+        </is>
+      </c>
+      <c r="P106" s="4" t="inlineStr">
+        <is>
+          <t>2026-01-15</t>
+        </is>
+      </c>
+      <c r="Q106" s="4" t="inlineStr">
+        <is>
+          <t>Đã bãi bỏ từ 16/01/2026 (chỉ áp dụng hành vi đã kết thúc trước ngày này)</t>
+        </is>
+      </c>
+      <c r="R106" s="4" t="inlineStr">
+        <is>
+          <t>NĐ 125/2020</t>
+        </is>
+      </c>
+      <c r="S106" s="4" t="inlineStr">
+        <is>
+          <t>Khoản 5 bị bãi bỏ bởi NĐ310; hành vi không lập hóa đơn nay thuộc khoản 3 mới (theo số lượng hóa đơn).</t>
         </is>
       </c>
     </row>
@@ -7723,7 +7747,7 @@
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>a</t>
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr">
@@ -7733,25 +7757,17 @@
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>Phạt tiền (khung)</t>
-        </is>
-      </c>
-      <c r="H107" s="3" t="n">
-        <v>2000000</v>
-      </c>
-      <c r="I107" s="3" t="n">
-        <v>5000000</v>
-      </c>
-      <c r="J107" s="3" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="K107" s="3" t="n">
-        <v>2500000</v>
-      </c>
+          <t>Cảnh cáo</t>
+        </is>
+      </c>
+      <c r="H107" s="3" t="n"/>
+      <c r="I107" s="3" t="n"/>
+      <c r="J107" s="3" t="n"/>
+      <c r="K107" s="3" t="n"/>
       <c r="L107" s="2" t="inlineStr"/>
       <c r="M107" s="2" t="inlineStr">
         <is>
-          <t>Nhóm A: hàng KM/quảng cáo/mẫu, cho biếu tặng, trả lương, tiêu dùng nội bộ, cho vay mượn/hoàn trả: 10 đến dưới 50 số; Nhóm B: bán hàng hóa, cung cấp dịch vụ: 02 đến dưới 10 số</t>
+          <t>Nhóm A: hàng KM/quảng cáo/mẫu, cho biếu tặng, trả lương, tiêu dùng nội bộ, cho vay mượn/hoàn trả: 01 số hóa đơn</t>
         </is>
       </c>
       <c r="N107" s="2" t="inlineStr"/>
@@ -7796,7 +7812,7 @@
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>d</t>
+          <t>b</t>
         </is>
       </c>
       <c r="F108" s="2" t="inlineStr">
@@ -7810,21 +7826,21 @@
         </is>
       </c>
       <c r="H108" s="3" t="n">
-        <v>5000000</v>
+        <v>500000</v>
       </c>
       <c r="I108" s="3" t="n">
-        <v>15000000</v>
+        <v>1500000</v>
       </c>
       <c r="J108" s="3" t="n">
-        <v>2500000</v>
+        <v>250000</v>
       </c>
       <c r="K108" s="3" t="n">
-        <v>7500000</v>
+        <v>750000</v>
       </c>
       <c r="L108" s="2" t="inlineStr"/>
       <c r="M108" s="2" t="inlineStr">
         <is>
-          <t>Nhóm A: hàng KM/quảng cáo/mẫu, cho biếu tặng, trả lương, tiêu dùng nội bộ, cho vay mượn/hoàn trả: 50 đến dưới 100 số; Nhóm B: bán hàng hóa, cung cấp dịch vụ: 10 đến dưới 20 số</t>
+          <t>Nhóm A: hàng KM/quảng cáo/mẫu, cho biếu tặng, trả lương, tiêu dùng nội bộ, cho vay mượn/hoàn trả: 02 đến dưới 10 số; Nhóm B: bán hàng hóa, cung cấp dịch vụ: 01 số</t>
         </is>
       </c>
       <c r="N108" s="2" t="inlineStr"/>
@@ -7869,7 +7885,7 @@
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>đ</t>
+          <t>c</t>
         </is>
       </c>
       <c r="F109" s="2" t="inlineStr">
@@ -7883,21 +7899,21 @@
         </is>
       </c>
       <c r="H109" s="3" t="n">
-        <v>15000000</v>
+        <v>2000000</v>
       </c>
       <c r="I109" s="3" t="n">
-        <v>30000000</v>
+        <v>5000000</v>
       </c>
       <c r="J109" s="3" t="n">
-        <v>7500000</v>
+        <v>1000000</v>
       </c>
       <c r="K109" s="3" t="n">
-        <v>15000000</v>
+        <v>2500000</v>
       </c>
       <c r="L109" s="2" t="inlineStr"/>
       <c r="M109" s="2" t="inlineStr">
         <is>
-          <t>Nhóm A: hàng KM/quảng cáo/mẫu, cho biếu tặng, trả lương, tiêu dùng nội bộ, cho vay mượn/hoàn trả: từ 100 số; Nhóm B: bán hàng hóa, cung cấp dịch vụ: 20 đến dưới 50 số</t>
+          <t>Nhóm A: hàng KM/quảng cáo/mẫu, cho biếu tặng, trả lương, tiêu dùng nội bộ, cho vay mượn/hoàn trả: 10 đến dưới 50 số; Nhóm B: bán hàng hóa, cung cấp dịch vụ: 02 đến dưới 10 số</t>
         </is>
       </c>
       <c r="N109" s="2" t="inlineStr"/>
@@ -7942,7 +7958,7 @@
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>e</t>
+          <t>d</t>
         </is>
       </c>
       <c r="F110" s="2" t="inlineStr">
@@ -7956,21 +7972,21 @@
         </is>
       </c>
       <c r="H110" s="3" t="n">
-        <v>30000000</v>
+        <v>5000000</v>
       </c>
       <c r="I110" s="3" t="n">
-        <v>50000000</v>
+        <v>15000000</v>
       </c>
       <c r="J110" s="3" t="n">
-        <v>15000000</v>
+        <v>2500000</v>
       </c>
       <c r="K110" s="3" t="n">
-        <v>25000000</v>
+        <v>7500000</v>
       </c>
       <c r="L110" s="2" t="inlineStr"/>
       <c r="M110" s="2" t="inlineStr">
         <is>
-          <t>Nhóm B: bán hàng hóa, cung cấp dịch vụ: 50 đến dưới 100 số</t>
+          <t>Nhóm A: hàng KM/quảng cáo/mẫu, cho biếu tặng, trả lương, tiêu dùng nội bộ, cho vay mượn/hoàn trả: 50 đến dưới 100 số; Nhóm B: bán hàng hóa, cung cấp dịch vụ: 10 đến dưới 20 số</t>
         </is>
       </c>
       <c r="N110" s="2" t="inlineStr"/>
@@ -8015,7 +8031,7 @@
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>đ</t>
         </is>
       </c>
       <c r="F111" s="2" t="inlineStr">
@@ -8029,21 +8045,21 @@
         </is>
       </c>
       <c r="H111" s="3" t="n">
-        <v>50000000</v>
+        <v>15000000</v>
       </c>
       <c r="I111" s="3" t="n">
-        <v>70000000</v>
+        <v>30000000</v>
       </c>
       <c r="J111" s="3" t="n">
-        <v>25000000</v>
+        <v>7500000</v>
       </c>
       <c r="K111" s="3" t="n">
-        <v>35000000</v>
+        <v>15000000</v>
       </c>
       <c r="L111" s="2" t="inlineStr"/>
       <c r="M111" s="2" t="inlineStr">
         <is>
-          <t>Nhóm B: bán hàng hóa, cung cấp dịch vụ: từ 100 số trở lên</t>
+          <t>Nhóm A: hàng KM/quảng cáo/mẫu, cho biếu tặng, trả lương, tiêu dùng nội bộ, cho vay mượn/hoàn trả: từ 100 số; Nhóm B: bán hàng hóa, cung cấp dịch vụ: 20 đến dưới 50 số</t>
         </is>
       </c>
       <c r="N111" s="2" t="inlineStr"/>
@@ -8084,38 +8100,42 @@
         <v>24</v>
       </c>
       <c r="D112" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>e</t>
         </is>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t>KHÔNG LẬP hóa đơn theo quy định</t>
+          <t>Lập hóa đơn KHÔNG ĐÚNG THỜI ĐIỂM theo quy định</t>
         </is>
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>Cảnh cáo</t>
-        </is>
-      </c>
-      <c r="H112" s="3" t="n"/>
-      <c r="I112" s="3" t="n"/>
-      <c r="J112" s="3" t="n"/>
-      <c r="K112" s="3" t="n"/>
+          <t>Phạt tiền (khung)</t>
+        </is>
+      </c>
+      <c r="H112" s="3" t="n">
+        <v>30000000</v>
+      </c>
+      <c r="I112" s="3" t="n">
+        <v>50000000</v>
+      </c>
+      <c r="J112" s="3" t="n">
+        <v>15000000</v>
+      </c>
+      <c r="K112" s="3" t="n">
+        <v>25000000</v>
+      </c>
       <c r="L112" s="2" t="inlineStr"/>
       <c r="M112" s="2" t="inlineStr">
         <is>
-          <t>Nhóm A: hàng KM/quảng cáo/mẫu, cho biếu tặng, trả lương, tiêu dùng nội bộ, cho vay mượn/hoàn trả: 01 số hóa đơn</t>
-        </is>
-      </c>
-      <c r="N112" s="2" t="inlineStr">
-        <is>
-          <t>Buộc lập hóa đơn theo quy định</t>
-        </is>
-      </c>
+          <t>Nhóm B: bán hàng hóa, cung cấp dịch vụ: 50 đến dưới 100 số</t>
+        </is>
+      </c>
+      <c r="N112" s="2" t="inlineStr"/>
       <c r="O112" s="2" t="inlineStr">
         <is>
           <t>2026-01-16</t>
@@ -8134,7 +8154,7 @@
       </c>
       <c r="S112" s="2" t="inlineStr">
         <is>
-          <t>Trường hợp không lập hóa đơn để trốn thuế: xem Điều 17.1.c (phạt 1-3 lần số thuế trốn). Điều 3(g) của khoản 3 Điều 5: nhiều hành vi trong một vụ việc chỉ phạt một hành vi.</t>
+          <t>Nhiều hành vi trong cùng một vụ việc chỉ bị xử phạt một hành vi theo khung tương ứng tổng số hóa đơn (điểm đ khoản 3 Điều 5 NĐ125 mới).</t>
         </is>
       </c>
     </row>
@@ -8153,16 +8173,16 @@
         <v>24</v>
       </c>
       <c r="D113" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>g</t>
         </is>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
-          <t>KHÔNG LẬP hóa đơn theo quy định</t>
+          <t>Lập hóa đơn KHÔNG ĐÚNG THỜI ĐIỂM theo quy định</t>
         </is>
       </c>
       <c r="G113" s="2" t="inlineStr">
@@ -8171,28 +8191,24 @@
         </is>
       </c>
       <c r="H113" s="3" t="n">
-        <v>1000000</v>
+        <v>50000000</v>
       </c>
       <c r="I113" s="3" t="n">
-        <v>2000000</v>
+        <v>70000000</v>
       </c>
       <c r="J113" s="3" t="n">
-        <v>500000</v>
+        <v>25000000</v>
       </c>
       <c r="K113" s="3" t="n">
-        <v>1000000</v>
+        <v>35000000</v>
       </c>
       <c r="L113" s="2" t="inlineStr"/>
       <c r="M113" s="2" t="inlineStr">
         <is>
-          <t>Nhóm A: hàng KM/quảng cáo/mẫu, cho biếu tặng, trả lương, tiêu dùng nội bộ, cho vay mượn/hoàn trả: 02 đến dưới 10 số; Nhóm B: bán hàng hóa, cung cấp dịch vụ: 01 số</t>
-        </is>
-      </c>
-      <c r="N113" s="2" t="inlineStr">
-        <is>
-          <t>Buộc lập hóa đơn theo quy định</t>
-        </is>
-      </c>
+          <t>Nhóm B: bán hàng hóa, cung cấp dịch vụ: từ 100 số trở lên</t>
+        </is>
+      </c>
+      <c r="N113" s="2" t="inlineStr"/>
       <c r="O113" s="2" t="inlineStr">
         <is>
           <t>2026-01-16</t>
@@ -8211,7 +8227,7 @@
       </c>
       <c r="S113" s="2" t="inlineStr">
         <is>
-          <t>Trường hợp không lập hóa đơn để trốn thuế: xem Điều 17.1.c (phạt 1-3 lần số thuế trốn). Điều 3(g) của khoản 3 Điều 5: nhiều hành vi trong một vụ việc chỉ phạt một hành vi.</t>
+          <t>Nhiều hành vi trong cùng một vụ việc chỉ bị xử phạt một hành vi theo khung tương ứng tổng số hóa đơn (điểm đ khoản 3 Điều 5 NĐ125 mới).</t>
         </is>
       </c>
     </row>
@@ -8234,7 +8250,7 @@
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>a</t>
         </is>
       </c>
       <c r="F114" s="2" t="inlineStr">
@@ -8244,25 +8260,17 @@
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>Phạt tiền (khung)</t>
-        </is>
-      </c>
-      <c r="H114" s="3" t="n">
-        <v>2000000</v>
-      </c>
-      <c r="I114" s="3" t="n">
-        <v>10000000</v>
-      </c>
-      <c r="J114" s="3" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="K114" s="3" t="n">
-        <v>5000000</v>
-      </c>
+          <t>Cảnh cáo</t>
+        </is>
+      </c>
+      <c r="H114" s="3" t="n"/>
+      <c r="I114" s="3" t="n"/>
+      <c r="J114" s="3" t="n"/>
+      <c r="K114" s="3" t="n"/>
       <c r="L114" s="2" t="inlineStr"/>
       <c r="M114" s="2" t="inlineStr">
         <is>
-          <t>Nhóm A: hàng KM/quảng cáo/mẫu, cho biếu tặng, trả lương, tiêu dùng nội bộ, cho vay mượn/hoàn trả: 10 đến dưới 50 số; Nhóm B: bán hàng hóa, cung cấp dịch vụ: 02 đến dưới 10 số</t>
+          <t>Nhóm A: hàng KM/quảng cáo/mẫu, cho biếu tặng, trả lương, tiêu dùng nội bộ, cho vay mượn/hoàn trả: 01 số hóa đơn</t>
         </is>
       </c>
       <c r="N114" s="2" t="inlineStr">
@@ -8288,7 +8296,7 @@
       </c>
       <c r="S114" s="2" t="inlineStr">
         <is>
-          <t>Trường hợp không lập hóa đơn để trốn thuế: xem Điều 17.1.c (phạt 1-3 lần số thuế trốn). Điều 3(g) của khoản 3 Điều 5: nhiều hành vi trong một vụ việc chỉ phạt một hành vi.</t>
+          <t>Trường hợp không lập hóa đơn để trốn thuế: xem Điều 17.1.c (phạt 1-3 lần số thuế trốn). Điểm e khoản 3 Điều 5 NĐ125 (sửa bởi NĐ310): nhiều hành vi không lập hóa đơn trong một vụ việc chỉ phạt một hành vi.</t>
         </is>
       </c>
     </row>
@@ -8311,7 +8319,7 @@
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>d</t>
+          <t>b</t>
         </is>
       </c>
       <c r="F115" s="2" t="inlineStr">
@@ -8325,21 +8333,21 @@
         </is>
       </c>
       <c r="H115" s="3" t="n">
-        <v>10000000</v>
+        <v>1000000</v>
       </c>
       <c r="I115" s="3" t="n">
-        <v>30000000</v>
+        <v>2000000</v>
       </c>
       <c r="J115" s="3" t="n">
-        <v>5000000</v>
+        <v>500000</v>
       </c>
       <c r="K115" s="3" t="n">
-        <v>15000000</v>
+        <v>1000000</v>
       </c>
       <c r="L115" s="2" t="inlineStr"/>
       <c r="M115" s="2" t="inlineStr">
         <is>
-          <t>Nhóm A: hàng KM/quảng cáo/mẫu, cho biếu tặng, trả lương, tiêu dùng nội bộ, cho vay mượn/hoàn trả: 50 đến dưới 100 số; Nhóm B: bán hàng hóa, cung cấp dịch vụ: 10 đến dưới 20 số</t>
+          <t>Nhóm A: hàng KM/quảng cáo/mẫu, cho biếu tặng, trả lương, tiêu dùng nội bộ, cho vay mượn/hoàn trả: 02 đến dưới 10 số; Nhóm B: bán hàng hóa, cung cấp dịch vụ: 01 số</t>
         </is>
       </c>
       <c r="N115" s="2" t="inlineStr">
@@ -8365,7 +8373,7 @@
       </c>
       <c r="S115" s="2" t="inlineStr">
         <is>
-          <t>Trường hợp không lập hóa đơn để trốn thuế: xem Điều 17.1.c (phạt 1-3 lần số thuế trốn). Điều 3(g) của khoản 3 Điều 5: nhiều hành vi trong một vụ việc chỉ phạt một hành vi.</t>
+          <t>Trường hợp không lập hóa đơn để trốn thuế: xem Điều 17.1.c (phạt 1-3 lần số thuế trốn). Điểm e khoản 3 Điều 5 NĐ125 (sửa bởi NĐ310): nhiều hành vi không lập hóa đơn trong một vụ việc chỉ phạt một hành vi.</t>
         </is>
       </c>
     </row>
@@ -8388,7 +8396,7 @@
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>đ</t>
+          <t>c</t>
         </is>
       </c>
       <c r="F116" s="2" t="inlineStr">
@@ -8402,21 +8410,21 @@
         </is>
       </c>
       <c r="H116" s="3" t="n">
-        <v>30000000</v>
+        <v>2000000</v>
       </c>
       <c r="I116" s="3" t="n">
-        <v>50000000</v>
+        <v>10000000</v>
       </c>
       <c r="J116" s="3" t="n">
-        <v>15000000</v>
+        <v>1000000</v>
       </c>
       <c r="K116" s="3" t="n">
-        <v>25000000</v>
+        <v>5000000</v>
       </c>
       <c r="L116" s="2" t="inlineStr"/>
       <c r="M116" s="2" t="inlineStr">
         <is>
-          <t>Nhóm A: hàng KM/quảng cáo/mẫu, cho biếu tặng, trả lương, tiêu dùng nội bộ, cho vay mượn/hoàn trả: từ 100 số; Nhóm B: bán hàng hóa, cung cấp dịch vụ: 20 đến dưới 50 số</t>
+          <t>Nhóm A: hàng KM/quảng cáo/mẫu, cho biếu tặng, trả lương, tiêu dùng nội bộ, cho vay mượn/hoàn trả: 10 đến dưới 50 số; Nhóm B: bán hàng hóa, cung cấp dịch vụ: 02 đến dưới 10 số</t>
         </is>
       </c>
       <c r="N116" s="2" t="inlineStr">
@@ -8442,7 +8450,7 @@
       </c>
       <c r="S116" s="2" t="inlineStr">
         <is>
-          <t>Trường hợp không lập hóa đơn để trốn thuế: xem Điều 17.1.c (phạt 1-3 lần số thuế trốn). Điều 3(g) của khoản 3 Điều 5: nhiều hành vi trong một vụ việc chỉ phạt một hành vi.</t>
+          <t>Trường hợp không lập hóa đơn để trốn thuế: xem Điều 17.1.c (phạt 1-3 lần số thuế trốn). Điểm e khoản 3 Điều 5 NĐ125 (sửa bởi NĐ310): nhiều hành vi không lập hóa đơn trong một vụ việc chỉ phạt một hành vi.</t>
         </is>
       </c>
     </row>
@@ -8465,7 +8473,7 @@
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>e</t>
+          <t>d</t>
         </is>
       </c>
       <c r="F117" s="2" t="inlineStr">
@@ -8479,21 +8487,21 @@
         </is>
       </c>
       <c r="H117" s="3" t="n">
-        <v>60000000</v>
+        <v>10000000</v>
       </c>
       <c r="I117" s="3" t="n">
-        <v>80000000</v>
+        <v>30000000</v>
       </c>
       <c r="J117" s="3" t="n">
-        <v>30000000</v>
+        <v>5000000</v>
       </c>
       <c r="K117" s="3" t="n">
-        <v>40000000</v>
+        <v>15000000</v>
       </c>
       <c r="L117" s="2" t="inlineStr"/>
       <c r="M117" s="2" t="inlineStr">
         <is>
-          <t>Nhóm B: bán hàng hóa, cung cấp dịch vụ: từ 50 số hóa đơn trở lên</t>
+          <t>Nhóm A: hàng KM/quảng cáo/mẫu, cho biếu tặng, trả lương, tiêu dùng nội bộ, cho vay mượn/hoàn trả: 50 đến dưới 100 số; Nhóm B: bán hàng hóa, cung cấp dịch vụ: 10 đến dưới 20 số</t>
         </is>
       </c>
       <c r="N117" s="2" t="inlineStr">
@@ -8519,7 +8527,7 @@
       </c>
       <c r="S117" s="2" t="inlineStr">
         <is>
-          <t>Trường hợp không lập hóa đơn để trốn thuế: xem Điều 17.1.c (phạt 1-3 lần số thuế trốn). Điều 3(g) của khoản 3 Điều 5: nhiều hành vi trong một vụ việc chỉ phạt một hành vi.</t>
+          <t>Trường hợp không lập hóa đơn để trốn thuế: xem Điều 17.1.c (phạt 1-3 lần số thuế trốn). Điểm e khoản 3 Điều 5 NĐ125 (sửa bởi NĐ310): nhiều hành vi không lập hóa đơn trong một vụ việc chỉ phạt một hành vi.</t>
         </is>
       </c>
     </row>
@@ -8535,36 +8543,52 @@
         </is>
       </c>
       <c r="C118" s="2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D118" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E118" s="2" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>đ</t>
+        </is>
+      </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
-          <t>Khai báo mất, cháy, hỏng hóa đơn quá hạn 01-05 ngày</t>
+          <t>KHÔNG LẬP hóa đơn theo quy định</t>
         </is>
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>Cảnh cáo</t>
-        </is>
-      </c>
-      <c r="H118" s="3" t="n"/>
-      <c r="I118" s="3" t="n"/>
-      <c r="J118" s="3" t="n"/>
-      <c r="K118" s="3" t="n"/>
+          <t>Phạt tiền (khung)</t>
+        </is>
+      </c>
+      <c r="H118" s="3" t="n">
+        <v>30000000</v>
+      </c>
+      <c r="I118" s="3" t="n">
+        <v>50000000</v>
+      </c>
+      <c r="J118" s="3" t="n">
+        <v>15000000</v>
+      </c>
+      <c r="K118" s="3" t="n">
+        <v>25000000</v>
+      </c>
       <c r="L118" s="2" t="inlineStr"/>
       <c r="M118" s="2" t="inlineStr">
         <is>
-          <t>Có tình tiết giảm nhẹ</t>
-        </is>
-      </c>
-      <c r="N118" s="2" t="inlineStr"/>
+          <t>Nhóm A: hàng KM/quảng cáo/mẫu, cho biếu tặng, trả lương, tiêu dùng nội bộ, cho vay mượn/hoàn trả: từ 100 số; Nhóm B: bán hàng hóa, cung cấp dịch vụ: 20 đến dưới 50 số</t>
+        </is>
+      </c>
+      <c r="N118" s="2" t="inlineStr">
+        <is>
+          <t>Buộc lập hóa đơn theo quy định</t>
+        </is>
+      </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
-          <t>2020-12-05</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="P118" s="2" t="inlineStr"/>
@@ -8575,12 +8599,12 @@
       </c>
       <c r="R118" s="2" t="inlineStr">
         <is>
-          <t>NĐ 125/2020+310/2025</t>
+          <t>NĐ 310/2025</t>
         </is>
       </c>
       <c r="S118" s="2" t="inlineStr">
         <is>
-          <t>NĐ310 chỉ sửa tên Điều 25.</t>
+          <t>Trường hợp không lập hóa đơn để trốn thuế: xem Điều 17.1.c (phạt 1-3 lần số thuế trốn). Điểm e khoản 3 Điều 5 NĐ125 (sửa bởi NĐ310): nhiều hành vi không lập hóa đơn trong một vụ việc chỉ phạt một hành vi.</t>
         </is>
       </c>
     </row>
@@ -8596,15 +8620,19 @@
         </is>
       </c>
       <c r="C119" s="2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D119" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E119" s="2" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="E119" s="2" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
-          <t>Khai báo mất, cháy, hỏng hóa đơn quá hạn 01-05 ngày</t>
+          <t>KHÔNG LẬP hóa đơn theo quy định</t>
         </is>
       </c>
       <c r="G119" s="2" t="inlineStr">
@@ -8613,27 +8641,31 @@
         </is>
       </c>
       <c r="H119" s="3" t="n">
-        <v>1000000</v>
+        <v>60000000</v>
       </c>
       <c r="I119" s="3" t="n">
-        <v>4000000</v>
+        <v>80000000</v>
       </c>
       <c r="J119" s="3" t="n">
-        <v>500000</v>
+        <v>30000000</v>
       </c>
       <c r="K119" s="3" t="n">
-        <v>2000000</v>
+        <v>40000000</v>
       </c>
       <c r="L119" s="2" t="inlineStr"/>
       <c r="M119" s="2" t="inlineStr">
         <is>
-          <t>Trừ trường hợp cảnh cáo khoản 1</t>
-        </is>
-      </c>
-      <c r="N119" s="2" t="inlineStr"/>
+          <t>Nhóm B: bán hàng hóa, cung cấp dịch vụ: từ 50 số hóa đơn trở lên</t>
+        </is>
+      </c>
+      <c r="N119" s="2" t="inlineStr">
+        <is>
+          <t>Buộc lập hóa đơn theo quy định</t>
+        </is>
+      </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
-          <t>2020-12-05</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="P119" s="2" t="inlineStr"/>
@@ -8644,10 +8676,14 @@
       </c>
       <c r="R119" s="2" t="inlineStr">
         <is>
-          <t>NĐ 125/2020</t>
-        </is>
-      </c>
-      <c r="S119" s="2" t="inlineStr"/>
+          <t>NĐ 310/2025</t>
+        </is>
+      </c>
+      <c r="S119" s="2" t="inlineStr">
+        <is>
+          <t>Trường hợp không lập hóa đơn để trốn thuế: xem Điều 17.1.c (phạt 1-3 lần số thuế trốn). Điểm e khoản 3 Điều 5 NĐ125 (sửa bởi NĐ310): nhiều hành vi không lập hóa đơn trong một vụ việc chỉ phạt một hành vi.</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
@@ -8664,37 +8700,29 @@
         <v>25</v>
       </c>
       <c r="D120" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="E120" s="2" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="E120" s="2" t="inlineStr"/>
       <c r="F120" s="2" t="inlineStr">
         <is>
-          <t>Khai báo mất, cháy, hỏng hóa đơn quá hạn từ 06 ngày</t>
+          <t>Khai báo mất, cháy, hỏng hóa đơn quá hạn 01-05 ngày</t>
         </is>
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>Phạt tiền (khung)</t>
-        </is>
-      </c>
-      <c r="H120" s="3" t="n">
-        <v>4000000</v>
-      </c>
-      <c r="I120" s="3" t="n">
-        <v>8000000</v>
-      </c>
-      <c r="J120" s="3" t="n">
-        <v>2000000</v>
-      </c>
-      <c r="K120" s="3" t="n">
-        <v>4000000</v>
-      </c>
+          <t>Cảnh cáo</t>
+        </is>
+      </c>
+      <c r="H120" s="3" t="n"/>
+      <c r="I120" s="3" t="n"/>
+      <c r="J120" s="3" t="n"/>
+      <c r="K120" s="3" t="n"/>
       <c r="L120" s="2" t="inlineStr"/>
-      <c r="M120" s="2" t="inlineStr"/>
+      <c r="M120" s="2" t="inlineStr">
+        <is>
+          <t>Có tình tiết giảm nhẹ</t>
+        </is>
+      </c>
       <c r="N120" s="2" t="inlineStr"/>
       <c r="O120" s="2" t="inlineStr">
         <is>
@@ -8709,10 +8737,14 @@
       </c>
       <c r="R120" s="2" t="inlineStr">
         <is>
-          <t>NĐ 125/2020</t>
-        </is>
-      </c>
-      <c r="S120" s="2" t="inlineStr"/>
+          <t>NĐ 125/2020+310/2025</t>
+        </is>
+      </c>
+      <c r="S120" s="2" t="inlineStr">
+        <is>
+          <t>NĐ310 chỉ sửa tên Điều 25.</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
@@ -8729,16 +8761,12 @@
         <v>25</v>
       </c>
       <c r="D121" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="E121" s="2" t="inlineStr">
-        <is>
-          <t>b</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="E121" s="2" t="inlineStr"/>
       <c r="F121" s="2" t="inlineStr">
         <is>
-          <t>Không khai báo mất, cháy, hỏng hóa đơn</t>
+          <t>Khai báo mất, cháy, hỏng hóa đơn quá hạn 01-05 ngày</t>
         </is>
       </c>
       <c r="G121" s="2" t="inlineStr">
@@ -8747,19 +8775,23 @@
         </is>
       </c>
       <c r="H121" s="3" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="I121" s="3" t="n">
         <v>4000000</v>
       </c>
-      <c r="I121" s="3" t="n">
-        <v>8000000</v>
-      </c>
       <c r="J121" s="3" t="n">
+        <v>500000</v>
+      </c>
+      <c r="K121" s="3" t="n">
         <v>2000000</v>
       </c>
-      <c r="K121" s="3" t="n">
-        <v>4000000</v>
-      </c>
       <c r="L121" s="2" t="inlineStr"/>
-      <c r="M121" s="2" t="inlineStr"/>
+      <c r="M121" s="2" t="inlineStr">
+        <is>
+          <t>Trừ trường hợp cảnh cáo khoản 1</t>
+        </is>
+      </c>
       <c r="N121" s="2" t="inlineStr"/>
       <c r="O121" s="2" t="inlineStr">
         <is>
@@ -8791,10 +8823,10 @@
         </is>
       </c>
       <c r="C122" s="2" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D122" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
@@ -8803,24 +8835,28 @@
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
-          <t>Làm mất, cháy, hỏng hóa đơn đã lập (trừ liên giao khách), đã kê khai thuế, có chứng từ chứng minh</t>
+          <t>Khai báo mất, cháy, hỏng hóa đơn quá hạn từ 06 ngày</t>
         </is>
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>Cảnh cáo</t>
-        </is>
-      </c>
-      <c r="H122" s="3" t="n"/>
-      <c r="I122" s="3" t="n"/>
-      <c r="J122" s="3" t="n"/>
-      <c r="K122" s="3" t="n"/>
+          <t>Phạt tiền (khung)</t>
+        </is>
+      </c>
+      <c r="H122" s="3" t="n">
+        <v>4000000</v>
+      </c>
+      <c r="I122" s="3" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="J122" s="3" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="K122" s="3" t="n">
+        <v>4000000</v>
+      </c>
       <c r="L122" s="2" t="inlineStr"/>
-      <c r="M122" s="2" t="inlineStr">
-        <is>
-          <t>Có tình tiết giảm nhẹ</t>
-        </is>
-      </c>
+      <c r="M122" s="2" t="inlineStr"/>
       <c r="N122" s="2" t="inlineStr"/>
       <c r="O122" s="2" t="inlineStr">
         <is>
@@ -8852,10 +8888,10 @@
         </is>
       </c>
       <c r="C123" s="2" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D123" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
@@ -8864,18 +8900,26 @@
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
-          <t>Làm mất, cháy, hỏng hóa đơn đã lập sai, đã xóa bỏ và đã lập hóa đơn thay thế</t>
+          <t>Không khai báo mất, cháy, hỏng hóa đơn</t>
         </is>
       </c>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>Cảnh cáo</t>
-        </is>
-      </c>
-      <c r="H123" s="3" t="n"/>
-      <c r="I123" s="3" t="n"/>
-      <c r="J123" s="3" t="n"/>
-      <c r="K123" s="3" t="n"/>
+          <t>Phạt tiền (khung)</t>
+        </is>
+      </c>
+      <c r="H123" s="3" t="n">
+        <v>4000000</v>
+      </c>
+      <c r="I123" s="3" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="J123" s="3" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="K123" s="3" t="n">
+        <v>4000000</v>
+      </c>
       <c r="L123" s="2" t="inlineStr"/>
       <c r="M123" s="2" t="inlineStr"/>
       <c r="N123" s="2" t="inlineStr"/>
@@ -8912,31 +8956,27 @@
         <v>26</v>
       </c>
       <c r="D124" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E124" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
-          <t>Làm mất, cháy, hỏng liên giao khách hàng của hóa đơn đã lập; người bán đã kê khai, có chứng từ</t>
+          <t>Làm mất, cháy, hỏng hóa đơn đã lập (trừ liên giao khách), đã kê khai thuế, có chứng từ chứng minh</t>
         </is>
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>Phạt tiền (khung)</t>
-        </is>
-      </c>
-      <c r="H124" s="3" t="n">
-        <v>3000000</v>
-      </c>
-      <c r="I124" s="3" t="n">
-        <v>5000000</v>
-      </c>
-      <c r="J124" s="3" t="n">
-        <v>1500000</v>
-      </c>
-      <c r="K124" s="3" t="n">
-        <v>2500000</v>
-      </c>
+          <t>Cảnh cáo</t>
+        </is>
+      </c>
+      <c r="H124" s="3" t="n"/>
+      <c r="I124" s="3" t="n"/>
+      <c r="J124" s="3" t="n"/>
+      <c r="K124" s="3" t="n"/>
       <c r="L124" s="2" t="inlineStr"/>
       <c r="M124" s="2" t="inlineStr">
         <is>
@@ -8977,35 +9017,27 @@
         <v>26</v>
       </c>
       <c r="D125" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>b</t>
         </is>
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
-          <t>Làm mất, cháy, hỏng hóa đơn đã phát hành / đã mua của cơ quan thuế nhưng chưa lập</t>
+          <t>Làm mất, cháy, hỏng hóa đơn đã lập sai, đã xóa bỏ và đã lập hóa đơn thay thế</t>
         </is>
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>Phạt tiền (khung)</t>
-        </is>
-      </c>
-      <c r="H125" s="3" t="n">
-        <v>4000000</v>
-      </c>
-      <c r="I125" s="3" t="n">
-        <v>8000000</v>
-      </c>
-      <c r="J125" s="3" t="n">
-        <v>2000000</v>
-      </c>
-      <c r="K125" s="3" t="n">
-        <v>4000000</v>
-      </c>
+          <t>Cảnh cáo</t>
+        </is>
+      </c>
+      <c r="H125" s="3" t="n"/>
+      <c r="I125" s="3" t="n"/>
+      <c r="J125" s="3" t="n"/>
+      <c r="K125" s="3" t="n"/>
       <c r="L125" s="2" t="inlineStr"/>
       <c r="M125" s="2" t="inlineStr"/>
       <c r="N125" s="2" t="inlineStr"/>
@@ -9022,14 +9054,10 @@
       </c>
       <c r="R125" s="2" t="inlineStr">
         <is>
-          <t>NĐ 125/2020+310/2025</t>
-        </is>
-      </c>
-      <c r="S125" s="2" t="inlineStr">
-        <is>
-          <t>NĐ310 sửa điểm a khoản 3 (chỉ sửa câu chữ 'hóa đơn mua của cơ quan thuế').</t>
-        </is>
-      </c>
+          <t>NĐ 125/2020</t>
+        </is>
+      </c>
+      <c r="S125" s="2" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
@@ -9046,13 +9074,9 @@
         <v>26</v>
       </c>
       <c r="D126" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="E126" s="2" t="inlineStr">
-        <is>
-          <t>b</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="E126" s="2" t="inlineStr"/>
       <c r="F126" s="2" t="inlineStr">
         <is>
           <t>Làm mất, cháy, hỏng liên giao khách hàng của hóa đơn đã lập; người bán đã kê khai, có chứng từ</t>
@@ -9064,19 +9088,23 @@
         </is>
       </c>
       <c r="H126" s="3" t="n">
-        <v>4000000</v>
+        <v>3000000</v>
       </c>
       <c r="I126" s="3" t="n">
-        <v>8000000</v>
+        <v>5000000</v>
       </c>
       <c r="J126" s="3" t="n">
-        <v>2000000</v>
+        <v>1500000</v>
       </c>
       <c r="K126" s="3" t="n">
-        <v>4000000</v>
+        <v>2500000</v>
       </c>
       <c r="L126" s="2" t="inlineStr"/>
-      <c r="M126" s="2" t="inlineStr"/>
+      <c r="M126" s="2" t="inlineStr">
+        <is>
+          <t>Có tình tiết giảm nhẹ</t>
+        </is>
+      </c>
       <c r="N126" s="2" t="inlineStr"/>
       <c r="O126" s="2" t="inlineStr">
         <is>
@@ -9097,65 +9125,73 @@
       <c r="S126" s="2" t="inlineStr"/>
     </row>
     <row r="127">
-      <c r="A127" s="2" t="inlineStr">
+      <c r="A127" s="4" t="inlineStr">
         <is>
           <t>P126</t>
         </is>
       </c>
-      <c r="B127" s="2" t="inlineStr">
+      <c r="B127" s="4" t="inlineStr">
         <is>
           <t>Hóa đơn</t>
         </is>
       </c>
-      <c r="C127" s="2" t="n">
+      <c r="C127" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="D127" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="E127" s="2" t="inlineStr"/>
-      <c r="F127" s="2" t="inlineStr">
-        <is>
-          <t>Làm mất, cháy, hỏng hóa đơn đã lập, đã khai, nộp thuế (trừ các trường hợp khoản 1, 2, 3)</t>
-        </is>
-      </c>
-      <c r="G127" s="2" t="inlineStr">
-        <is>
-          <t>Phạt tiền (khung)</t>
-        </is>
-      </c>
-      <c r="H127" s="3" t="n">
-        <v>5000000</v>
-      </c>
-      <c r="I127" s="3" t="n">
-        <v>10000000</v>
-      </c>
-      <c r="J127" s="3" t="n">
-        <v>2500000</v>
-      </c>
-      <c r="K127" s="3" t="n">
-        <v>5000000</v>
-      </c>
-      <c r="L127" s="2" t="inlineStr"/>
-      <c r="M127" s="2" t="inlineStr"/>
-      <c r="N127" s="2" t="inlineStr"/>
-      <c r="O127" s="2" t="inlineStr">
-        <is>
-          <t>2020-12-05</t>
-        </is>
-      </c>
-      <c r="P127" s="2" t="inlineStr"/>
-      <c r="Q127" s="2" t="inlineStr">
-        <is>
-          <t>Còn hiệu lực</t>
-        </is>
-      </c>
-      <c r="R127" s="2" t="inlineStr">
-        <is>
-          <t>NĐ 125/2020</t>
-        </is>
-      </c>
-      <c r="S127" s="2" t="inlineStr"/>
+      <c r="D127" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E127" s="4" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="F127" s="4" t="inlineStr">
+        <is>
+          <t>Làm mất, cháy, hỏng hóa đơn đã phát hành, đã mua của cơ quan thuế nhưng chưa lập</t>
+        </is>
+      </c>
+      <c r="G127" s="4" t="inlineStr">
+        <is>
+          <t>Phạt tiền (khung)</t>
+        </is>
+      </c>
+      <c r="H127" s="5" t="n">
+        <v>4000000</v>
+      </c>
+      <c r="I127" s="5" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="J127" s="5" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="K127" s="5" t="n">
+        <v>4000000</v>
+      </c>
+      <c r="L127" s="4" t="inlineStr"/>
+      <c r="M127" s="4" t="inlineStr"/>
+      <c r="N127" s="4" t="inlineStr"/>
+      <c r="O127" s="4" t="inlineStr">
+        <is>
+          <t>2020-12-05</t>
+        </is>
+      </c>
+      <c r="P127" s="4" t="inlineStr">
+        <is>
+          <t>2026-01-15</t>
+        </is>
+      </c>
+      <c r="Q127" s="4" t="inlineStr">
+        <is>
+          <t>Đã được thay bằng quy định mới từ 16/01/2026 (chỉ áp dụng hành vi đã kết thúc trước ngày này)</t>
+        </is>
+      </c>
+      <c r="R127" s="4" t="inlineStr">
+        <is>
+          <t>NĐ 125/2020</t>
+        </is>
+      </c>
+      <c r="S127" s="4" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
@@ -9169,36 +9205,44 @@
         </is>
       </c>
       <c r="C128" s="2" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D128" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E128" s="2" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="E128" s="2" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
-          <t>Hủy/tiêu hủy hóa đơn quá hạn 01-05 ngày làm việc</t>
+          <t>Làm mất, cháy, hỏng hóa đơn mua của cơ quan thuế nhưng chưa lập</t>
         </is>
       </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>Cảnh cáo</t>
-        </is>
-      </c>
-      <c r="H128" s="3" t="n"/>
-      <c r="I128" s="3" t="n"/>
-      <c r="J128" s="3" t="n"/>
-      <c r="K128" s="3" t="n"/>
+          <t>Phạt tiền (khung)</t>
+        </is>
+      </c>
+      <c r="H128" s="3" t="n">
+        <v>4000000</v>
+      </c>
+      <c r="I128" s="3" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="J128" s="3" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="K128" s="3" t="n">
+        <v>4000000</v>
+      </c>
       <c r="L128" s="2" t="inlineStr"/>
-      <c r="M128" s="2" t="inlineStr">
-        <is>
-          <t>Có tình tiết giảm nhẹ</t>
-        </is>
-      </c>
+      <c r="M128" s="2" t="inlineStr"/>
       <c r="N128" s="2" t="inlineStr"/>
       <c r="O128" s="2" t="inlineStr">
         <is>
-          <t>2020-12-05</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="P128" s="2" t="inlineStr"/>
@@ -9209,217 +9253,201 @@
       </c>
       <c r="R128" s="2" t="inlineStr">
         <is>
-          <t>NĐ 125/2020+310/2025</t>
-        </is>
-      </c>
-      <c r="S128" s="2" t="inlineStr"/>
+          <t>NĐ 310/2025</t>
+        </is>
+      </c>
+      <c r="S128" s="2" t="inlineStr">
+        <is>
+          <t>NĐ310 bỏ cụm 'đã phát hành' - phạm vi hẹp hơn bản cũ.</t>
+        </is>
+      </c>
     </row>
     <row r="129">
-      <c r="A129" s="4" t="inlineStr">
+      <c r="A129" s="2" t="inlineStr">
         <is>
           <t>P128</t>
         </is>
       </c>
-      <c r="B129" s="4" t="inlineStr">
+      <c r="B129" s="2" t="inlineStr">
         <is>
           <t>Hóa đơn</t>
         </is>
       </c>
-      <c r="C129" s="4" t="n">
+      <c r="C129" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="D129" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E129" s="2" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t>Làm mất, cháy, hỏng liên giao khách hàng của hóa đơn đã lập; người bán đã kê khai, có chứng từ</t>
+        </is>
+      </c>
+      <c r="G129" s="2" t="inlineStr">
+        <is>
+          <t>Phạt tiền (khung)</t>
+        </is>
+      </c>
+      <c r="H129" s="3" t="n">
+        <v>4000000</v>
+      </c>
+      <c r="I129" s="3" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="J129" s="3" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="K129" s="3" t="n">
+        <v>4000000</v>
+      </c>
+      <c r="L129" s="2" t="inlineStr"/>
+      <c r="M129" s="2" t="inlineStr"/>
+      <c r="N129" s="2" t="inlineStr"/>
+      <c r="O129" s="2" t="inlineStr">
+        <is>
+          <t>2020-12-05</t>
+        </is>
+      </c>
+      <c r="P129" s="2" t="inlineStr"/>
+      <c r="Q129" s="2" t="inlineStr">
+        <is>
+          <t>Còn hiệu lực</t>
+        </is>
+      </c>
+      <c r="R129" s="2" t="inlineStr">
+        <is>
+          <t>NĐ 125/2020</t>
+        </is>
+      </c>
+      <c r="S129" s="2" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>P129</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>Hóa đơn</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="D130" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E130" s="2" t="inlineStr"/>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t>Làm mất, cháy, hỏng hóa đơn đã lập, đã khai, nộp thuế (trừ các trường hợp khoản 1, 2, 3)</t>
+        </is>
+      </c>
+      <c r="G130" s="2" t="inlineStr">
+        <is>
+          <t>Phạt tiền (khung)</t>
+        </is>
+      </c>
+      <c r="H130" s="3" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="I130" s="3" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="J130" s="3" t="n">
+        <v>2500000</v>
+      </c>
+      <c r="K130" s="3" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="L130" s="2" t="inlineStr"/>
+      <c r="M130" s="2" t="inlineStr"/>
+      <c r="N130" s="2" t="inlineStr"/>
+      <c r="O130" s="2" t="inlineStr">
+        <is>
+          <t>2020-12-05</t>
+        </is>
+      </c>
+      <c r="P130" s="2" t="inlineStr"/>
+      <c r="Q130" s="2" t="inlineStr">
+        <is>
+          <t>Còn hiệu lực</t>
+        </is>
+      </c>
+      <c r="R130" s="2" t="inlineStr">
+        <is>
+          <t>NĐ 125/2020</t>
+        </is>
+      </c>
+      <c r="S130" s="2" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="4" t="inlineStr">
+        <is>
+          <t>P130</t>
+        </is>
+      </c>
+      <c r="B131" s="4" t="inlineStr">
+        <is>
+          <t>Hóa đơn</t>
+        </is>
+      </c>
+      <c r="C131" s="4" t="n">
         <v>27</v>
       </c>
-      <c r="D129" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="E129" s="4" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="F129" s="4" t="inlineStr">
-        <is>
-          <t>Hủy không đúng quy định hóa đơn đã phát hành nhưng chưa lập, hóa đơn không còn giá trị sử dụng</t>
-        </is>
-      </c>
-      <c r="G129" s="4" t="inlineStr">
-        <is>
-          <t>Phạt tiền (khung)</t>
-        </is>
-      </c>
-      <c r="H129" s="5" t="n">
-        <v>2000000</v>
-      </c>
-      <c r="I129" s="5" t="n">
-        <v>4000000</v>
-      </c>
-      <c r="J129" s="5" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="K129" s="5" t="n">
-        <v>2000000</v>
-      </c>
-      <c r="L129" s="4" t="inlineStr"/>
-      <c r="M129" s="4" t="inlineStr"/>
-      <c r="N129" s="4" t="inlineStr"/>
-      <c r="O129" s="4" t="inlineStr">
-        <is>
-          <t>2020-12-05</t>
-        </is>
-      </c>
-      <c r="P129" s="4" t="inlineStr">
+      <c r="D131" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E131" s="4" t="inlineStr"/>
+      <c r="F131" s="4" t="inlineStr">
+        <is>
+          <t>Hủy/tiêu hủy hóa đơn quá hạn 01-05 ngày làm việc</t>
+        </is>
+      </c>
+      <c r="G131" s="4" t="inlineStr">
+        <is>
+          <t>Cảnh cáo</t>
+        </is>
+      </c>
+      <c r="H131" s="5" t="n"/>
+      <c r="I131" s="5" t="n"/>
+      <c r="J131" s="5" t="n"/>
+      <c r="K131" s="5" t="n"/>
+      <c r="L131" s="4" t="inlineStr"/>
+      <c r="M131" s="4" t="inlineStr">
+        <is>
+          <t>Có tình tiết giảm nhẹ</t>
+        </is>
+      </c>
+      <c r="N131" s="4" t="inlineStr"/>
+      <c r="O131" s="4" t="inlineStr">
+        <is>
+          <t>2020-12-05</t>
+        </is>
+      </c>
+      <c r="P131" s="4" t="inlineStr">
         <is>
           <t>2026-01-15</t>
         </is>
       </c>
-      <c r="Q129" s="4" t="inlineStr">
+      <c r="Q131" s="4" t="inlineStr">
         <is>
           <t>Đã được thay bằng quy định mới từ 16/01/2026 (chỉ áp dụng hành vi đã kết thúc trước ngày này)</t>
         </is>
       </c>
-      <c r="R129" s="4" t="inlineStr">
-        <is>
-          <t>NĐ 125/2020</t>
-        </is>
-      </c>
-      <c r="S129" s="4" t="inlineStr"/>
-    </row>
-    <row r="130">
-      <c r="A130" s="4" t="inlineStr">
-        <is>
-          <t>P129</t>
-        </is>
-      </c>
-      <c r="B130" s="4" t="inlineStr">
-        <is>
-          <t>Hóa đơn</t>
-        </is>
-      </c>
-      <c r="C130" s="4" t="n">
-        <v>27</v>
-      </c>
-      <c r="D130" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="E130" s="4" t="inlineStr">
-        <is>
-          <t>b</t>
-        </is>
-      </c>
-      <c r="F130" s="4" t="inlineStr">
-        <is>
-          <t>Không hủy hóa đơn đã phát hành nhưng chưa lập, không còn giá trị sử dụng; không hủy hóa đơn mua của cơ quan thuế đã hết hạn sử dụng</t>
-        </is>
-      </c>
-      <c r="G130" s="4" t="inlineStr">
-        <is>
-          <t>Phạt tiền (khung)</t>
-        </is>
-      </c>
-      <c r="H130" s="5" t="n">
-        <v>2000000</v>
-      </c>
-      <c r="I130" s="5" t="n">
-        <v>4000000</v>
-      </c>
-      <c r="J130" s="5" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="K130" s="5" t="n">
-        <v>2000000</v>
-      </c>
-      <c r="L130" s="4" t="inlineStr"/>
-      <c r="M130" s="4" t="inlineStr"/>
-      <c r="N130" s="4" t="inlineStr">
-        <is>
-          <t>Buộc hủy hóa đơn</t>
-        </is>
-      </c>
-      <c r="O130" s="4" t="inlineStr">
-        <is>
-          <t>2020-12-05</t>
-        </is>
-      </c>
-      <c r="P130" s="4" t="inlineStr">
-        <is>
-          <t>2026-01-15</t>
-        </is>
-      </c>
-      <c r="Q130" s="4" t="inlineStr">
-        <is>
-          <t>Đã được thay bằng quy định mới từ 16/01/2026 (chỉ áp dụng hành vi đã kết thúc trước ngày này)</t>
-        </is>
-      </c>
-      <c r="R130" s="4" t="inlineStr">
-        <is>
-          <t>NĐ 125/2020</t>
-        </is>
-      </c>
-      <c r="S130" s="4" t="inlineStr"/>
-    </row>
-    <row r="131">
-      <c r="A131" s="2" t="inlineStr">
-        <is>
-          <t>P130</t>
-        </is>
-      </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>Hóa đơn</t>
-        </is>
-      </c>
-      <c r="C131" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="D131" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E131" s="2" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="F131" s="2" t="inlineStr">
-        <is>
-          <t>Tiêu hủy không đúng quy định hóa đơn đặt in mua của cơ quan thuế không tiếp tục sử dụng, không còn giá trị</t>
-        </is>
-      </c>
-      <c r="G131" s="2" t="inlineStr">
-        <is>
-          <t>Phạt tiền (khung)</t>
-        </is>
-      </c>
-      <c r="H131" s="3" t="n">
-        <v>2000000</v>
-      </c>
-      <c r="I131" s="3" t="n">
-        <v>4000000</v>
-      </c>
-      <c r="J131" s="3" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="K131" s="3" t="n">
-        <v>2000000</v>
-      </c>
-      <c r="L131" s="2" t="inlineStr"/>
-      <c r="M131" s="2" t="inlineStr"/>
-      <c r="N131" s="2" t="inlineStr"/>
-      <c r="O131" s="2" t="inlineStr">
-        <is>
-          <t>2026-01-16</t>
-        </is>
-      </c>
-      <c r="P131" s="2" t="inlineStr"/>
-      <c r="Q131" s="2" t="inlineStr">
-        <is>
-          <t>Còn hiệu lực</t>
-        </is>
-      </c>
-      <c r="R131" s="2" t="inlineStr">
-        <is>
-          <t>NĐ 310/2025</t>
-        </is>
-      </c>
-      <c r="S131" s="2" t="inlineStr"/>
+      <c r="R131" s="4" t="inlineStr">
+        <is>
+          <t>NĐ 125/2020</t>
+        </is>
+      </c>
+      <c r="S131" s="4" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
@@ -9436,42 +9464,30 @@
         <v>27</v>
       </c>
       <c r="D132" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E132" s="2" t="inlineStr">
-        <is>
-          <t>b</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="E132" s="2" t="inlineStr"/>
       <c r="F132" s="2" t="inlineStr">
         <is>
-          <t>Không tiêu hủy hóa đơn đặt in mua của cơ quan thuế không tiếp tục sử dụng, không còn giá trị</t>
+          <t>Tiêu hủy hóa đơn quá hạn 01-05 ngày làm việc</t>
         </is>
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>Phạt tiền (khung)</t>
-        </is>
-      </c>
-      <c r="H132" s="3" t="n">
-        <v>2000000</v>
-      </c>
-      <c r="I132" s="3" t="n">
-        <v>4000000</v>
-      </c>
-      <c r="J132" s="3" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="K132" s="3" t="n">
-        <v>2000000</v>
-      </c>
+          <t>Cảnh cáo</t>
+        </is>
+      </c>
+      <c r="H132" s="3" t="n"/>
+      <c r="I132" s="3" t="n"/>
+      <c r="J132" s="3" t="n"/>
+      <c r="K132" s="3" t="n"/>
       <c r="L132" s="2" t="inlineStr"/>
-      <c r="M132" s="2" t="inlineStr"/>
-      <c r="N132" s="2" t="inlineStr">
-        <is>
-          <t>Buộc tiêu hủy hóa đơn</t>
-        </is>
-      </c>
+      <c r="M132" s="2" t="inlineStr">
+        <is>
+          <t>Có tình tiết giảm nhẹ</t>
+        </is>
+      </c>
+      <c r="N132" s="2" t="inlineStr"/>
       <c r="O132" s="2" t="inlineStr">
         <is>
           <t>2026-01-16</t>
@@ -9491,73 +9507,73 @@
       <c r="S132" s="2" t="inlineStr"/>
     </row>
     <row r="133">
-      <c r="A133" s="2" t="inlineStr">
+      <c r="A133" s="4" t="inlineStr">
         <is>
           <t>P132</t>
         </is>
       </c>
-      <c r="B133" s="2" t="inlineStr">
+      <c r="B133" s="4" t="inlineStr">
         <is>
           <t>Hóa đơn</t>
         </is>
       </c>
-      <c r="C133" s="2" t="n">
+      <c r="C133" s="4" t="n">
         <v>27</v>
       </c>
-      <c r="D133" s="2" t="n">
+      <c r="D133" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="E133" s="2" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
-      <c r="F133" s="2" t="inlineStr">
-        <is>
-          <t>Hủy/tiêu hủy hóa đơn quá hạn 01-10 ngày làm việc</t>
-        </is>
-      </c>
-      <c r="G133" s="2" t="inlineStr">
-        <is>
-          <t>Phạt tiền (khung)</t>
-        </is>
-      </c>
-      <c r="H133" s="3" t="n">
+      <c r="E133" s="4" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="F133" s="4" t="inlineStr">
+        <is>
+          <t>Hủy không đúng quy định hóa đơn đã phát hành nhưng chưa lập, hóa đơn không còn giá trị sử dụng</t>
+        </is>
+      </c>
+      <c r="G133" s="4" t="inlineStr">
+        <is>
+          <t>Phạt tiền (khung)</t>
+        </is>
+      </c>
+      <c r="H133" s="5" t="n">
         <v>2000000</v>
       </c>
-      <c r="I133" s="3" t="n">
+      <c r="I133" s="5" t="n">
         <v>4000000</v>
       </c>
-      <c r="J133" s="3" t="n">
+      <c r="J133" s="5" t="n">
         <v>1000000</v>
       </c>
-      <c r="K133" s="3" t="n">
+      <c r="K133" s="5" t="n">
         <v>2000000</v>
       </c>
-      <c r="L133" s="2" t="inlineStr"/>
-      <c r="M133" s="2" t="inlineStr">
-        <is>
-          <t>Trừ trường hợp cảnh cáo khoản 1</t>
-        </is>
-      </c>
-      <c r="N133" s="2" t="inlineStr"/>
-      <c r="O133" s="2" t="inlineStr">
-        <is>
-          <t>2020-12-05</t>
-        </is>
-      </c>
-      <c r="P133" s="2" t="inlineStr"/>
-      <c r="Q133" s="2" t="inlineStr">
-        <is>
-          <t>Còn hiệu lực</t>
-        </is>
-      </c>
-      <c r="R133" s="2" t="inlineStr">
-        <is>
-          <t>NĐ 125/2020</t>
-        </is>
-      </c>
-      <c r="S133" s="2" t="inlineStr"/>
+      <c r="L133" s="4" t="inlineStr"/>
+      <c r="M133" s="4" t="inlineStr"/>
+      <c r="N133" s="4" t="inlineStr"/>
+      <c r="O133" s="4" t="inlineStr">
+        <is>
+          <t>2020-12-05</t>
+        </is>
+      </c>
+      <c r="P133" s="4" t="inlineStr">
+        <is>
+          <t>2026-01-15</t>
+        </is>
+      </c>
+      <c r="Q133" s="4" t="inlineStr">
+        <is>
+          <t>Đã được thay bằng quy định mới từ 16/01/2026 (chỉ áp dụng hành vi đã kết thúc trước ngày này)</t>
+        </is>
+      </c>
+      <c r="R133" s="4" t="inlineStr">
+        <is>
+          <t>NĐ 125/2020</t>
+        </is>
+      </c>
+      <c r="S133" s="4" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" s="4" t="inlineStr">
@@ -9574,16 +9590,16 @@
         <v>27</v>
       </c>
       <c r="D134" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E134" s="4" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>b</t>
         </is>
       </c>
       <c r="F134" s="4" t="inlineStr">
         <is>
-          <t>Hủy/tiêu hủy hóa đơn quá hạn từ 11 ngày làm việc</t>
+          <t>Không hủy hóa đơn đã phát hành nhưng chưa lập, không còn giá trị sử dụng; không hủy hóa đơn mua của cơ quan thuế đã hết hạn sử dụng</t>
         </is>
       </c>
       <c r="G134" s="4" t="inlineStr">
@@ -9592,20 +9608,24 @@
         </is>
       </c>
       <c r="H134" s="5" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="I134" s="5" t="n">
         <v>4000000</v>
       </c>
-      <c r="I134" s="5" t="n">
-        <v>8000000</v>
-      </c>
       <c r="J134" s="5" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="K134" s="5" t="n">
         <v>2000000</v>
-      </c>
-      <c r="K134" s="5" t="n">
-        <v>4000000</v>
       </c>
       <c r="L134" s="4" t="inlineStr"/>
       <c r="M134" s="4" t="inlineStr"/>
-      <c r="N134" s="4" t="inlineStr"/>
+      <c r="N134" s="4" t="inlineStr">
+        <is>
+          <t>Buộc hủy hóa đơn</t>
+        </is>
+      </c>
       <c r="O134" s="4" t="inlineStr">
         <is>
           <t>2020-12-05</t>
@@ -9629,146 +9649,138 @@
       <c r="S134" s="4" t="inlineStr"/>
     </row>
     <row r="135">
-      <c r="A135" s="4" t="inlineStr">
+      <c r="A135" s="2" t="inlineStr">
         <is>
           <t>P134</t>
         </is>
       </c>
-      <c r="B135" s="4" t="inlineStr">
+      <c r="B135" s="2" t="inlineStr">
         <is>
           <t>Hóa đơn</t>
         </is>
       </c>
-      <c r="C135" s="4" t="n">
+      <c r="C135" s="2" t="n">
         <v>27</v>
       </c>
-      <c r="D135" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="E135" s="4" t="inlineStr">
+      <c r="D135" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E135" s="2" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="F135" s="2" t="inlineStr">
+        <is>
+          <t>Tiêu hủy không đúng quy định hóa đơn đặt in mua của cơ quan thuế không tiếp tục sử dụng, không còn giá trị</t>
+        </is>
+      </c>
+      <c r="G135" s="2" t="inlineStr">
+        <is>
+          <t>Phạt tiền (khung)</t>
+        </is>
+      </c>
+      <c r="H135" s="3" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="I135" s="3" t="n">
+        <v>4000000</v>
+      </c>
+      <c r="J135" s="3" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="K135" s="3" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="L135" s="2" t="inlineStr"/>
+      <c r="M135" s="2" t="inlineStr"/>
+      <c r="N135" s="2" t="inlineStr"/>
+      <c r="O135" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="P135" s="2" t="inlineStr"/>
+      <c r="Q135" s="2" t="inlineStr">
+        <is>
+          <t>Còn hiệu lực</t>
+        </is>
+      </c>
+      <c r="R135" s="2" t="inlineStr">
+        <is>
+          <t>NĐ 310/2025</t>
+        </is>
+      </c>
+      <c r="S135" s="2" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>P135</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>Hóa đơn</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="D136" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E136" s="2" t="inlineStr">
         <is>
           <t>b</t>
         </is>
       </c>
-      <c r="F135" s="4" t="inlineStr">
-        <is>
-          <t>Không hủy, không tiêu hủy hóa đơn theo quy định</t>
-        </is>
-      </c>
-      <c r="G135" s="4" t="inlineStr">
-        <is>
-          <t>Phạt tiền (khung)</t>
-        </is>
-      </c>
-      <c r="H135" s="5" t="n">
+      <c r="F136" s="2" t="inlineStr">
+        <is>
+          <t>Không tiêu hủy hóa đơn đặt in mua của cơ quan thuế không tiếp tục sử dụng, không còn giá trị</t>
+        </is>
+      </c>
+      <c r="G136" s="2" t="inlineStr">
+        <is>
+          <t>Phạt tiền (khung)</t>
+        </is>
+      </c>
+      <c r="H136" s="3" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="I136" s="3" t="n">
         <v>4000000</v>
       </c>
-      <c r="I135" s="5" t="n">
-        <v>8000000</v>
-      </c>
-      <c r="J135" s="5" t="n">
+      <c r="J136" s="3" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="K136" s="3" t="n">
         <v>2000000</v>
       </c>
-      <c r="K135" s="5" t="n">
-        <v>4000000</v>
-      </c>
-      <c r="L135" s="4" t="inlineStr"/>
-      <c r="M135" s="4" t="inlineStr"/>
-      <c r="N135" s="4" t="inlineStr">
-        <is>
-          <t>Buộc hủy, tiêu hủy hóa đơn</t>
-        </is>
-      </c>
-      <c r="O135" s="4" t="inlineStr">
-        <is>
-          <t>2020-12-05</t>
-        </is>
-      </c>
-      <c r="P135" s="4" t="inlineStr">
-        <is>
-          <t>2026-01-15</t>
-        </is>
-      </c>
-      <c r="Q135" s="4" t="inlineStr">
-        <is>
-          <t>Đã được thay bằng quy định mới từ 16/01/2026 (chỉ áp dụng hành vi đã kết thúc trước ngày này)</t>
-        </is>
-      </c>
-      <c r="R135" s="4" t="inlineStr">
-        <is>
-          <t>NĐ 125/2020</t>
-        </is>
-      </c>
-      <c r="S135" s="4" t="inlineStr"/>
-    </row>
-    <row r="136">
-      <c r="A136" s="4" t="inlineStr">
-        <is>
-          <t>P135</t>
-        </is>
-      </c>
-      <c r="B136" s="4" t="inlineStr">
-        <is>
-          <t>Hóa đơn</t>
-        </is>
-      </c>
-      <c r="C136" s="4" t="n">
-        <v>27</v>
-      </c>
-      <c r="D136" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="E136" s="4" t="inlineStr">
-        <is>
-          <t>đ</t>
-        </is>
-      </c>
-      <c r="F136" s="4" t="inlineStr">
-        <is>
-          <t>Hủy/tiêu hủy hóa đơn không đúng trình tự, thủ tục</t>
-        </is>
-      </c>
-      <c r="G136" s="4" t="inlineStr">
-        <is>
-          <t>Phạt tiền (khung)</t>
-        </is>
-      </c>
-      <c r="H136" s="5" t="n">
-        <v>4000000</v>
-      </c>
-      <c r="I136" s="5" t="n">
-        <v>8000000</v>
-      </c>
-      <c r="J136" s="5" t="n">
-        <v>2000000</v>
-      </c>
-      <c r="K136" s="5" t="n">
-        <v>4000000</v>
-      </c>
-      <c r="L136" s="4" t="inlineStr"/>
-      <c r="M136" s="4" t="inlineStr"/>
-      <c r="N136" s="4" t="inlineStr"/>
-      <c r="O136" s="4" t="inlineStr">
-        <is>
-          <t>2020-12-05</t>
-        </is>
-      </c>
-      <c r="P136" s="4" t="inlineStr">
-        <is>
-          <t>2026-01-15</t>
-        </is>
-      </c>
-      <c r="Q136" s="4" t="inlineStr">
-        <is>
-          <t>Đã được thay bằng quy định mới từ 16/01/2026 (chỉ áp dụng hành vi đã kết thúc trước ngày này)</t>
-        </is>
-      </c>
-      <c r="R136" s="4" t="inlineStr">
-        <is>
-          <t>NĐ 125/2020</t>
-        </is>
-      </c>
-      <c r="S136" s="4" t="inlineStr"/>
+      <c r="L136" s="2" t="inlineStr"/>
+      <c r="M136" s="2" t="inlineStr"/>
+      <c r="N136" s="2" t="inlineStr">
+        <is>
+          <t>Buộc tiêu hủy hóa đơn</t>
+        </is>
+      </c>
+      <c r="O136" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="P136" s="2" t="inlineStr"/>
+      <c r="Q136" s="2" t="inlineStr">
+        <is>
+          <t>Còn hiệu lực</t>
+        </is>
+      </c>
+      <c r="R136" s="2" t="inlineStr">
+        <is>
+          <t>NĐ 310/2025</t>
+        </is>
+      </c>
+      <c r="S136" s="2" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" s="4" t="inlineStr">
@@ -9785,16 +9797,16 @@
         <v>27</v>
       </c>
       <c r="D137" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E137" s="4" t="inlineStr">
         <is>
-          <t>e</t>
+          <t>c</t>
         </is>
       </c>
       <c r="F137" s="4" t="inlineStr">
         <is>
-          <t>Tiêu hủy hóa đơn không đúng các trường hợp phải tiêu hủy</t>
+          <t>Hủy/tiêu hủy hóa đơn quá hạn 01-10 ngày làm việc</t>
         </is>
       </c>
       <c r="G137" s="4" t="inlineStr">
@@ -9803,19 +9815,23 @@
         </is>
       </c>
       <c r="H137" s="5" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="I137" s="5" t="n">
         <v>4000000</v>
       </c>
-      <c r="I137" s="5" t="n">
-        <v>8000000</v>
-      </c>
       <c r="J137" s="5" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="K137" s="5" t="n">
         <v>2000000</v>
       </c>
-      <c r="K137" s="5" t="n">
-        <v>4000000</v>
-      </c>
       <c r="L137" s="4" t="inlineStr"/>
-      <c r="M137" s="4" t="inlineStr"/>
+      <c r="M137" s="4" t="inlineStr">
+        <is>
+          <t>Trừ trường hợp cảnh cáo khoản 1</t>
+        </is>
+      </c>
       <c r="N137" s="4" t="inlineStr"/>
       <c r="O137" s="4" t="inlineStr">
         <is>
@@ -9840,77 +9856,73 @@
       <c r="S137" s="4" t="inlineStr"/>
     </row>
     <row r="138">
-      <c r="A138" s="4" t="inlineStr">
+      <c r="A138" s="2" t="inlineStr">
         <is>
           <t>P137</t>
         </is>
       </c>
-      <c r="B138" s="4" t="inlineStr">
+      <c r="B138" s="2" t="inlineStr">
         <is>
           <t>Hóa đơn</t>
         </is>
       </c>
-      <c r="C138" s="4" t="n">
+      <c r="C138" s="2" t="n">
         <v>27</v>
       </c>
-      <c r="D138" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="E138" s="4" t="inlineStr">
+      <c r="D138" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E138" s="2" t="inlineStr">
         <is>
           <t>c</t>
         </is>
       </c>
-      <c r="F138" s="4" t="inlineStr">
-        <is>
-          <t>Không hủy hóa đơn điện tử lập sai sót sau khi quá hạn cơ quan thuế thông báo kiểm tra sai, sót</t>
-        </is>
-      </c>
-      <c r="G138" s="4" t="inlineStr">
-        <is>
-          <t>Phạt tiền (khung)</t>
-        </is>
-      </c>
-      <c r="H138" s="5" t="n">
+      <c r="F138" s="2" t="inlineStr">
+        <is>
+          <t>Tiêu hủy hóa đơn quá hạn 01-10 ngày làm việc</t>
+        </is>
+      </c>
+      <c r="G138" s="2" t="inlineStr">
+        <is>
+          <t>Phạt tiền (khung)</t>
+        </is>
+      </c>
+      <c r="H138" s="3" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="I138" s="3" t="n">
         <v>4000000</v>
       </c>
-      <c r="I138" s="5" t="n">
-        <v>8000000</v>
-      </c>
-      <c r="J138" s="5" t="n">
+      <c r="J138" s="3" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="K138" s="3" t="n">
         <v>2000000</v>
       </c>
-      <c r="K138" s="5" t="n">
-        <v>4000000</v>
-      </c>
-      <c r="L138" s="4" t="inlineStr"/>
-      <c r="M138" s="4" t="inlineStr"/>
-      <c r="N138" s="4" t="inlineStr">
-        <is>
-          <t>Buộc hủy hóa đơn</t>
-        </is>
-      </c>
-      <c r="O138" s="4" t="inlineStr">
-        <is>
-          <t>2020-12-05</t>
-        </is>
-      </c>
-      <c r="P138" s="4" t="inlineStr">
-        <is>
-          <t>2026-01-15</t>
-        </is>
-      </c>
-      <c r="Q138" s="4" t="inlineStr">
-        <is>
-          <t>Đã bãi bỏ từ 16/01/2026 (chỉ áp dụng hành vi đã kết thúc trước ngày này)</t>
-        </is>
-      </c>
-      <c r="R138" s="4" t="inlineStr">
-        <is>
-          <t>NĐ 125/2020</t>
-        </is>
-      </c>
-      <c r="S138" s="4" t="inlineStr"/>
+      <c r="L138" s="2" t="inlineStr"/>
+      <c r="M138" s="2" t="inlineStr">
+        <is>
+          <t>Trừ trường hợp cảnh cáo khoản 1</t>
+        </is>
+      </c>
+      <c r="N138" s="2" t="inlineStr"/>
+      <c r="O138" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="P138" s="2" t="inlineStr"/>
+      <c r="Q138" s="2" t="inlineStr">
+        <is>
+          <t>Còn hiệu lực</t>
+        </is>
+      </c>
+      <c r="R138" s="2" t="inlineStr">
+        <is>
+          <t>NĐ 310/2025</t>
+        </is>
+      </c>
+      <c r="S138" s="2" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" s="4" t="inlineStr">
@@ -9931,12 +9943,12 @@
       </c>
       <c r="E139" s="4" t="inlineStr">
         <is>
-          <t>d</t>
+          <t>a</t>
         </is>
       </c>
       <c r="F139" s="4" t="inlineStr">
         <is>
-          <t>Không hủy hóa đơn đặt in chưa phát hành nhưng không còn sử dụng</t>
+          <t>Hủy/tiêu hủy hóa đơn quá hạn từ 11 ngày làm việc</t>
         </is>
       </c>
       <c r="G139" s="4" t="inlineStr">
@@ -9958,381 +9970,385 @@
       </c>
       <c r="L139" s="4" t="inlineStr"/>
       <c r="M139" s="4" t="inlineStr"/>
-      <c r="N139" s="4" t="inlineStr">
+      <c r="N139" s="4" t="inlineStr"/>
+      <c r="O139" s="4" t="inlineStr">
+        <is>
+          <t>2020-12-05</t>
+        </is>
+      </c>
+      <c r="P139" s="4" t="inlineStr">
+        <is>
+          <t>2026-01-15</t>
+        </is>
+      </c>
+      <c r="Q139" s="4" t="inlineStr">
+        <is>
+          <t>Đã được thay bằng quy định mới từ 16/01/2026 (chỉ áp dụng hành vi đã kết thúc trước ngày này)</t>
+        </is>
+      </c>
+      <c r="R139" s="4" t="inlineStr">
+        <is>
+          <t>NĐ 125/2020</t>
+        </is>
+      </c>
+      <c r="S139" s="4" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="4" t="inlineStr">
+        <is>
+          <t>P139</t>
+        </is>
+      </c>
+      <c r="B140" s="4" t="inlineStr">
+        <is>
+          <t>Hóa đơn</t>
+        </is>
+      </c>
+      <c r="C140" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="D140" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E140" s="4" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="F140" s="4" t="inlineStr">
+        <is>
+          <t>Không hủy, không tiêu hủy hóa đơn theo quy định</t>
+        </is>
+      </c>
+      <c r="G140" s="4" t="inlineStr">
+        <is>
+          <t>Phạt tiền (khung)</t>
+        </is>
+      </c>
+      <c r="H140" s="5" t="n">
+        <v>4000000</v>
+      </c>
+      <c r="I140" s="5" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="J140" s="5" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="K140" s="5" t="n">
+        <v>4000000</v>
+      </c>
+      <c r="L140" s="4" t="inlineStr"/>
+      <c r="M140" s="4" t="inlineStr"/>
+      <c r="N140" s="4" t="inlineStr">
+        <is>
+          <t>Buộc hủy, tiêu hủy hóa đơn</t>
+        </is>
+      </c>
+      <c r="O140" s="4" t="inlineStr">
+        <is>
+          <t>2020-12-05</t>
+        </is>
+      </c>
+      <c r="P140" s="4" t="inlineStr">
+        <is>
+          <t>2026-01-15</t>
+        </is>
+      </c>
+      <c r="Q140" s="4" t="inlineStr">
+        <is>
+          <t>Đã được thay bằng quy định mới từ 16/01/2026 (chỉ áp dụng hành vi đã kết thúc trước ngày này)</t>
+        </is>
+      </c>
+      <c r="R140" s="4" t="inlineStr">
+        <is>
+          <t>NĐ 125/2020</t>
+        </is>
+      </c>
+      <c r="S140" s="4" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="4" t="inlineStr">
+        <is>
+          <t>P140</t>
+        </is>
+      </c>
+      <c r="B141" s="4" t="inlineStr">
+        <is>
+          <t>Hóa đơn</t>
+        </is>
+      </c>
+      <c r="C141" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="D141" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E141" s="4" t="inlineStr">
+        <is>
+          <t>đ</t>
+        </is>
+      </c>
+      <c r="F141" s="4" t="inlineStr">
+        <is>
+          <t>Hủy/tiêu hủy hóa đơn không đúng trình tự, thủ tục</t>
+        </is>
+      </c>
+      <c r="G141" s="4" t="inlineStr">
+        <is>
+          <t>Phạt tiền (khung)</t>
+        </is>
+      </c>
+      <c r="H141" s="5" t="n">
+        <v>4000000</v>
+      </c>
+      <c r="I141" s="5" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="J141" s="5" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="K141" s="5" t="n">
+        <v>4000000</v>
+      </c>
+      <c r="L141" s="4" t="inlineStr"/>
+      <c r="M141" s="4" t="inlineStr"/>
+      <c r="N141" s="4" t="inlineStr"/>
+      <c r="O141" s="4" t="inlineStr">
+        <is>
+          <t>2020-12-05</t>
+        </is>
+      </c>
+      <c r="P141" s="4" t="inlineStr">
+        <is>
+          <t>2026-01-15</t>
+        </is>
+      </c>
+      <c r="Q141" s="4" t="inlineStr">
+        <is>
+          <t>Đã được thay bằng quy định mới từ 16/01/2026 (chỉ áp dụng hành vi đã kết thúc trước ngày này)</t>
+        </is>
+      </c>
+      <c r="R141" s="4" t="inlineStr">
+        <is>
+          <t>NĐ 125/2020</t>
+        </is>
+      </c>
+      <c r="S141" s="4" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="4" t="inlineStr">
+        <is>
+          <t>P141</t>
+        </is>
+      </c>
+      <c r="B142" s="4" t="inlineStr">
+        <is>
+          <t>Hóa đơn</t>
+        </is>
+      </c>
+      <c r="C142" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="D142" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E142" s="4" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="F142" s="4" t="inlineStr">
+        <is>
+          <t>Tiêu hủy hóa đơn không đúng các trường hợp phải tiêu hủy</t>
+        </is>
+      </c>
+      <c r="G142" s="4" t="inlineStr">
+        <is>
+          <t>Phạt tiền (khung)</t>
+        </is>
+      </c>
+      <c r="H142" s="5" t="n">
+        <v>4000000</v>
+      </c>
+      <c r="I142" s="5" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="J142" s="5" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="K142" s="5" t="n">
+        <v>4000000</v>
+      </c>
+      <c r="L142" s="4" t="inlineStr"/>
+      <c r="M142" s="4" t="inlineStr"/>
+      <c r="N142" s="4" t="inlineStr"/>
+      <c r="O142" s="4" t="inlineStr">
+        <is>
+          <t>2020-12-05</t>
+        </is>
+      </c>
+      <c r="P142" s="4" t="inlineStr">
+        <is>
+          <t>2026-01-15</t>
+        </is>
+      </c>
+      <c r="Q142" s="4" t="inlineStr">
+        <is>
+          <t>Đã được thay bằng quy định mới từ 16/01/2026 (chỉ áp dụng hành vi đã kết thúc trước ngày này)</t>
+        </is>
+      </c>
+      <c r="R142" s="4" t="inlineStr">
+        <is>
+          <t>NĐ 125/2020</t>
+        </is>
+      </c>
+      <c r="S142" s="4" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="4" t="inlineStr">
+        <is>
+          <t>P142</t>
+        </is>
+      </c>
+      <c r="B143" s="4" t="inlineStr">
+        <is>
+          <t>Hóa đơn</t>
+        </is>
+      </c>
+      <c r="C143" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="D143" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E143" s="4" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="F143" s="4" t="inlineStr">
+        <is>
+          <t>Không hủy hóa đơn điện tử lập sai sót sau khi quá hạn cơ quan thuế thông báo kiểm tra sai, sót</t>
+        </is>
+      </c>
+      <c r="G143" s="4" t="inlineStr">
+        <is>
+          <t>Phạt tiền (khung)</t>
+        </is>
+      </c>
+      <c r="H143" s="5" t="n">
+        <v>4000000</v>
+      </c>
+      <c r="I143" s="5" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="J143" s="5" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="K143" s="5" t="n">
+        <v>4000000</v>
+      </c>
+      <c r="L143" s="4" t="inlineStr"/>
+      <c r="M143" s="4" t="inlineStr"/>
+      <c r="N143" s="4" t="inlineStr">
         <is>
           <t>Buộc hủy hóa đơn</t>
         </is>
       </c>
-      <c r="O139" s="4" t="inlineStr">
-        <is>
-          <t>2020-12-05</t>
-        </is>
-      </c>
-      <c r="P139" s="4" t="inlineStr">
+      <c r="O143" s="4" t="inlineStr">
+        <is>
+          <t>2020-12-05</t>
+        </is>
+      </c>
+      <c r="P143" s="4" t="inlineStr">
         <is>
           <t>2026-01-15</t>
         </is>
       </c>
-      <c r="Q139" s="4" t="inlineStr">
+      <c r="Q143" s="4" t="inlineStr">
         <is>
           <t>Đã bãi bỏ từ 16/01/2026 (chỉ áp dụng hành vi đã kết thúc trước ngày này)</t>
         </is>
       </c>
-      <c r="R139" s="4" t="inlineStr">
-        <is>
-          <t>NĐ 125/2020</t>
-        </is>
-      </c>
-      <c r="S139" s="4" t="inlineStr"/>
-    </row>
-    <row r="140">
-      <c r="A140" s="2" t="inlineStr">
-        <is>
-          <t>P139</t>
-        </is>
-      </c>
-      <c r="B140" s="2" t="inlineStr">
+      <c r="R143" s="4" t="inlineStr">
+        <is>
+          <t>NĐ 125/2020</t>
+        </is>
+      </c>
+      <c r="S143" s="4" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="4" t="inlineStr">
+        <is>
+          <t>P143</t>
+        </is>
+      </c>
+      <c r="B144" s="4" t="inlineStr">
         <is>
           <t>Hóa đơn</t>
         </is>
       </c>
-      <c r="C140" s="2" t="n">
+      <c r="C144" s="4" t="n">
         <v>27</v>
       </c>
-      <c r="D140" s="2" t="n">
+      <c r="D144" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="E140" s="2" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="F140" s="2" t="inlineStr">
-        <is>
-          <t>Tiêu hủy hóa đơn quá hạn từ 11 ngày làm việc</t>
-        </is>
-      </c>
-      <c r="G140" s="2" t="inlineStr">
-        <is>
-          <t>Phạt tiền (khung)</t>
-        </is>
-      </c>
-      <c r="H140" s="3" t="n">
+      <c r="E144" s="4" t="inlineStr">
+        <is>
+          <t>d</t>
+        </is>
+      </c>
+      <c r="F144" s="4" t="inlineStr">
+        <is>
+          <t>Không hủy hóa đơn đặt in chưa phát hành nhưng không còn sử dụng</t>
+        </is>
+      </c>
+      <c r="G144" s="4" t="inlineStr">
+        <is>
+          <t>Phạt tiền (khung)</t>
+        </is>
+      </c>
+      <c r="H144" s="5" t="n">
         <v>4000000</v>
       </c>
-      <c r="I140" s="3" t="n">
+      <c r="I144" s="5" t="n">
         <v>8000000</v>
       </c>
-      <c r="J140" s="3" t="n">
+      <c r="J144" s="5" t="n">
         <v>2000000</v>
       </c>
-      <c r="K140" s="3" t="n">
+      <c r="K144" s="5" t="n">
         <v>4000000</v>
       </c>
-      <c r="L140" s="2" t="inlineStr"/>
-      <c r="M140" s="2" t="inlineStr"/>
-      <c r="N140" s="2" t="inlineStr"/>
-      <c r="O140" s="2" t="inlineStr">
-        <is>
-          <t>2026-01-16</t>
-        </is>
-      </c>
-      <c r="P140" s="2" t="inlineStr"/>
-      <c r="Q140" s="2" t="inlineStr">
-        <is>
-          <t>Còn hiệu lực</t>
-        </is>
-      </c>
-      <c r="R140" s="2" t="inlineStr">
-        <is>
-          <t>NĐ 310/2025</t>
-        </is>
-      </c>
-      <c r="S140" s="2" t="inlineStr">
-        <is>
-          <t>Ký hiệu điểm theo bản OCR NĐ310 (đánh số lại a-d, đ); cần đối chiếu với bản gốc.</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" s="2" t="inlineStr">
-        <is>
-          <t>P140</t>
-        </is>
-      </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>Hóa đơn</t>
-        </is>
-      </c>
-      <c r="C141" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="D141" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="E141" s="2" t="inlineStr">
-        <is>
-          <t>b</t>
-        </is>
-      </c>
-      <c r="F141" s="2" t="inlineStr">
-        <is>
-          <t>Không tiêu hủy hóa đơn theo quy định</t>
-        </is>
-      </c>
-      <c r="G141" s="2" t="inlineStr">
-        <is>
-          <t>Phạt tiền (khung)</t>
-        </is>
-      </c>
-      <c r="H141" s="3" t="n">
-        <v>4000000</v>
-      </c>
-      <c r="I141" s="3" t="n">
-        <v>8000000</v>
-      </c>
-      <c r="J141" s="3" t="n">
-        <v>2000000</v>
-      </c>
-      <c r="K141" s="3" t="n">
-        <v>4000000</v>
-      </c>
-      <c r="L141" s="2" t="inlineStr"/>
-      <c r="M141" s="2" t="inlineStr"/>
-      <c r="N141" s="2" t="inlineStr">
-        <is>
-          <t>Buộc tiêu hủy hóa đơn</t>
-        </is>
-      </c>
-      <c r="O141" s="2" t="inlineStr">
-        <is>
-          <t>2026-01-16</t>
-        </is>
-      </c>
-      <c r="P141" s="2" t="inlineStr"/>
-      <c r="Q141" s="2" t="inlineStr">
-        <is>
-          <t>Còn hiệu lực</t>
-        </is>
-      </c>
-      <c r="R141" s="2" t="inlineStr">
-        <is>
-          <t>NĐ 310/2025</t>
-        </is>
-      </c>
-      <c r="S141" s="2" t="inlineStr">
-        <is>
-          <t>Ký hiệu điểm theo bản OCR NĐ310 (đánh số lại a-d, đ); cần đối chiếu với bản gốc.</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" s="2" t="inlineStr">
-        <is>
-          <t>P141</t>
-        </is>
-      </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>Hóa đơn</t>
-        </is>
-      </c>
-      <c r="C142" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="D142" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="E142" s="2" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
-      <c r="F142" s="2" t="inlineStr">
-        <is>
-          <t>Tiêu hủy hóa đơn không đúng trình tự, thủ tục</t>
-        </is>
-      </c>
-      <c r="G142" s="2" t="inlineStr">
-        <is>
-          <t>Phạt tiền (khung)</t>
-        </is>
-      </c>
-      <c r="H142" s="3" t="n">
-        <v>4000000</v>
-      </c>
-      <c r="I142" s="3" t="n">
-        <v>8000000</v>
-      </c>
-      <c r="J142" s="3" t="n">
-        <v>2000000</v>
-      </c>
-      <c r="K142" s="3" t="n">
-        <v>4000000</v>
-      </c>
-      <c r="L142" s="2" t="inlineStr"/>
-      <c r="M142" s="2" t="inlineStr"/>
-      <c r="N142" s="2" t="inlineStr"/>
-      <c r="O142" s="2" t="inlineStr">
-        <is>
-          <t>2026-01-16</t>
-        </is>
-      </c>
-      <c r="P142" s="2" t="inlineStr"/>
-      <c r="Q142" s="2" t="inlineStr">
-        <is>
-          <t>Còn hiệu lực</t>
-        </is>
-      </c>
-      <c r="R142" s="2" t="inlineStr">
-        <is>
-          <t>NĐ 310/2025</t>
-        </is>
-      </c>
-      <c r="S142" s="2" t="inlineStr">
-        <is>
-          <t>Ký hiệu điểm theo bản OCR NĐ310 (đánh số lại a-d, đ); cần đối chiếu với bản gốc.</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" s="2" t="inlineStr">
-        <is>
-          <t>P142</t>
-        </is>
-      </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>Hóa đơn</t>
-        </is>
-      </c>
-      <c r="C143" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="D143" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="E143" s="2" t="inlineStr">
-        <is>
-          <t>đ</t>
-        </is>
-      </c>
-      <c r="F143" s="2" t="inlineStr">
-        <is>
-          <t>Tiêu hủy hóa đơn không đúng các trường hợp phải tiêu hủy</t>
-        </is>
-      </c>
-      <c r="G143" s="2" t="inlineStr">
-        <is>
-          <t>Phạt tiền (khung)</t>
-        </is>
-      </c>
-      <c r="H143" s="3" t="n">
-        <v>4000000</v>
-      </c>
-      <c r="I143" s="3" t="n">
-        <v>8000000</v>
-      </c>
-      <c r="J143" s="3" t="n">
-        <v>2000000</v>
-      </c>
-      <c r="K143" s="3" t="n">
-        <v>4000000</v>
-      </c>
-      <c r="L143" s="2" t="inlineStr"/>
-      <c r="M143" s="2" t="inlineStr"/>
-      <c r="N143" s="2" t="inlineStr"/>
-      <c r="O143" s="2" t="inlineStr">
-        <is>
-          <t>2026-01-16</t>
-        </is>
-      </c>
-      <c r="P143" s="2" t="inlineStr"/>
-      <c r="Q143" s="2" t="inlineStr">
-        <is>
-          <t>Còn hiệu lực</t>
-        </is>
-      </c>
-      <c r="R143" s="2" t="inlineStr">
-        <is>
-          <t>NĐ 310/2025</t>
-        </is>
-      </c>
-      <c r="S143" s="2" t="inlineStr">
-        <is>
-          <t>Ký hiệu điểm theo bản OCR NĐ310 (đánh số lại a-d, đ); cần đối chiếu với bản gốc.</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" s="2" t="inlineStr">
-        <is>
-          <t>P143</t>
-        </is>
-      </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t>Hóa đơn</t>
-        </is>
-      </c>
-      <c r="C144" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="D144" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E144" s="2" t="inlineStr"/>
-      <c r="F144" s="2" t="inlineStr">
-        <is>
-          <t>Sử dụng hóa đơn không hợp pháp / sử dụng không hợp pháp hóa đơn (Điều 4 NĐ125)</t>
-        </is>
-      </c>
-      <c r="G144" s="2" t="inlineStr">
-        <is>
-          <t>Phạt tiền (khung)</t>
-        </is>
-      </c>
-      <c r="H144" s="3" t="n">
-        <v>20000000</v>
-      </c>
-      <c r="I144" s="3" t="n">
-        <v>50000000</v>
-      </c>
-      <c r="J144" s="3" t="n">
-        <v>10000000</v>
-      </c>
-      <c r="K144" s="3" t="n">
-        <v>25000000</v>
-      </c>
-      <c r="L144" s="2" t="inlineStr"/>
-      <c r="M144" s="2" t="inlineStr">
-        <is>
-          <t>Trừ điểm đ khoản 1 Điều 16 và điểm d khoản 1 Điều 17 (khi thuộc diện phạt 20% hoặc trốn thuế)</t>
-        </is>
-      </c>
-      <c r="N144" s="2" t="inlineStr">
-        <is>
-          <t>Buộc hủy hóa đơn đã sử dụng (khoản 2 Điều 28 bị bãi bỏ từ 16/01/2026)</t>
-        </is>
-      </c>
-      <c r="O144" s="2" t="inlineStr">
-        <is>
-          <t>2020-12-05</t>
-        </is>
-      </c>
-      <c r="P144" s="2" t="inlineStr"/>
-      <c r="Q144" s="2" t="inlineStr">
-        <is>
-          <t>Còn hiệu lực</t>
-        </is>
-      </c>
-      <c r="R144" s="2" t="inlineStr">
-        <is>
-          <t>NĐ 125/2020</t>
-        </is>
-      </c>
-      <c r="S144" s="2" t="inlineStr"/>
+      <c r="L144" s="4" t="inlineStr"/>
+      <c r="M144" s="4" t="inlineStr"/>
+      <c r="N144" s="4" t="inlineStr">
+        <is>
+          <t>Buộc hủy hóa đơn</t>
+        </is>
+      </c>
+      <c r="O144" s="4" t="inlineStr">
+        <is>
+          <t>2020-12-05</t>
+        </is>
+      </c>
+      <c r="P144" s="4" t="inlineStr">
+        <is>
+          <t>2026-01-15</t>
+        </is>
+      </c>
+      <c r="Q144" s="4" t="inlineStr">
+        <is>
+          <t>Đã bãi bỏ từ 16/01/2026 (chỉ áp dụng hành vi đã kết thúc trước ngày này)</t>
+        </is>
+      </c>
+      <c r="R144" s="4" t="inlineStr">
+        <is>
+          <t>NĐ 125/2020</t>
+        </is>
+      </c>
+      <c r="S144" s="4" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
@@ -10346,36 +10362,44 @@
         </is>
       </c>
       <c r="C145" s="2" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D145" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E145" s="2" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="E145" s="2" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
       <c r="F145" s="2" t="inlineStr">
         <is>
-          <t>Nộp thông báo, báo cáo về hóa đơn quá hạn 01-05 ngày</t>
+          <t>Tiêu hủy hóa đơn quá hạn từ 11 ngày làm việc</t>
         </is>
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>Cảnh cáo</t>
-        </is>
-      </c>
-      <c r="H145" s="3" t="n"/>
-      <c r="I145" s="3" t="n"/>
-      <c r="J145" s="3" t="n"/>
-      <c r="K145" s="3" t="n"/>
+          <t>Phạt tiền (khung)</t>
+        </is>
+      </c>
+      <c r="H145" s="3" t="n">
+        <v>4000000</v>
+      </c>
+      <c r="I145" s="3" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="J145" s="3" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="K145" s="3" t="n">
+        <v>4000000</v>
+      </c>
       <c r="L145" s="2" t="inlineStr"/>
-      <c r="M145" s="2" t="inlineStr">
-        <is>
-          <t>Có tình tiết giảm nhẹ</t>
-        </is>
-      </c>
+      <c r="M145" s="2" t="inlineStr"/>
       <c r="N145" s="2" t="inlineStr"/>
       <c r="O145" s="2" t="inlineStr">
         <is>
-          <t>2020-12-05</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="P145" s="2" t="inlineStr"/>
@@ -10386,10 +10410,14 @@
       </c>
       <c r="R145" s="2" t="inlineStr">
         <is>
-          <t>NĐ 125/2020</t>
-        </is>
-      </c>
-      <c r="S145" s="2" t="inlineStr"/>
+          <t>NĐ 310/2025</t>
+        </is>
+      </c>
+      <c r="S145" s="2" t="inlineStr">
+        <is>
+          <t>Ký hiệu điểm theo bản OCR NĐ310 (đánh số lại a-d, đ); cần đối chiếu với bản gốc.</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
@@ -10403,19 +10431,19 @@
         </is>
       </c>
       <c r="C146" s="2" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D146" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>b</t>
         </is>
       </c>
       <c r="F146" s="2" t="inlineStr">
         <is>
-          <t>Nộp thông báo, báo cáo về hóa đơn quá hạn 01-10 ngày</t>
+          <t>Không tiêu hủy hóa đơn theo quy định</t>
         </is>
       </c>
       <c r="G146" s="2" t="inlineStr">
@@ -10424,27 +10452,27 @@
         </is>
       </c>
       <c r="H146" s="3" t="n">
-        <v>1000000</v>
+        <v>4000000</v>
       </c>
       <c r="I146" s="3" t="n">
-        <v>3000000</v>
+        <v>8000000</v>
       </c>
       <c r="J146" s="3" t="n">
-        <v>500000</v>
+        <v>2000000</v>
       </c>
       <c r="K146" s="3" t="n">
-        <v>1500000</v>
+        <v>4000000</v>
       </c>
       <c r="L146" s="2" t="inlineStr"/>
-      <c r="M146" s="2" t="inlineStr">
-        <is>
-          <t>Trừ trường hợp cảnh cáo khoản 1</t>
-        </is>
-      </c>
-      <c r="N146" s="2" t="inlineStr"/>
+      <c r="M146" s="2" t="inlineStr"/>
+      <c r="N146" s="2" t="inlineStr">
+        <is>
+          <t>Buộc tiêu hủy hóa đơn</t>
+        </is>
+      </c>
       <c r="O146" s="2" t="inlineStr">
         <is>
-          <t>2020-12-05</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="P146" s="2" t="inlineStr"/>
@@ -10455,10 +10483,14 @@
       </c>
       <c r="R146" s="2" t="inlineStr">
         <is>
-          <t>NĐ 125/2020</t>
-        </is>
-      </c>
-      <c r="S146" s="2" t="inlineStr"/>
+          <t>NĐ 310/2025</t>
+        </is>
+      </c>
+      <c r="S146" s="2" t="inlineStr">
+        <is>
+          <t>Ký hiệu điểm theo bản OCR NĐ310 (đánh số lại a-d, đ); cần đối chiếu với bản gốc.</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
@@ -10472,19 +10504,19 @@
         </is>
       </c>
       <c r="C147" s="2" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D147" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E147" s="2" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>c</t>
         </is>
       </c>
       <c r="F147" s="2" t="inlineStr">
         <is>
-          <t>Lập sai / không đầy đủ nội dung thông báo, báo cáo về hóa đơn</t>
+          <t>Tiêu hủy hóa đơn không đúng trình tự, thủ tục</t>
         </is>
       </c>
       <c r="G147" s="2" t="inlineStr">
@@ -10493,27 +10525,23 @@
         </is>
       </c>
       <c r="H147" s="3" t="n">
-        <v>1000000</v>
+        <v>4000000</v>
       </c>
       <c r="I147" s="3" t="n">
-        <v>3000000</v>
+        <v>8000000</v>
       </c>
       <c r="J147" s="3" t="n">
-        <v>500000</v>
+        <v>2000000</v>
       </c>
       <c r="K147" s="3" t="n">
-        <v>1500000</v>
+        <v>4000000</v>
       </c>
       <c r="L147" s="2" t="inlineStr"/>
       <c r="M147" s="2" t="inlineStr"/>
-      <c r="N147" s="2" t="inlineStr">
-        <is>
-          <t>Buộc lập, gửi thông báo, báo cáo về hóa đơn</t>
-        </is>
-      </c>
+      <c r="N147" s="2" t="inlineStr"/>
       <c r="O147" s="2" t="inlineStr">
         <is>
-          <t>2020-12-05</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="P147" s="2" t="inlineStr"/>
@@ -10524,12 +10552,12 @@
       </c>
       <c r="R147" s="2" t="inlineStr">
         <is>
-          <t>NĐ 125/2020</t>
+          <t>NĐ 310/2025</t>
         </is>
       </c>
       <c r="S147" s="2" t="inlineStr">
         <is>
-          <t>Không phạt nếu tự phát hiện, lập lại báo cáo thay thế trước khi có quyết định thanh tra/kiểm tra.</t>
+          <t>Ký hiệu điểm theo bản OCR NĐ310 (đánh số lại a-d, đ); cần đối chiếu với bản gốc.</t>
         </is>
       </c>
     </row>
@@ -10545,15 +10573,19 @@
         </is>
       </c>
       <c r="C148" s="2" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D148" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="E148" s="2" t="inlineStr"/>
+      <c r="E148" s="2" t="inlineStr">
+        <is>
+          <t>đ</t>
+        </is>
+      </c>
       <c r="F148" s="2" t="inlineStr">
         <is>
-          <t>Nộp thông báo, báo cáo về hóa đơn quá hạn 11-20 ngày</t>
+          <t>Tiêu hủy hóa đơn không đúng các trường hợp phải tiêu hủy</t>
         </is>
       </c>
       <c r="G148" s="2" t="inlineStr">
@@ -10562,23 +10594,23 @@
         </is>
       </c>
       <c r="H148" s="3" t="n">
+        <v>4000000</v>
+      </c>
+      <c r="I148" s="3" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="J148" s="3" t="n">
         <v>2000000</v>
       </c>
-      <c r="I148" s="3" t="n">
+      <c r="K148" s="3" t="n">
         <v>4000000</v>
-      </c>
-      <c r="J148" s="3" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="K148" s="3" t="n">
-        <v>2000000</v>
       </c>
       <c r="L148" s="2" t="inlineStr"/>
       <c r="M148" s="2" t="inlineStr"/>
       <c r="N148" s="2" t="inlineStr"/>
       <c r="O148" s="2" t="inlineStr">
         <is>
-          <t>2020-12-05</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="P148" s="2" t="inlineStr"/>
@@ -10589,10 +10621,14 @@
       </c>
       <c r="R148" s="2" t="inlineStr">
         <is>
-          <t>NĐ 125/2020</t>
-        </is>
-      </c>
-      <c r="S148" s="2" t="inlineStr"/>
+          <t>NĐ 310/2025</t>
+        </is>
+      </c>
+      <c r="S148" s="2" t="inlineStr">
+        <is>
+          <t>Ký hiệu điểm theo bản OCR NĐ310 (đánh số lại a-d, đ); cần đối chiếu với bản gốc.</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
@@ -10606,15 +10642,15 @@
         </is>
       </c>
       <c r="C149" s="2" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D149" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E149" s="2" t="inlineStr"/>
       <c r="F149" s="2" t="inlineStr">
         <is>
-          <t>Nộp thông báo, báo cáo về hóa đơn quá hạn 21-90 ngày</t>
+          <t>Sử dụng hóa đơn không hợp pháp / sử dụng không hợp pháp hóa đơn (Điều 4 NĐ125)</t>
         </is>
       </c>
       <c r="G149" s="2" t="inlineStr">
@@ -10623,20 +10659,28 @@
         </is>
       </c>
       <c r="H149" s="3" t="n">
-        <v>4000000</v>
+        <v>20000000</v>
       </c>
       <c r="I149" s="3" t="n">
-        <v>8000000</v>
+        <v>50000000</v>
       </c>
       <c r="J149" s="3" t="n">
-        <v>2000000</v>
+        <v>10000000</v>
       </c>
       <c r="K149" s="3" t="n">
-        <v>4000000</v>
+        <v>25000000</v>
       </c>
       <c r="L149" s="2" t="inlineStr"/>
-      <c r="M149" s="2" t="inlineStr"/>
-      <c r="N149" s="2" t="inlineStr"/>
+      <c r="M149" s="2" t="inlineStr">
+        <is>
+          <t>Trừ điểm đ khoản 1 Điều 16 và điểm d khoản 1 Điều 17 (khi thuộc diện phạt 20% hoặc trốn thuế)</t>
+        </is>
+      </c>
+      <c r="N149" s="2" t="inlineStr">
+        <is>
+          <t>Đến 15/01/2026: buộc hủy hóa đơn đã sử dụng (khoản 2 Điều 28 bị bãi bỏ từ 16/01/2026)</t>
+        </is>
+      </c>
       <c r="O149" s="2" t="inlineStr">
         <is>
           <t>2020-12-05</t>
@@ -10670,37 +10714,29 @@
         <v>29</v>
       </c>
       <c r="D150" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="E150" s="2" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="E150" s="2" t="inlineStr"/>
       <c r="F150" s="2" t="inlineStr">
         <is>
-          <t>Nộp thông báo, báo cáo về hóa đơn quá hạn từ 91 ngày</t>
+          <t>Nộp thông báo, báo cáo về hóa đơn quá hạn 01-05 ngày</t>
         </is>
       </c>
       <c r="G150" s="2" t="inlineStr">
         <is>
-          <t>Phạt tiền (khung)</t>
-        </is>
-      </c>
-      <c r="H150" s="3" t="n">
-        <v>5000000</v>
-      </c>
-      <c r="I150" s="3" t="n">
-        <v>15000000</v>
-      </c>
-      <c r="J150" s="3" t="n">
-        <v>2500000</v>
-      </c>
-      <c r="K150" s="3" t="n">
-        <v>7500000</v>
-      </c>
+          <t>Cảnh cáo</t>
+        </is>
+      </c>
+      <c r="H150" s="3" t="n"/>
+      <c r="I150" s="3" t="n"/>
+      <c r="J150" s="3" t="n"/>
+      <c r="K150" s="3" t="n"/>
       <c r="L150" s="2" t="inlineStr"/>
-      <c r="M150" s="2" t="inlineStr"/>
+      <c r="M150" s="2" t="inlineStr">
+        <is>
+          <t>Có tình tiết giảm nhẹ</t>
+        </is>
+      </c>
       <c r="N150" s="2" t="inlineStr"/>
       <c r="O150" s="2" t="inlineStr">
         <is>
@@ -10735,16 +10771,16 @@
         <v>29</v>
       </c>
       <c r="D151" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>a</t>
         </is>
       </c>
       <c r="F151" s="2" t="inlineStr">
         <is>
-          <t>Không nộp thông báo, báo cáo về hóa đơn</t>
+          <t>Nộp thông báo, báo cáo về hóa đơn quá hạn 01-10 ngày</t>
         </is>
       </c>
       <c r="G151" s="2" t="inlineStr">
@@ -10753,24 +10789,24 @@
         </is>
       </c>
       <c r="H151" s="3" t="n">
-        <v>5000000</v>
+        <v>1000000</v>
       </c>
       <c r="I151" s="3" t="n">
-        <v>15000000</v>
+        <v>3000000</v>
       </c>
       <c r="J151" s="3" t="n">
-        <v>2500000</v>
+        <v>500000</v>
       </c>
       <c r="K151" s="3" t="n">
-        <v>7500000</v>
+        <v>1500000</v>
       </c>
       <c r="L151" s="2" t="inlineStr"/>
-      <c r="M151" s="2" t="inlineStr"/>
-      <c r="N151" s="2" t="inlineStr">
-        <is>
-          <t>Buộc lập, gửi thông báo, báo cáo về hóa đơn</t>
-        </is>
-      </c>
+      <c r="M151" s="2" t="inlineStr">
+        <is>
+          <t>Trừ trường hợp cảnh cáo khoản 1</t>
+        </is>
+      </c>
+      <c r="N151" s="2" t="inlineStr"/>
       <c r="O151" s="2" t="inlineStr">
         <is>
           <t>2020-12-05</t>
@@ -10801,15 +10837,19 @@
         </is>
       </c>
       <c r="C152" s="2" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D152" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E152" s="2" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="E152" s="2" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
       <c r="F152" s="2" t="inlineStr">
         <is>
-          <t>Chuyển dữ liệu hóa đơn điện tử cho cơ quan thuế quá hạn 01-05 ngày làm việc</t>
+          <t>Lập sai / không đầy đủ nội dung thông báo, báo cáo về hóa đơn</t>
         </is>
       </c>
       <c r="G152" s="2" t="inlineStr">
@@ -10818,20 +10858,24 @@
         </is>
       </c>
       <c r="H152" s="3" t="n">
-        <v>2000000</v>
+        <v>1000000</v>
       </c>
       <c r="I152" s="3" t="n">
-        <v>5000000</v>
+        <v>3000000</v>
       </c>
       <c r="J152" s="3" t="n">
-        <v>1000000</v>
+        <v>500000</v>
       </c>
       <c r="K152" s="3" t="n">
-        <v>2500000</v>
+        <v>1500000</v>
       </c>
       <c r="L152" s="2" t="inlineStr"/>
       <c r="M152" s="2" t="inlineStr"/>
-      <c r="N152" s="2" t="inlineStr"/>
+      <c r="N152" s="2" t="inlineStr">
+        <is>
+          <t>Buộc lập, gửi thông báo, báo cáo về hóa đơn</t>
+        </is>
+      </c>
       <c r="O152" s="2" t="inlineStr">
         <is>
           <t>2020-12-05</t>
@@ -10848,7 +10892,11 @@
           <t>NĐ 125/2020</t>
         </is>
       </c>
-      <c r="S152" s="2" t="inlineStr"/>
+      <c r="S152" s="2" t="inlineStr">
+        <is>
+          <t>Không phạt nếu tự phát hiện, lập lại báo cáo thay thế trước khi có quyết định thanh tra/kiểm tra.</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
@@ -10862,19 +10910,15 @@
         </is>
       </c>
       <c r="C153" s="2" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D153" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E153" s="2" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="E153" s="2" t="inlineStr"/>
       <c r="F153" s="2" t="inlineStr">
         <is>
-          <t>Chuyển dữ liệu hóa đơn điện tử quá hạn 06-10 ngày làm việc</t>
+          <t>Nộp thông báo, báo cáo về hóa đơn quá hạn 11-20 ngày</t>
         </is>
       </c>
       <c r="G153" s="2" t="inlineStr">
@@ -10883,16 +10927,16 @@
         </is>
       </c>
       <c r="H153" s="3" t="n">
-        <v>5000000</v>
+        <v>2000000</v>
       </c>
       <c r="I153" s="3" t="n">
-        <v>8000000</v>
+        <v>4000000</v>
       </c>
       <c r="J153" s="3" t="n">
-        <v>2500000</v>
+        <v>1000000</v>
       </c>
       <c r="K153" s="3" t="n">
-        <v>4000000</v>
+        <v>2000000</v>
       </c>
       <c r="L153" s="2" t="inlineStr"/>
       <c r="M153" s="2" t="inlineStr"/>
@@ -10927,19 +10971,15 @@
         </is>
       </c>
       <c r="C154" s="2" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D154" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E154" s="2" t="inlineStr">
-        <is>
-          <t>b</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="E154" s="2" t="inlineStr"/>
       <c r="F154" s="2" t="inlineStr">
         <is>
-          <t>Chuyển bảng tổng hợp dữ liệu hóa đơn điện tử không đầy đủ số lượng hóa đơn đã lập trong kỳ</t>
+          <t>Nộp thông báo, báo cáo về hóa đơn quá hạn 21-90 ngày</t>
         </is>
       </c>
       <c r="G154" s="2" t="inlineStr">
@@ -10948,24 +10988,20 @@
         </is>
       </c>
       <c r="H154" s="3" t="n">
-        <v>5000000</v>
+        <v>4000000</v>
       </c>
       <c r="I154" s="3" t="n">
         <v>8000000</v>
       </c>
       <c r="J154" s="3" t="n">
-        <v>2500000</v>
+        <v>2000000</v>
       </c>
       <c r="K154" s="3" t="n">
         <v>4000000</v>
       </c>
       <c r="L154" s="2" t="inlineStr"/>
       <c r="M154" s="2" t="inlineStr"/>
-      <c r="N154" s="2" t="inlineStr">
-        <is>
-          <t>Buộc chuyển dữ liệu hóa đơn điện tử</t>
-        </is>
-      </c>
+      <c r="N154" s="2" t="inlineStr"/>
       <c r="O154" s="2" t="inlineStr">
         <is>
           <t>2020-12-05</t>
@@ -10996,10 +11032,10 @@
         </is>
       </c>
       <c r="C155" s="2" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D155" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E155" s="2" t="inlineStr">
         <is>
@@ -11008,7 +11044,7 @@
       </c>
       <c r="F155" s="2" t="inlineStr">
         <is>
-          <t>Chuyển dữ liệu hóa đơn điện tử quá hạn từ 11 ngày làm việc</t>
+          <t>Nộp thông báo, báo cáo về hóa đơn quá hạn từ 91 ngày</t>
         </is>
       </c>
       <c r="G155" s="2" t="inlineStr">
@@ -11017,16 +11053,16 @@
         </is>
       </c>
       <c r="H155" s="3" t="n">
-        <v>10000000</v>
+        <v>5000000</v>
       </c>
       <c r="I155" s="3" t="n">
-        <v>20000000</v>
+        <v>15000000</v>
       </c>
       <c r="J155" s="3" t="n">
-        <v>5000000</v>
+        <v>2500000</v>
       </c>
       <c r="K155" s="3" t="n">
-        <v>10000000</v>
+        <v>7500000</v>
       </c>
       <c r="L155" s="2" t="inlineStr"/>
       <c r="M155" s="2" t="inlineStr"/>
@@ -11061,10 +11097,10 @@
         </is>
       </c>
       <c r="C156" s="2" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D156" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E156" s="2" t="inlineStr">
         <is>
@@ -11073,7 +11109,7 @@
       </c>
       <c r="F156" s="2" t="inlineStr">
         <is>
-          <t>Không chuyển dữ liệu hóa đơn điện tử cho cơ quan thuế theo thời hạn</t>
+          <t>Không nộp thông báo, báo cáo về hóa đơn</t>
         </is>
       </c>
       <c r="G156" s="2" t="inlineStr">
@@ -11082,22 +11118,22 @@
         </is>
       </c>
       <c r="H156" s="3" t="n">
-        <v>10000000</v>
+        <v>5000000</v>
       </c>
       <c r="I156" s="3" t="n">
-        <v>20000000</v>
+        <v>15000000</v>
       </c>
       <c r="J156" s="3" t="n">
-        <v>5000000</v>
+        <v>2500000</v>
       </c>
       <c r="K156" s="3" t="n">
-        <v>10000000</v>
+        <v>7500000</v>
       </c>
       <c r="L156" s="2" t="inlineStr"/>
       <c r="M156" s="2" t="inlineStr"/>
       <c r="N156" s="2" t="inlineStr">
         <is>
-          <t>Buộc chuyển dữ liệu hóa đơn điện tử</t>
+          <t>Buộc lập, gửi thông báo, báo cáo về hóa đơn</t>
         </is>
       </c>
       <c r="O156" s="2" t="inlineStr">
@@ -11119,146 +11155,130 @@
       <c r="S156" s="2" t="inlineStr"/>
     </row>
     <row r="157">
-      <c r="A157" s="4" t="inlineStr">
+      <c r="A157" s="2" t="inlineStr">
         <is>
           <t>P156</t>
         </is>
       </c>
-      <c r="B157" s="4" t="inlineStr">
+      <c r="B157" s="2" t="inlineStr">
         <is>
           <t>Hóa đơn</t>
         </is>
       </c>
-      <c r="C157" s="4" t="n">
-        <v>31</v>
-      </c>
-      <c r="D157" s="4" t="inlineStr"/>
-      <c r="E157" s="4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F157" s="4" t="inlineStr">
-        <is>
-          <t>Cung cấp phần mềm hóa đơn tự in không đảm bảo nguyên tắc / in ra không đủ nội dung</t>
-        </is>
-      </c>
-      <c r="G157" s="4" t="inlineStr">
-        <is>
-          <t>Phạt tiền (khung)</t>
-        </is>
-      </c>
-      <c r="H157" s="5" t="n">
+      <c r="C157" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="D157" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E157" s="2" t="inlineStr"/>
+      <c r="F157" s="2" t="inlineStr">
+        <is>
+          <t>Chuyển dữ liệu hóa đơn điện tử cho cơ quan thuế quá hạn 01-05 ngày làm việc</t>
+        </is>
+      </c>
+      <c r="G157" s="2" t="inlineStr">
+        <is>
+          <t>Phạt tiền (khung)</t>
+        </is>
+      </c>
+      <c r="H157" s="3" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="I157" s="3" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="J157" s="3" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="K157" s="3" t="n">
+        <v>2500000</v>
+      </c>
+      <c r="L157" s="2" t="inlineStr"/>
+      <c r="M157" s="2" t="inlineStr"/>
+      <c r="N157" s="2" t="inlineStr"/>
+      <c r="O157" s="2" t="inlineStr">
+        <is>
+          <t>2020-12-05</t>
+        </is>
+      </c>
+      <c r="P157" s="2" t="inlineStr"/>
+      <c r="Q157" s="2" t="inlineStr">
+        <is>
+          <t>Còn hiệu lực</t>
+        </is>
+      </c>
+      <c r="R157" s="2" t="inlineStr">
+        <is>
+          <t>NĐ 125/2020</t>
+        </is>
+      </c>
+      <c r="S157" s="2" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>P157</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>Hóa đơn</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="D158" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E158" s="2" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="F158" s="2" t="inlineStr">
+        <is>
+          <t>Chuyển dữ liệu hóa đơn điện tử quá hạn 06-10 ngày làm việc</t>
+        </is>
+      </c>
+      <c r="G158" s="2" t="inlineStr">
+        <is>
+          <t>Phạt tiền (khung)</t>
+        </is>
+      </c>
+      <c r="H158" s="3" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="I158" s="3" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="J158" s="3" t="n">
+        <v>2500000</v>
+      </c>
+      <c r="K158" s="3" t="n">
         <v>4000000</v>
       </c>
-      <c r="I157" s="5" t="n">
-        <v>8000000</v>
-      </c>
-      <c r="J157" s="5" t="n">
-        <v>2000000</v>
-      </c>
-      <c r="K157" s="5" t="n">
-        <v>4000000</v>
-      </c>
-      <c r="L157" s="4" t="inlineStr"/>
-      <c r="M157" s="4" t="inlineStr"/>
-      <c r="N157" s="4" t="inlineStr"/>
-      <c r="O157" s="4" t="inlineStr">
-        <is>
-          <t>2020-12-05</t>
-        </is>
-      </c>
-      <c r="P157" s="4" t="inlineStr">
-        <is>
-          <t>2026-01-15</t>
-        </is>
-      </c>
-      <c r="Q157" s="4" t="inlineStr">
-        <is>
-          <t>Đã được thay bằng quy định mới từ 16/01/2026 (chỉ áp dụng hành vi đã kết thúc trước ngày này)</t>
-        </is>
-      </c>
-      <c r="R157" s="4" t="inlineStr">
-        <is>
-          <t>NĐ 125/2020</t>
-        </is>
-      </c>
-      <c r="S157" s="4" t="inlineStr">
-        <is>
-          <t>Dành cho tổ chức cung cấp dịch vụ/phần mềm hóa đơn.</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" s="4" t="inlineStr">
-        <is>
-          <t>P157</t>
-        </is>
-      </c>
-      <c r="B158" s="4" t="inlineStr">
-        <is>
-          <t>Hóa đơn</t>
-        </is>
-      </c>
-      <c r="C158" s="4" t="n">
-        <v>31</v>
-      </c>
-      <c r="D158" s="4" t="inlineStr"/>
-      <c r="E158" s="4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F158" s="4" t="inlineStr">
-        <is>
-          <t>Cung cấp phần mềm hóa đơn điện tử không đảm bảo nguyên tắc</t>
-        </is>
-      </c>
-      <c r="G158" s="4" t="inlineStr">
-        <is>
-          <t>Phạt tiền (khung)</t>
-        </is>
-      </c>
-      <c r="H158" s="5" t="n">
-        <v>4000000</v>
-      </c>
-      <c r="I158" s="5" t="n">
-        <v>8000000</v>
-      </c>
-      <c r="J158" s="5" t="n">
-        <v>2000000</v>
-      </c>
-      <c r="K158" s="5" t="n">
-        <v>4000000</v>
-      </c>
-      <c r="L158" s="4" t="inlineStr"/>
-      <c r="M158" s="4" t="inlineStr"/>
-      <c r="N158" s="4" t="inlineStr"/>
-      <c r="O158" s="4" t="inlineStr">
-        <is>
-          <t>2020-12-05</t>
-        </is>
-      </c>
-      <c r="P158" s="4" t="inlineStr">
-        <is>
-          <t>2026-01-15</t>
-        </is>
-      </c>
-      <c r="Q158" s="4" t="inlineStr">
-        <is>
-          <t>Đã được thay bằng quy định mới từ 16/01/2026 (chỉ áp dụng hành vi đã kết thúc trước ngày này)</t>
-        </is>
-      </c>
-      <c r="R158" s="4" t="inlineStr">
-        <is>
-          <t>NĐ 125/2020</t>
-        </is>
-      </c>
-      <c r="S158" s="4" t="inlineStr">
-        <is>
-          <t>Dành cho tổ chức cung cấp dịch vụ/phần mềm hóa đơn.</t>
-        </is>
-      </c>
+      <c r="L158" s="2" t="inlineStr"/>
+      <c r="M158" s="2" t="inlineStr"/>
+      <c r="N158" s="2" t="inlineStr"/>
+      <c r="O158" s="2" t="inlineStr">
+        <is>
+          <t>2020-12-05</t>
+        </is>
+      </c>
+      <c r="P158" s="2" t="inlineStr"/>
+      <c r="Q158" s="2" t="inlineStr">
+        <is>
+          <t>Còn hiệu lực</t>
+        </is>
+      </c>
+      <c r="R158" s="2" t="inlineStr">
+        <is>
+          <t>NĐ 125/2020</t>
+        </is>
+      </c>
+      <c r="S158" s="2" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
@@ -11272,13 +11292,19 @@
         </is>
       </c>
       <c r="C159" s="2" t="n">
-        <v>31</v>
-      </c>
-      <c r="D159" s="2" t="inlineStr"/>
-      <c r="E159" s="2" t="inlineStr"/>
+        <v>30</v>
+      </c>
+      <c r="D159" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E159" s="2" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
       <c r="F159" s="2" t="inlineStr">
         <is>
-          <t>Cung cấp giải pháp khởi tạo, kết nối, nhận, truyền, lưu trữ, xử lý dữ liệu hóa đơn điện tử không đảm bảo nguyên tắc</t>
+          <t>Chuyển bảng tổng hợp dữ liệu hóa đơn điện tử không đầy đủ số lượng hóa đơn đã lập trong kỳ</t>
         </is>
       </c>
       <c r="G159" s="2" t="inlineStr">
@@ -11287,23 +11313,27 @@
         </is>
       </c>
       <c r="H159" s="3" t="n">
-        <v>4000000</v>
+        <v>5000000</v>
       </c>
       <c r="I159" s="3" t="n">
         <v>8000000</v>
       </c>
       <c r="J159" s="3" t="n">
-        <v>2000000</v>
+        <v>2500000</v>
       </c>
       <c r="K159" s="3" t="n">
         <v>4000000</v>
       </c>
       <c r="L159" s="2" t="inlineStr"/>
       <c r="M159" s="2" t="inlineStr"/>
-      <c r="N159" s="2" t="inlineStr"/>
+      <c r="N159" s="2" t="inlineStr">
+        <is>
+          <t>Buộc chuyển dữ liệu hóa đơn điện tử</t>
+        </is>
+      </c>
       <c r="O159" s="2" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2020-12-05</t>
         </is>
       </c>
       <c r="P159" s="2" t="inlineStr"/>
@@ -11317,14 +11347,345 @@
           <t>NĐ 125/2020</t>
         </is>
       </c>
-      <c r="S159" s="2" t="inlineStr">
+      <c r="S159" s="2" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>P159</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>Hóa đơn</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="D160" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E160" s="2" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="F160" s="2" t="inlineStr">
+        <is>
+          <t>Chuyển dữ liệu hóa đơn điện tử quá hạn từ 11 ngày làm việc</t>
+        </is>
+      </c>
+      <c r="G160" s="2" t="inlineStr">
+        <is>
+          <t>Phạt tiền (khung)</t>
+        </is>
+      </c>
+      <c r="H160" s="3" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="I160" s="3" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="J160" s="3" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="K160" s="3" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="L160" s="2" t="inlineStr"/>
+      <c r="M160" s="2" t="inlineStr"/>
+      <c r="N160" s="2" t="inlineStr"/>
+      <c r="O160" s="2" t="inlineStr">
+        <is>
+          <t>2020-12-05</t>
+        </is>
+      </c>
+      <c r="P160" s="2" t="inlineStr"/>
+      <c r="Q160" s="2" t="inlineStr">
+        <is>
+          <t>Còn hiệu lực</t>
+        </is>
+      </c>
+      <c r="R160" s="2" t="inlineStr">
+        <is>
+          <t>NĐ 125/2020</t>
+        </is>
+      </c>
+      <c r="S160" s="2" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
+        <is>
+          <t>P160</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>Hóa đơn</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="D161" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E161" s="2" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="F161" s="2" t="inlineStr">
+        <is>
+          <t>Không chuyển dữ liệu hóa đơn điện tử cho cơ quan thuế theo thời hạn</t>
+        </is>
+      </c>
+      <c r="G161" s="2" t="inlineStr">
+        <is>
+          <t>Phạt tiền (khung)</t>
+        </is>
+      </c>
+      <c r="H161" s="3" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="I161" s="3" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="J161" s="3" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="K161" s="3" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="L161" s="2" t="inlineStr"/>
+      <c r="M161" s="2" t="inlineStr"/>
+      <c r="N161" s="2" t="inlineStr">
+        <is>
+          <t>Buộc chuyển dữ liệu hóa đơn điện tử</t>
+        </is>
+      </c>
+      <c r="O161" s="2" t="inlineStr">
+        <is>
+          <t>2020-12-05</t>
+        </is>
+      </c>
+      <c r="P161" s="2" t="inlineStr"/>
+      <c r="Q161" s="2" t="inlineStr">
+        <is>
+          <t>Còn hiệu lực</t>
+        </is>
+      </c>
+      <c r="R161" s="2" t="inlineStr">
+        <is>
+          <t>NĐ 125/2020</t>
+        </is>
+      </c>
+      <c r="S161" s="2" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" s="4" t="inlineStr">
+        <is>
+          <t>P161</t>
+        </is>
+      </c>
+      <c r="B162" s="4" t="inlineStr">
+        <is>
+          <t>Hóa đơn</t>
+        </is>
+      </c>
+      <c r="C162" s="4" t="n">
+        <v>31</v>
+      </c>
+      <c r="D162" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E162" s="4" t="inlineStr"/>
+      <c r="F162" s="4" t="inlineStr">
+        <is>
+          <t>Cung cấp phần mềm hóa đơn tự in không đảm bảo nguyên tắc / in ra không đủ nội dung</t>
+        </is>
+      </c>
+      <c r="G162" s="4" t="inlineStr">
+        <is>
+          <t>Phạt tiền (khung)</t>
+        </is>
+      </c>
+      <c r="H162" s="5" t="n">
+        <v>4000000</v>
+      </c>
+      <c r="I162" s="5" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="J162" s="5" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="K162" s="5" t="n">
+        <v>4000000</v>
+      </c>
+      <c r="L162" s="4" t="inlineStr"/>
+      <c r="M162" s="4" t="inlineStr"/>
+      <c r="N162" s="4" t="inlineStr"/>
+      <c r="O162" s="4" t="inlineStr">
+        <is>
+          <t>2020-12-05</t>
+        </is>
+      </c>
+      <c r="P162" s="4" t="inlineStr">
+        <is>
+          <t>2026-01-15</t>
+        </is>
+      </c>
+      <c r="Q162" s="4" t="inlineStr">
+        <is>
+          <t>Đã được thay bằng quy định mới từ 16/01/2026 (chỉ áp dụng hành vi đã kết thúc trước ngày này)</t>
+        </is>
+      </c>
+      <c r="R162" s="4" t="inlineStr">
+        <is>
+          <t>NĐ 125/2020</t>
+        </is>
+      </c>
+      <c r="S162" s="4" t="inlineStr">
+        <is>
+          <t>Dành cho tổ chức cung cấp dịch vụ/phần mềm hóa đơn.</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="4" t="inlineStr">
+        <is>
+          <t>P162</t>
+        </is>
+      </c>
+      <c r="B163" s="4" t="inlineStr">
+        <is>
+          <t>Hóa đơn</t>
+        </is>
+      </c>
+      <c r="C163" s="4" t="n">
+        <v>31</v>
+      </c>
+      <c r="D163" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E163" s="4" t="inlineStr"/>
+      <c r="F163" s="4" t="inlineStr">
+        <is>
+          <t>Cung cấp phần mềm hóa đơn điện tử không đảm bảo nguyên tắc</t>
+        </is>
+      </c>
+      <c r="G163" s="4" t="inlineStr">
+        <is>
+          <t>Phạt tiền (khung)</t>
+        </is>
+      </c>
+      <c r="H163" s="5" t="n">
+        <v>4000000</v>
+      </c>
+      <c r="I163" s="5" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="J163" s="5" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="K163" s="5" t="n">
+        <v>4000000</v>
+      </c>
+      <c r="L163" s="4" t="inlineStr"/>
+      <c r="M163" s="4" t="inlineStr"/>
+      <c r="N163" s="4" t="inlineStr"/>
+      <c r="O163" s="4" t="inlineStr">
+        <is>
+          <t>2020-12-05</t>
+        </is>
+      </c>
+      <c r="P163" s="4" t="inlineStr">
+        <is>
+          <t>2026-01-15</t>
+        </is>
+      </c>
+      <c r="Q163" s="4" t="inlineStr">
+        <is>
+          <t>Đã được thay bằng quy định mới từ 16/01/2026 (chỉ áp dụng hành vi đã kết thúc trước ngày này)</t>
+        </is>
+      </c>
+      <c r="R163" s="4" t="inlineStr">
+        <is>
+          <t>NĐ 125/2020</t>
+        </is>
+      </c>
+      <c r="S163" s="4" t="inlineStr">
+        <is>
+          <t>Dành cho tổ chức cung cấp dịch vụ/phần mềm hóa đơn.</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>P163</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>Hóa đơn</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="D164" s="2" t="inlineStr"/>
+      <c r="E164" s="2" t="inlineStr"/>
+      <c r="F164" s="2" t="inlineStr">
+        <is>
+          <t>Cung cấp giải pháp khởi tạo, kết nối, nhận, truyền, lưu trữ, xử lý dữ liệu hóa đơn điện tử không đảm bảo nguyên tắc</t>
+        </is>
+      </c>
+      <c r="G164" s="2" t="inlineStr">
+        <is>
+          <t>Phạt tiền (khung)</t>
+        </is>
+      </c>
+      <c r="H164" s="3" t="n">
+        <v>4000000</v>
+      </c>
+      <c r="I164" s="3" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="J164" s="3" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="K164" s="3" t="n">
+        <v>4000000</v>
+      </c>
+      <c r="L164" s="2" t="inlineStr"/>
+      <c r="M164" s="2" t="inlineStr"/>
+      <c r="N164" s="2" t="inlineStr"/>
+      <c r="O164" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="P164" s="2" t="inlineStr"/>
+      <c r="Q164" s="2" t="inlineStr">
+        <is>
+          <t>Còn hiệu lực</t>
+        </is>
+      </c>
+      <c r="R164" s="2" t="inlineStr">
+        <is>
+          <t>NĐ 310/2025+125/2020</t>
+        </is>
+      </c>
+      <c r="S164" s="2" t="inlineStr">
         <is>
           <t>NĐ310 thay Điều 31. Số tiền trong file OCR NĐ310 bị lỗi ('§.000.000'); khung 4-8 triệu được đối chiếu với Điều 31 NĐ125 gốc (cùng khung) - cần xác nhận lại trên bản PDF NĐ310.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S159"/>
+  <autoFilter ref="A1:S164"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -11335,7 +11696,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -11363,51 +11724,51 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Mức tối đa mỗi hành vi - thủ tục thuế</t>
+          <t>Mức tối đa mỗi hành vi (đến hết 15/01/2026)</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Tổ chức: tối đa 200.000.000 đ; cá nhân: tối đa 100.000.000 đ (hộ gia đình, hộ kinh doanh áp dụng như cá nhân)</t>
+          <t>Thủ tục thuế - tổ chức: tối đa 200.000.000 đ; cá nhân/hộ KD: tối đa 100.000.000 đ. Hóa đơn - tổ chức: tối đa 100.000.000 đ; cá nhân/hộ KD: tối đa 50.000.000 đ. Hình thức bổ sung: đình chỉ hoạt động in hóa đơn (khoản 2 Điều 7).</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Điều 7.1.b, 7.4.a NĐ125 (NĐ310 sửa: dẫn chiếu quy định pháp luật về xử lý vi phạm hành chính)</t>
+          <t>Điều 7.1.b, 7.2, 7.4.a NĐ125 gốc</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Mức tối đa mỗi hành vi - hóa đơn</t>
+          <t>Mức phạt tối đa mỗi hành vi (từ 16/01/2026)</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Tổ chức: tối đa 100.000.000 đ; cá nhân: tối đa 50.000.000 đ</t>
+          <t>NĐ310 thay điểm b khoản 1 Điều 7: mức phạt tiền tối đa đối với hành vi vi phạm thủ tục thuế và hóa đơn thực hiện theo pháp luật về xử lý vi phạm hành chính (con số cụ thể KHÔNG nêu trong NĐ310 và không có trong nguồn đã cung cấp). Khoản 2 Điều 7 (đình chỉ in hóa đơn) bị bãi bỏ.</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Điều 7.1.b NĐ125</t>
+          <t>Điều 1.5.a, Điều 2.2 NĐ310</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Khung phạt trong bảng = mức phạt đối với TỔ CHỨC</t>
+          <t>Mức phạt cá nhân so với tổ chức</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Mức phạt cá nhân/hộ kinh doanh áp dụng riêng. Cột 'cá nhân' trong file Excel là số THAM KHẢO bằng 1/2 mức tổ chức (theo Luật XLVPHC - văn bản này KHÔNG nằm trong hai nguồn đã cung cấp, cần xác nhận). Ngoại lệ: hành vi chỉ áp dụng cho tổ chức/ngân hàng.</t>
+          <t>Khung phạt trong bảng là mức đối với TỔ CHỨC. Với cùng một hành vi, mức phạt tổ chức gấp 02 lần mức phạt cá nhân, TRỪ hành vi tại Điều 16, 17, 18. Hộ gia đình, hộ kinh doanh áp dụng như cá nhân. Cột 'cá nhân' trong Excel = 1/2 mức tổ chức; không tính cho hành vi Điều 16, 17, 18 (phạt theo tỷ lệ). Điều 19 sau sửa đổi NĐ310 không còn khoản nêu rõ nguyên tắc này - nên đối chiếu thêm.</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Điều 7.4.a NĐ125; Luật XLVPHC (cần xác nhận)</t>
+          <t>Điều 5.5, Điều 7.4.a NĐ125 (NĐ310 không sửa Điều 5.5)</t>
         </is>
       </c>
     </row>
@@ -11499,83 +11860,100 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Thời hiệu xử phạt</t>
+          <t>Gộp hành vi trong cùng một ngày/vụ việc</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Thủ tục thuế: 02 năm; trốn thuế (chưa đến mức hình sự) và khai sai dẫn đến thiếu thuế: 05 năm. Hóa đơn: xem Điều 8 NĐ125 (hành vi đã kết thúc / đang thực hiện).</t>
+          <t>Cùng một ngày khai sai nhiều chỉ tiêu: phạt 01 hành vi có khung cao nhất. Cùng ngày chậm nộp nhiều hồ sơ khai cùng sắc thuế: phạt 01 hành vi cao nhất. Nhiều hóa đơn lập không đúng thời điểm / không lập trong một vụ việc: phạt 01 hành vi theo tổng số hóa đơn.</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Điều 8.2 NĐ125 (sửa bởi NĐ310)</t>
+          <t>Điều 5.3 NĐ125 (sửa bởi NĐ310)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Gộp hành vi trong cùng một ngày/vụ việc</t>
+          <t>Quy mô lớn (đến hết 15/01/2026)</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Cùng một ngày khai sai nhiều chỉ tiêu: phạt 01 hành vi có khung cao nhất. Cùng ngày chậm nộp nhiều hồ sơ khai cùng sắc thuế: phạt 01 hành vi cao nhất. Nhiều hóa đơn lập không đúng thời điểm / không lập trong một vụ việc: phạt 01 hành vi theo tổng số hóa đơn.</t>
+          <t>Thuế: số thuế (thiếu/trốn/miễn giảm hoàn cao hơn) từ 100.000.000 đ hoặc giá trị hàng hóa dịch vụ từ 500.000.000 đ trở lên. Hóa đơn: từ 10 số hóa đơn trở lên.</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Điều 5.3 NĐ125 (sửa bởi NĐ310)</t>
+          <t>Điều 6.2 NĐ125 gốc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Quy mô lớn</t>
+          <t>Quy mô lớn (từ 16/01/2026)</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Thuế: số thuế (thiếu/trốn/miễn giảm hoàn cao hơn) từ 100.000.000 đ hoặc giá trị hàng hóa dịch vụ từ 500.000.000 đ trở lên (NĐ125 gốc). Hóa đơn: từ 10 số hóa đơn trở lên (hành vi tại khoản 2 Điều 22, Điều 26, 27). NĐ310: trốn thuế từ 100.000.000 đ trở lên khi chuyển hồ sơ.</t>
+          <t>Hóa đơn: từ 10 số hóa đơn trở lên, chỉ đối với hành vi tại khoản 2 Điều 22, Điều 26, Điều 27. Thuế: chỉ còn trốn thuế từ 100.000.000 đ trở lên khi chuyển hồ sơ xử lý hình sự (tiêu chí 500 triệu giá trị hàng hóa không còn trong nội dung sửa đổi).</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Điều 6.2 NĐ125 (sửa bởi NĐ310)</t>
+          <t>Điều 1.4 NĐ310 (thay khoản 2 Điều 6)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Hiệu lực và chuyển tiếp</t>
+          <t>Thời hiệu xử phạt</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>NĐ125 hiệu lực 05/12/2020. NĐ310 hiệu lực 16/01/2026. Hành vi đã kết thúc trước 16/01/2026: áp dụng văn bản có hiệu lực tại thời điểm vi phạm. Hành vi đang thực hiện trước ngày này và bị phát hiện sau ngày này: áp dụng NĐ310.</t>
+          <t>Hóa đơn: 01 năm (danh sách hành vi 'đang thực hiện' đã được NĐ310 sửa tại Điều 8.1). Thủ tục thuế: 02 năm. Trốn thuế (chưa đến mức hình sự) và khai sai dẫn đến thiếu thuế: 05 năm.</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Điều 3 NĐ310</t>
+          <t>Điều 8.1.a NĐ125; Điều 8.2 NĐ125 (sửa bởi NĐ310)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>Hiệu lực và chuyển tiếp</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>NĐ125 hiệu lực 05/12/2020. NĐ310 hiệu lực 16/01/2026. Hành vi đã kết thúc trước 16/01/2026: áp dụng văn bản có hiệu lực tại thời điểm vi phạm. Hành vi đang thực hiện trước ngày này và bị phát hiện sau ngày này: áp dụng NĐ310.</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Điều 3 NĐ310</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
           <t>Chưa nằm trong bảng này</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>Tiền chậm nộp (0,03%/ngày), vi phạm hải quan, bảo hiểm xã hội, lao động, chuyển giá/GDLK ngoài các điều của NĐ125; mức phạt từng nghị định chuyên ngành. Văn bản gốc chưa được cung cấp.</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Tiền chậm nộp tiền thuế (tỷ lệ theo Luật Quản lý thuế - văn bản chưa được cung cấp, bảng này không nêu tỷ lệ); truy thu thuế; vi phạm hải quan, bảo hiểm xã hội, lao động; các nghị định xử phạt chuyên ngành khác.</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>

--- a/outputs/penalty_catalog/penalty_catalog.xlsx
+++ b/outputs/penalty_catalog/penalty_catalog.xlsx
@@ -7217,7 +7217,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>Đã được thay bằng quy định mới từ 16/01/2026 (chỉ áp dụng hành vi đã kết thúc trước ngày này)</t>
+          <t>Đã được NĐ102/2021 thay bằng quy định mới từ 01/01/2022 (chỉ áp dụng cho hành vi đã kết thúc trước ngày này)</t>
         </is>
       </c>
       <c r="T91" s="4" t="inlineStr">
@@ -10339,7 +10339,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>Đã được thay bằng quy định mới từ 16/01/2026 (chỉ áp dụng hành vi đã kết thúc trước ngày này)</t>
+          <t>Đã được NĐ102/2021 thay bằng quy định mới từ 01/01/2022 (chỉ áp dụng cho hành vi đã kết thúc trước ngày này)</t>
         </is>
       </c>
       <c r="T133" s="4" t="inlineStr">
@@ -20810,7 +20810,7 @@
       </c>
       <c r="G276" s="2" t="inlineStr">
         <is>
-          <t>Tiêu thụ hàng hóa đang chịu sự giám sát hải quan, trừ trường hợp quy định tại khoản 5 Điều này. Trường hợp vi phạm quy định tại điểm này mà tang vật vi phạm thuộc đối tượng không chịu thuế, miễn thuế, hàng hóa áp dụng thuế suất theo hạn ngạch thuế quan và không vi phạm quy định về chính sách quản lý hàng hóa xuất khẩu, nhập khẩu thì xử phạt theo quy định tại điểm g khoản 1 Điều 15 Nghị định này</t>
+          <t>Tiêu thụ hàng hóa đang chịu sự giám sát hải quan, trừ trường hợp quy định tại khoản 5 Điều này</t>
         </is>
       </c>
       <c r="H276" s="2" t="inlineStr">
@@ -22090,7 +22090,11 @@
           <t>Phạt 01 lần số tiền thuế trốn trong trường hợp không có tình tiết tăng nặng; Trường hợp có tình tiết tăng nặng thì mỗi tình tiết tăng nặng mức phạt tăng lên 0,2 lần nhưng không vượt quá 03 lần số tiền thuế trốn</t>
         </is>
       </c>
-      <c r="N293" s="2" t="inlineStr"/>
+      <c r="N293" s="2" t="inlineStr">
+        <is>
+          <t>Người nộp thuế có hành vi vi phạm quy định tại khoản 1 Điều này mà không bị truy cứu trách nhiệm hình sự thì bị phạt tiền như sau</t>
+        </is>
+      </c>
       <c r="O293" s="2" t="inlineStr">
         <is>
           <t>Buộc nộp đủ số tiền thuế trốn đối với hành vi vi phạm quy định tại Điều này</t>
@@ -22161,7 +22165,11 @@
           <t>Phạt 01 lần số tiền thuế trốn trong trường hợp không có tình tiết tăng nặng; Trường hợp có tình tiết tăng nặng thì mỗi tình tiết tăng nặng mức phạt tăng lên 0,2 lần nhưng không vượt quá 03 lần số tiền thuế trốn</t>
         </is>
       </c>
-      <c r="N294" s="2" t="inlineStr"/>
+      <c r="N294" s="2" t="inlineStr">
+        <is>
+          <t>Người nộp thuế có hành vi vi phạm quy định tại khoản 1 Điều này mà không bị truy cứu trách nhiệm hình sự thì bị phạt tiền như sau</t>
+        </is>
+      </c>
       <c r="O294" s="2" t="inlineStr">
         <is>
           <t>Buộc nộp đủ số tiền thuế trốn đối với hành vi vi phạm quy định tại Điều này</t>
@@ -22232,7 +22240,11 @@
           <t>Phạt 01 lần số tiền thuế trốn trong trường hợp không có tình tiết tăng nặng; Trường hợp có tình tiết tăng nặng thì mỗi tình tiết tăng nặng mức phạt tăng lên 0,2 lần nhưng không vượt quá 03 lần số tiền thuế trốn</t>
         </is>
       </c>
-      <c r="N295" s="2" t="inlineStr"/>
+      <c r="N295" s="2" t="inlineStr">
+        <is>
+          <t>Người nộp thuế có hành vi vi phạm quy định tại khoản 1 Điều này mà không bị truy cứu trách nhiệm hình sự thì bị phạt tiền như sau</t>
+        </is>
+      </c>
       <c r="O295" s="2" t="inlineStr">
         <is>
           <t>Buộc nộp đủ số tiền thuế trốn đối với hành vi vi phạm quy định tại Điều này</t>
@@ -22303,7 +22315,11 @@
           <t>Phạt 01 lần số tiền thuế trốn trong trường hợp không có tình tiết tăng nặng; Trường hợp có tình tiết tăng nặng thì mỗi tình tiết tăng nặng mức phạt tăng lên 0,2 lần nhưng không vượt quá 03 lần số tiền thuế trốn</t>
         </is>
       </c>
-      <c r="N296" s="2" t="inlineStr"/>
+      <c r="N296" s="2" t="inlineStr">
+        <is>
+          <t>Người nộp thuế có hành vi vi phạm quy định tại khoản 1 Điều này mà không bị truy cứu trách nhiệm hình sự thì bị phạt tiền như sau</t>
+        </is>
+      </c>
       <c r="O296" s="2" t="inlineStr">
         <is>
           <t>Buộc nộp đủ số tiền thuế trốn đối với hành vi vi phạm quy định tại Điều này</t>
@@ -22374,7 +22390,11 @@
           <t>Phạt 01 lần số tiền thuế trốn trong trường hợp không có tình tiết tăng nặng; Trường hợp có tình tiết tăng nặng thì mỗi tình tiết tăng nặng mức phạt tăng lên 0,2 lần nhưng không vượt quá 03 lần số tiền thuế trốn</t>
         </is>
       </c>
-      <c r="N297" s="2" t="inlineStr"/>
+      <c r="N297" s="2" t="inlineStr">
+        <is>
+          <t>Người nộp thuế có hành vi vi phạm quy định tại khoản 1 Điều này mà không bị truy cứu trách nhiệm hình sự thì bị phạt tiền như sau</t>
+        </is>
+      </c>
       <c r="O297" s="2" t="inlineStr">
         <is>
           <t>Buộc nộp đủ số tiền thuế trốn đối với hành vi vi phạm quy định tại Điều này</t>
@@ -22445,7 +22465,11 @@
           <t>Phạt 01 lần số tiền thuế trốn trong trường hợp không có tình tiết tăng nặng; Trường hợp có tình tiết tăng nặng thì mỗi tình tiết tăng nặng mức phạt tăng lên 0,2 lần nhưng không vượt quá 03 lần số tiền thuế trốn</t>
         </is>
       </c>
-      <c r="N298" s="2" t="inlineStr"/>
+      <c r="N298" s="2" t="inlineStr">
+        <is>
+          <t>Người nộp thuế có hành vi vi phạm quy định tại khoản 1 Điều này mà không bị truy cứu trách nhiệm hình sự thì bị phạt tiền như sau</t>
+        </is>
+      </c>
       <c r="O298" s="2" t="inlineStr">
         <is>
           <t>Buộc nộp đủ số tiền thuế trốn đối với hành vi vi phạm quy định tại Điều này</t>
@@ -22516,7 +22540,11 @@
           <t>Phạt 01 lần số tiền thuế trốn trong trường hợp không có tình tiết tăng nặng; Trường hợp có tình tiết tăng nặng thì mỗi tình tiết tăng nặng mức phạt tăng lên 0,2 lần nhưng không vượt quá 03 lần số tiền thuế trốn</t>
         </is>
       </c>
-      <c r="N299" s="2" t="inlineStr"/>
+      <c r="N299" s="2" t="inlineStr">
+        <is>
+          <t>Người nộp thuế có hành vi vi phạm quy định tại khoản 1 Điều này mà không bị truy cứu trách nhiệm hình sự thì bị phạt tiền như sau</t>
+        </is>
+      </c>
       <c r="O299" s="2" t="inlineStr">
         <is>
           <t>Buộc nộp đủ số tiền thuế trốn đối với hành vi vi phạm quy định tại Điều này</t>
@@ -22587,7 +22615,11 @@
           <t>Phạt 01 lần số tiền thuế trốn trong trường hợp không có tình tiết tăng nặng; Trường hợp có tình tiết tăng nặng thì mỗi tình tiết tăng nặng mức phạt tăng lên 0,2 lần nhưng không vượt quá 03 lần số tiền thuế trốn</t>
         </is>
       </c>
-      <c r="N300" s="2" t="inlineStr"/>
+      <c r="N300" s="2" t="inlineStr">
+        <is>
+          <t>Người nộp thuế có hành vi vi phạm quy định tại khoản 1 Điều này mà không bị truy cứu trách nhiệm hình sự thì bị phạt tiền như sau</t>
+        </is>
+      </c>
       <c r="O300" s="2" t="inlineStr">
         <is>
           <t>Buộc nộp đủ số tiền thuế trốn đối với hành vi vi phạm quy định tại Điều này</t>
@@ -22658,7 +22690,11 @@
           <t>Phạt 01 lần số tiền thuế trốn trong trường hợp không có tình tiết tăng nặng; Trường hợp có tình tiết tăng nặng thì mỗi tình tiết tăng nặng mức phạt tăng lên 0,2 lần nhưng không vượt quá 03 lần số tiền thuế trốn</t>
         </is>
       </c>
-      <c r="N301" s="2" t="inlineStr"/>
+      <c r="N301" s="2" t="inlineStr">
+        <is>
+          <t>Người nộp thuế có hành vi vi phạm quy định tại khoản 1 Điều này mà không bị truy cứu trách nhiệm hình sự thì bị phạt tiền như sau</t>
+        </is>
+      </c>
       <c r="O301" s="2" t="inlineStr">
         <is>
           <t>Buộc nộp đủ số tiền thuế trốn đối với hành vi vi phạm quy định tại Điều này</t>
@@ -22729,7 +22765,11 @@
           <t>Phạt 01 lần số tiền thuế trốn trong trường hợp không có tình tiết tăng nặng; Trường hợp có tình tiết tăng nặng thì mỗi tình tiết tăng nặng mức phạt tăng lên 0,2 lần nhưng không vượt quá 03 lần số tiền thuế trốn</t>
         </is>
       </c>
-      <c r="N302" s="2" t="inlineStr"/>
+      <c r="N302" s="2" t="inlineStr">
+        <is>
+          <t>Người nộp thuế có hành vi vi phạm quy định tại khoản 1 Điều này mà không bị truy cứu trách nhiệm hình sự thì bị phạt tiền như sau</t>
+        </is>
+      </c>
       <c r="O302" s="2" t="inlineStr">
         <is>
           <t>Buộc nộp đủ số tiền thuế trốn đối với hành vi vi phạm quy định tại Điều này</t>
@@ -22800,7 +22840,11 @@
           <t>Phạt 01 lần số tiền thuế trốn trong trường hợp không có tình tiết tăng nặng; Trường hợp có tình tiết tăng nặng thì mỗi tình tiết tăng nặng mức phạt tăng lên 0,2 lần nhưng không vượt quá 03 lần số tiền thuế trốn</t>
         </is>
       </c>
-      <c r="N303" s="2" t="inlineStr"/>
+      <c r="N303" s="2" t="inlineStr">
+        <is>
+          <t>Người nộp thuế có hành vi vi phạm quy định tại khoản 1 Điều này mà không bị truy cứu trách nhiệm hình sự thì bị phạt tiền như sau</t>
+        </is>
+      </c>
       <c r="O303" s="2" t="inlineStr">
         <is>
           <t>Buộc nộp đủ số tiền thuế trốn đối với hành vi vi phạm quy định tại Điều này</t>
@@ -24130,7 +24174,11 @@
           <t>Buộc tiêu hủy tang vật vi phạm hành chính là hàng hóa, vật phẩm gây hại cho sức khỏe con người, vật nuôi, cây trồng và môi trường, văn hóa phẩm có nội dung độc hại đối với hành vi vi phạm quy định tại Điều này | Buộc nộp lại số tiền bằng trị giá tang vật đã bị tiêu thụ, tẩu tán, tiêu hủy trái quy định của pháp luật đối với hành vi vi phạm quy định tại Điều này</t>
         </is>
       </c>
-      <c r="P319" s="2" t="inlineStr"/>
+      <c r="P319" s="2" t="inlineStr">
+        <is>
+          <t>Tịch thu tang vật vi phạm hành chính đối với hành vi vi phạm quy định tại Điều này, trừ tang vật vi phạm bị áp dụng biện pháp khắc phục hậu quả quy định tại điểm a khoản 3 Điều này</t>
+        </is>
+      </c>
       <c r="Q319" s="2" t="inlineStr">
         <is>
           <t>2026-07-01</t>
@@ -24209,7 +24257,11 @@
           <t>Buộc tiêu hủy tang vật vi phạm hành chính là hàng hóa, vật phẩm gây hại cho sức khỏe con người, vật nuôi, cây trồng và môi trường, văn hóa phẩm có nội dung độc hại đối với hành vi vi phạm quy định tại Điều này | Buộc nộp lại số tiền bằng trị giá tang vật đã bị tiêu thụ, tẩu tán, tiêu hủy trái quy định của pháp luật đối với hành vi vi phạm quy định tại Điều này</t>
         </is>
       </c>
-      <c r="P320" s="2" t="inlineStr"/>
+      <c r="P320" s="2" t="inlineStr">
+        <is>
+          <t>Tịch thu tang vật vi phạm hành chính đối với hành vi vi phạm quy định tại Điều này, trừ tang vật vi phạm bị áp dụng biện pháp khắc phục hậu quả quy định tại điểm a khoản 3 Điều này</t>
+        </is>
+      </c>
       <c r="Q320" s="2" t="inlineStr">
         <is>
           <t>2026-07-01</t>
@@ -24288,7 +24340,11 @@
           <t>Buộc tiêu hủy tang vật vi phạm hành chính là hàng hóa, vật phẩm gây hại cho sức khỏe con người, vật nuôi, cây trồng và môi trường, văn hóa phẩm có nội dung độc hại đối với hành vi vi phạm quy định tại Điều này | Buộc nộp lại số tiền bằng trị giá tang vật đã bị tiêu thụ, tẩu tán, tiêu hủy trái quy định của pháp luật đối với hành vi vi phạm quy định tại Điều này</t>
         </is>
       </c>
-      <c r="P321" s="2" t="inlineStr"/>
+      <c r="P321" s="2" t="inlineStr">
+        <is>
+          <t>Tịch thu tang vật vi phạm hành chính đối với hành vi vi phạm quy định tại Điều này, trừ tang vật vi phạm bị áp dụng biện pháp khắc phục hậu quả quy định tại điểm a khoản 3 Điều này</t>
+        </is>
+      </c>
       <c r="Q321" s="2" t="inlineStr">
         <is>
           <t>2026-07-01</t>
@@ -24367,7 +24423,11 @@
           <t>Buộc tiêu hủy tang vật vi phạm hành chính là hàng hóa, vật phẩm gây hại cho sức khỏe con người, vật nuôi, cây trồng và môi trường, văn hóa phẩm có nội dung độc hại đối với hành vi vi phạm quy định tại Điều này | Buộc nộp lại số tiền bằng trị giá tang vật đã bị tiêu thụ, tẩu tán, tiêu hủy trái quy định của pháp luật đối với hành vi vi phạm quy định tại Điều này</t>
         </is>
       </c>
-      <c r="P322" s="2" t="inlineStr"/>
+      <c r="P322" s="2" t="inlineStr">
+        <is>
+          <t>Tịch thu tang vật vi phạm hành chính đối với hành vi vi phạm quy định tại Điều này, trừ tang vật vi phạm bị áp dụng biện pháp khắc phục hậu quả quy định tại điểm a khoản 3 Điều này</t>
+        </is>
+      </c>
       <c r="Q322" s="2" t="inlineStr">
         <is>
           <t>2026-07-01</t>
@@ -24446,7 +24506,11 @@
           <t>Buộc tiêu hủy tang vật vi phạm hành chính là hàng hóa, vật phẩm gây hại cho sức khỏe con người, vật nuôi, cây trồng và môi trường, văn hóa phẩm có nội dung độc hại đối với hành vi vi phạm quy định tại Điều này | Buộc nộp lại số tiền bằng trị giá tang vật đã bị tiêu thụ, tẩu tán, tiêu hủy trái quy định của pháp luật đối với hành vi vi phạm quy định tại Điều này</t>
         </is>
       </c>
-      <c r="P323" s="2" t="inlineStr"/>
+      <c r="P323" s="2" t="inlineStr">
+        <is>
+          <t>Tịch thu tang vật vi phạm hành chính đối với hành vi vi phạm quy định tại Điều này, trừ tang vật vi phạm bị áp dụng biện pháp khắc phục hậu quả quy định tại điểm a khoản 3 Điều này</t>
+        </is>
+      </c>
       <c r="Q323" s="2" t="inlineStr">
         <is>
           <t>2026-07-01</t>
@@ -32718,7 +32782,7 @@
       </c>
       <c r="G432" s="4" t="inlineStr">
         <is>
-          <t>Vi phạm quy định tại khoản 1 Điều này mà người khai hải quan tự phát hiện và khai bổ sung hồ sơ thuế sau khi có kết luận kiểm tra, thanh tra. Vi phạm quy định tại các điểm b, c, d khoản này mà cá nhân, tổ chức vi phạm không tự nguyện khắc phục hậu quả bằng cách nộp đủ số tiền thuế phải nộp trước thời điểm lập biên bản vi phạm hành chính thì xử phạt theo quy định tại điểm c khoản 1 Điều 14 Nghị định này</t>
+          <t>Vi phạm quy định tại khoản 1 Điều này mà người khai hải quan tự phát hiện và khai bổ sung hồ sơ thuế sau khi có kết luận kiểm tra, thanh tra</t>
         </is>
       </c>
       <c r="H432" s="4" t="inlineStr">
@@ -36806,7 +36870,7 @@
       </c>
       <c r="G484" s="4" t="inlineStr">
         <is>
-          <t>Tiêu thụ hàng hóa đang chịu sự giám sát hải quan, trừ trường hợp quy định tại khoản 5 Điều này. Trường hợp vi phạm quy định tại điểm này mà tang vật vi phạm thuộc đối tượng không chịu thuế, miễn thuế, xét miễn thuế, hàng hóa áp dụng thuế suất theo hạn ngạch thuế quan và không vi phạm quy định về chính sách quản lý hàng hóa xuất khẩu, nhập khẩu thì xử phạt theo quy định tại điểm g khoản 1 Điều 14 Nghị định này</t>
+          <t>Tiêu thụ hàng hóa đang chịu sự giám sát hải quan, trừ trường hợp quy định tại khoản 5 Điều này</t>
         </is>
       </c>
       <c r="H484" s="4" t="inlineStr">
@@ -38154,7 +38218,11 @@
           <t>Phạt 01 lần số tiền thuế trốn trong trường hợp không có tình tiết tăng nặng; Trường hợp có tình tiết tăng nặng thì mỗi tình tiết tăng nặng mức phạt tăng lên 0,2 lần nhưng không vượt quá 03 lần số tiền thuế trốn</t>
         </is>
       </c>
-      <c r="N501" s="4" t="inlineStr"/>
+      <c r="N501" s="4" t="inlineStr">
+        <is>
+          <t>Người nộp thuế có hành vi vi phạm quy định tại khoản 1 Điều này mà không bị truy cứu trách nhiệm hình sự thì bị phạt tiền như sau</t>
+        </is>
+      </c>
       <c r="O501" s="4" t="inlineStr">
         <is>
           <t>Buộc nộp đủ số tiền thuế trốn đối với hành vi vi phạm quy định tại Điều này</t>
@@ -38229,7 +38297,11 @@
           <t>Phạt 01 lần số tiền thuế trốn trong trường hợp không có tình tiết tăng nặng; Trường hợp có tình tiết tăng nặng thì mỗi tình tiết tăng nặng mức phạt tăng lên 0,2 lần nhưng không vượt quá 03 lần số tiền thuế trốn</t>
         </is>
       </c>
-      <c r="N502" s="4" t="inlineStr"/>
+      <c r="N502" s="4" t="inlineStr">
+        <is>
+          <t>Người nộp thuế có hành vi vi phạm quy định tại khoản 1 Điều này mà không bị truy cứu trách nhiệm hình sự thì bị phạt tiền như sau</t>
+        </is>
+      </c>
       <c r="O502" s="4" t="inlineStr">
         <is>
           <t>Buộc nộp đủ số tiền thuế trốn đối với hành vi vi phạm quy định tại Điều này</t>
@@ -38304,7 +38376,11 @@
           <t>Phạt 01 lần số tiền thuế trốn trong trường hợp không có tình tiết tăng nặng; Trường hợp có tình tiết tăng nặng thì mỗi tình tiết tăng nặng mức phạt tăng lên 0,2 lần nhưng không vượt quá 03 lần số tiền thuế trốn</t>
         </is>
       </c>
-      <c r="N503" s="4" t="inlineStr"/>
+      <c r="N503" s="4" t="inlineStr">
+        <is>
+          <t>Người nộp thuế có hành vi vi phạm quy định tại khoản 1 Điều này mà không bị truy cứu trách nhiệm hình sự thì bị phạt tiền như sau</t>
+        </is>
+      </c>
       <c r="O503" s="4" t="inlineStr">
         <is>
           <t>Buộc nộp đủ số tiền thuế trốn đối với hành vi vi phạm quy định tại Điều này</t>
@@ -38379,7 +38455,11 @@
           <t>Phạt 01 lần số tiền thuế trốn trong trường hợp không có tình tiết tăng nặng; Trường hợp có tình tiết tăng nặng thì mỗi tình tiết tăng nặng mức phạt tăng lên 0,2 lần nhưng không vượt quá 03 lần số tiền thuế trốn</t>
         </is>
       </c>
-      <c r="N504" s="4" t="inlineStr"/>
+      <c r="N504" s="4" t="inlineStr">
+        <is>
+          <t>Người nộp thuế có hành vi vi phạm quy định tại khoản 1 Điều này mà không bị truy cứu trách nhiệm hình sự thì bị phạt tiền như sau</t>
+        </is>
+      </c>
       <c r="O504" s="4" t="inlineStr">
         <is>
           <t>Buộc nộp đủ số tiền thuế trốn đối với hành vi vi phạm quy định tại Điều này</t>
@@ -38454,7 +38534,11 @@
           <t>Phạt 01 lần số tiền thuế trốn trong trường hợp không có tình tiết tăng nặng; Trường hợp có tình tiết tăng nặng thì mỗi tình tiết tăng nặng mức phạt tăng lên 0,2 lần nhưng không vượt quá 03 lần số tiền thuế trốn</t>
         </is>
       </c>
-      <c r="N505" s="4" t="inlineStr"/>
+      <c r="N505" s="4" t="inlineStr">
+        <is>
+          <t>Người nộp thuế có hành vi vi phạm quy định tại khoản 1 Điều này mà không bị truy cứu trách nhiệm hình sự thì bị phạt tiền như sau</t>
+        </is>
+      </c>
       <c r="O505" s="4" t="inlineStr">
         <is>
           <t>Buộc nộp đủ số tiền thuế trốn đối với hành vi vi phạm quy định tại Điều này</t>
@@ -38529,7 +38613,11 @@
           <t>Phạt 01 lần số tiền thuế trốn trong trường hợp không có tình tiết tăng nặng; Trường hợp có tình tiết tăng nặng thì mỗi tình tiết tăng nặng mức phạt tăng lên 0,2 lần nhưng không vượt quá 03 lần số tiền thuế trốn</t>
         </is>
       </c>
-      <c r="N506" s="4" t="inlineStr"/>
+      <c r="N506" s="4" t="inlineStr">
+        <is>
+          <t>Người nộp thuế có hành vi vi phạm quy định tại khoản 1 Điều này mà không bị truy cứu trách nhiệm hình sự thì bị phạt tiền như sau</t>
+        </is>
+      </c>
       <c r="O506" s="4" t="inlineStr">
         <is>
           <t>Buộc nộp đủ số tiền thuế trốn đối với hành vi vi phạm quy định tại Điều này</t>
@@ -38604,7 +38692,11 @@
           <t>Phạt 01 lần số tiền thuế trốn trong trường hợp không có tình tiết tăng nặng; Trường hợp có tình tiết tăng nặng thì mỗi tình tiết tăng nặng mức phạt tăng lên 0,2 lần nhưng không vượt quá 03 lần số tiền thuế trốn</t>
         </is>
       </c>
-      <c r="N507" s="4" t="inlineStr"/>
+      <c r="N507" s="4" t="inlineStr">
+        <is>
+          <t>Người nộp thuế có hành vi vi phạm quy định tại khoản 1 Điều này mà không bị truy cứu trách nhiệm hình sự thì bị phạt tiền như sau</t>
+        </is>
+      </c>
       <c r="O507" s="4" t="inlineStr">
         <is>
           <t>Buộc nộp đủ số tiền thuế trốn đối với hành vi vi phạm quy định tại Điều này</t>
@@ -38679,7 +38771,11 @@
           <t>Phạt 01 lần số tiền thuế trốn trong trường hợp không có tình tiết tăng nặng; Trường hợp có tình tiết tăng nặng thì mỗi tình tiết tăng nặng mức phạt tăng lên 0,2 lần nhưng không vượt quá 03 lần số tiền thuế trốn</t>
         </is>
       </c>
-      <c r="N508" s="4" t="inlineStr"/>
+      <c r="N508" s="4" t="inlineStr">
+        <is>
+          <t>Người nộp thuế có hành vi vi phạm quy định tại khoản 1 Điều này mà không bị truy cứu trách nhiệm hình sự thì bị phạt tiền như sau</t>
+        </is>
+      </c>
       <c r="O508" s="4" t="inlineStr">
         <is>
           <t>Buộc nộp đủ số tiền thuế trốn đối với hành vi vi phạm quy định tại Điều này</t>
@@ -38754,7 +38850,11 @@
           <t>Phạt 01 lần số tiền thuế trốn trong trường hợp không có tình tiết tăng nặng; Trường hợp có tình tiết tăng nặng thì mỗi tình tiết tăng nặng mức phạt tăng lên 0,2 lần nhưng không vượt quá 03 lần số tiền thuế trốn</t>
         </is>
       </c>
-      <c r="N509" s="4" t="inlineStr"/>
+      <c r="N509" s="4" t="inlineStr">
+        <is>
+          <t>Người nộp thuế có hành vi vi phạm quy định tại khoản 1 Điều này mà không bị truy cứu trách nhiệm hình sự thì bị phạt tiền như sau</t>
+        </is>
+      </c>
       <c r="O509" s="4" t="inlineStr">
         <is>
           <t>Buộc nộp đủ số tiền thuế trốn đối với hành vi vi phạm quy định tại Điều này</t>
@@ -38829,7 +38929,11 @@
           <t>Phạt 01 lần số tiền thuế trốn trong trường hợp không có tình tiết tăng nặng; Trường hợp có tình tiết tăng nặng thì mỗi tình tiết tăng nặng mức phạt tăng lên 0,2 lần nhưng không vượt quá 03 lần số tiền thuế trốn</t>
         </is>
       </c>
-      <c r="N510" s="4" t="inlineStr"/>
+      <c r="N510" s="4" t="inlineStr">
+        <is>
+          <t>Người nộp thuế có hành vi vi phạm quy định tại khoản 1 Điều này mà không bị truy cứu trách nhiệm hình sự thì bị phạt tiền như sau</t>
+        </is>
+      </c>
       <c r="O510" s="4" t="inlineStr">
         <is>
           <t>Buộc nộp đủ số tiền thuế trốn đối với hành vi vi phạm quy định tại Điều này</t>
@@ -38904,7 +39008,11 @@
           <t>Phạt 01 lần số tiền thuế trốn trong trường hợp không có tình tiết tăng nặng; Trường hợp có tình tiết tăng nặng thì mỗi tình tiết tăng nặng mức phạt tăng lên 0,2 lần nhưng không vượt quá 03 lần số tiền thuế trốn</t>
         </is>
       </c>
-      <c r="N511" s="4" t="inlineStr"/>
+      <c r="N511" s="4" t="inlineStr">
+        <is>
+          <t>Người nộp thuế có hành vi vi phạm quy định tại khoản 1 Điều này mà không bị truy cứu trách nhiệm hình sự thì bị phạt tiền như sau</t>
+        </is>
+      </c>
       <c r="O511" s="4" t="inlineStr">
         <is>
           <t>Buộc nộp đủ số tiền thuế trốn đối với hành vi vi phạm quy định tại Điều này</t>
@@ -39950,7 +40058,11 @@
           <t>Buộc tiêu hủy tang vật vi phạm hành chính là hàng hóa, vật phẩm gây hại cho sức khỏe con người, vật nuôi, cây trồng và môi trường, văn hóa phẩm có nội dung độc hại đối với hành vi vi phạm quy định tại Điều này | Buộc nộp lại số tiền bằng trị giá tang vật đã bị tiêu thụ, tẩu tán, tiêu hủy trái quy định của pháp luật đối với hành vi vi phạm quy định tại Điều này</t>
         </is>
       </c>
-      <c r="P523" s="4" t="inlineStr"/>
+      <c r="P523" s="4" t="inlineStr">
+        <is>
+          <t>Tịch thu tang vật vi phạm hành chính đối với hành vi vi phạm quy định tại Điều này, trừ tang vật vi phạm bị áp dụng biện pháp khắc phục hậu quả quy định tại điểm a khoản 3 Điều này</t>
+        </is>
+      </c>
       <c r="Q523" s="4" t="inlineStr">
         <is>
           <t>2020-12-10</t>
@@ -40033,7 +40145,11 @@
           <t>Buộc tiêu hủy tang vật vi phạm hành chính là hàng hóa, vật phẩm gây hại cho sức khỏe con người, vật nuôi, cây trồng và môi trường, văn hóa phẩm có nội dung độc hại đối với hành vi vi phạm quy định tại Điều này | Buộc nộp lại số tiền bằng trị giá tang vật đã bị tiêu thụ, tẩu tán, tiêu hủy trái quy định của pháp luật đối với hành vi vi phạm quy định tại Điều này</t>
         </is>
       </c>
-      <c r="P524" s="4" t="inlineStr"/>
+      <c r="P524" s="4" t="inlineStr">
+        <is>
+          <t>Tịch thu tang vật vi phạm hành chính đối với hành vi vi phạm quy định tại Điều này, trừ tang vật vi phạm bị áp dụng biện pháp khắc phục hậu quả quy định tại điểm a khoản 3 Điều này</t>
+        </is>
+      </c>
       <c r="Q524" s="4" t="inlineStr">
         <is>
           <t>2020-12-10</t>
@@ -40116,7 +40232,11 @@
           <t>Buộc tiêu hủy tang vật vi phạm hành chính là hàng hóa, vật phẩm gây hại cho sức khỏe con người, vật nuôi, cây trồng và môi trường, văn hóa phẩm có nội dung độc hại đối với hành vi vi phạm quy định tại Điều này | Buộc nộp lại số tiền bằng trị giá tang vật đã bị tiêu thụ, tẩu tán, tiêu hủy trái quy định của pháp luật đối với hành vi vi phạm quy định tại Điều này</t>
         </is>
       </c>
-      <c r="P525" s="4" t="inlineStr"/>
+      <c r="P525" s="4" t="inlineStr">
+        <is>
+          <t>Tịch thu tang vật vi phạm hành chính đối với hành vi vi phạm quy định tại Điều này, trừ tang vật vi phạm bị áp dụng biện pháp khắc phục hậu quả quy định tại điểm a khoản 3 Điều này</t>
+        </is>
+      </c>
       <c r="Q525" s="4" t="inlineStr">
         <is>
           <t>2020-12-10</t>
@@ -40199,7 +40319,11 @@
           <t>Buộc tiêu hủy tang vật vi phạm hành chính là hàng hóa, vật phẩm gây hại cho sức khỏe con người, vật nuôi, cây trồng và môi trường, văn hóa phẩm có nội dung độc hại đối với hành vi vi phạm quy định tại Điều này | Buộc nộp lại số tiền bằng trị giá tang vật đã bị tiêu thụ, tẩu tán, tiêu hủy trái quy định của pháp luật đối với hành vi vi phạm quy định tại Điều này</t>
         </is>
       </c>
-      <c r="P526" s="4" t="inlineStr"/>
+      <c r="P526" s="4" t="inlineStr">
+        <is>
+          <t>Tịch thu tang vật vi phạm hành chính đối với hành vi vi phạm quy định tại Điều này, trừ tang vật vi phạm bị áp dụng biện pháp khắc phục hậu quả quy định tại điểm a khoản 3 Điều này</t>
+        </is>
+      </c>
       <c r="Q526" s="4" t="inlineStr">
         <is>
           <t>2020-12-10</t>
@@ -40282,7 +40406,11 @@
           <t>Buộc tiêu hủy tang vật vi phạm hành chính là hàng hóa, vật phẩm gây hại cho sức khỏe con người, vật nuôi, cây trồng và môi trường, văn hóa phẩm có nội dung độc hại đối với hành vi vi phạm quy định tại Điều này | Buộc nộp lại số tiền bằng trị giá tang vật đã bị tiêu thụ, tẩu tán, tiêu hủy trái quy định của pháp luật đối với hành vi vi phạm quy định tại Điều này</t>
         </is>
       </c>
-      <c r="P527" s="4" t="inlineStr"/>
+      <c r="P527" s="4" t="inlineStr">
+        <is>
+          <t>Tịch thu tang vật vi phạm hành chính đối với hành vi vi phạm quy định tại Điều này, trừ tang vật vi phạm bị áp dụng biện pháp khắc phục hậu quả quy định tại điểm a khoản 3 Điều này</t>
+        </is>
+      </c>
       <c r="Q527" s="4" t="inlineStr">
         <is>
           <t>2020-12-10</t>
@@ -44096,18 +44224,22 @@
       </c>
       <c r="H575" s="4" t="inlineStr">
         <is>
-          <t>Phạt theo tỷ lệ</t>
-        </is>
-      </c>
-      <c r="I575" s="5" t="n"/>
-      <c r="J575" s="5" t="n"/>
-      <c r="K575" s="5" t="n"/>
-      <c r="L575" s="5" t="n"/>
-      <c r="M575" s="4" t="inlineStr">
-        <is>
-          <t>Phạt tiền từ 1.000.000 đến 3.000.000 đồng</t>
-        </is>
-      </c>
+          <t>Phạt tiền (khung)</t>
+        </is>
+      </c>
+      <c r="I575" s="5" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="J575" s="5" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="K575" s="5" t="n">
+        <v>500000</v>
+      </c>
+      <c r="L575" s="5" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="M575" s="4" t="inlineStr"/>
       <c r="N575" s="4" t="inlineStr"/>
       <c r="O575" s="4" t="inlineStr"/>
       <c r="P575" s="4" t="inlineStr"/>
@@ -44167,18 +44299,22 @@
       </c>
       <c r="H576" s="4" t="inlineStr">
         <is>
-          <t>Phạt theo tỷ lệ</t>
-        </is>
-      </c>
-      <c r="I576" s="5" t="n"/>
-      <c r="J576" s="5" t="n"/>
-      <c r="K576" s="5" t="n"/>
-      <c r="L576" s="5" t="n"/>
-      <c r="M576" s="4" t="inlineStr">
-        <is>
-          <t>Phạt tiền từ 1.000.000 đến 3.000.000 đồng</t>
-        </is>
-      </c>
+          <t>Phạt tiền (khung)</t>
+        </is>
+      </c>
+      <c r="I576" s="5" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="J576" s="5" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="K576" s="5" t="n">
+        <v>500000</v>
+      </c>
+      <c r="L576" s="5" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="M576" s="4" t="inlineStr"/>
       <c r="N576" s="4" t="inlineStr"/>
       <c r="O576" s="4" t="inlineStr"/>
       <c r="P576" s="4" t="inlineStr"/>
@@ -44855,7 +44991,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -45075,7 +45211,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Hóa đơn: 01 năm với hành vi trước 01/01/2022; 02 năm từ 01/01/2022 (Điều 1.1 NĐ102/2021). Danh sách hành vi 'đang thực hiện' được NĐ310 sửa tại Điều 8.1. Thủ tục thuế: 02 năm. Trốn thuế (chưa đến mức hình sự) và khai sai dẫn đến thiếu thuế: 05 năm.</t>
+          <t>Hóa đơn: 01 năm với hành vi trước 01/01/2022; 02 năm từ 01/01/2022 (Điều 1.1 NĐ102/2021). Danh sách hành vi 'đang thực hiện' được NĐ310 sửa tại Điều 8.1. Thủ tục thuế: 02 năm. Trốn thuế (chưa đến mức hình sự) và khai sai dẫn đến thiếu thuế: 05 năm. Cách chia 01 năm / 02 năm theo ngày hành vi là cách hiểu của bảng (NĐ102 Điều 7.2 chỉ cho áp dụng quy định mới đối với hành vi cũ khi nhẹ hơn). NĐ102 Điều 6.1.b bãi bỏ khoản 3 Điều 8 NĐ125 (quy định riêng về hồ sơ do cơ quan tố tụng hình sự chuyển đến).</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -45092,7 +45228,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>NĐ125 hiệu lực 05/12/2020. NĐ102/2021 (sửa NĐ125) hiệu lực 01/01/2022. NĐ310 hiệu lực 16/01/2026. Hành vi đã kết thúc trước 16/01/2026: áp dụng văn bản có hiệu lực tại thời điểm vi phạm. Hành vi đang thực hiện trước ngày này và bị phát hiện sau ngày này: áp dụng NĐ310.</t>
+          <t>NĐ125 hiệu lực 05/12/2020. NĐ102/2021 (sửa NĐ125) hiệu lực 01/01/2022. NĐ310 hiệu lực 16/01/2026. Hành vi đã kết thúc trước 16/01/2026: áp dụng văn bản có hiệu lực tại thời điểm vi phạm. Hành vi đang thực hiện trước ngày này và bị phát hiện sau ngày này: áp dụng NĐ310. Với NĐ102/2021 (Điều 7): hành vi xảy ra trước 01/01/2022 bị phát hiện sau đó thì áp dụng NĐ102 nếu NĐ102 không quy định trách nhiệm pháp lý hoặc quy định nhẹ hơn; quyết định xử phạt đã ban hành mà còn khiếu nại: giải quyết theo nghị định có hiệu lực tại thời điểm hành vi; hồ sơ đề nghị miễn tiền phạt tiếp nhận trước 01/01/2022: theo NĐ125 gốc.</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -45104,134 +45240,151 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Chưa nằm trong bảng này</t>
+          <t>Miễn, giảm tiền phạt (thuế, hóa đơn)</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Tiền chậm nộp tiền thuế (tỷ lệ theo Luật Quản lý thuế - văn bản chưa được cung cấp, bảng này không nêu tỷ lệ); truy thu thuế; vi phạm hải quan, bảo hiểm xã hội, lao động; các nghị định xử phạt chuyên ngành khác.</t>
+          <t>Điều 43 NĐ125 do NĐ102 thay thế (từ 01/01/2022): thực hiện theo Điều 77 Luật Xử lý vi phạm hành chính. Mức miễn, giảm tối đa bằng số tiền phạt trong quyết định xử phạt và không quá giá trị tài sản, hàng hóa bị thiệt hại sau khi trừ giá trị được bảo hiểm, bồi thường (bất khả kháng cần hồ sơ chứng minh thiệt hại). Không miễn, giảm nếu đã thi hành xong quyết định xử phạt. Được miễn, giảm tiền phạt thì được miễn, giảm tiền chậm nộp tiền phạt tương ứng. Miễn, giảm không đúng bị hủy hoặc điều chỉnh, thu lại tiền phạt và tính tiền chậm nộp.</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Điều 43 NĐ125 (thay thế bởi Điều 1.6 NĐ102/2021)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Hải quan: văn bản áp dụng và quan hệ với NĐ125</t>
+          <t>Chưa nằm trong bảng này</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>NĐ 169/2026/NĐ-CP (hiệu lực 01/07/2026) thay thế NĐ 128/2020/NĐ-CP và Điều 2 NĐ 102/2021/NĐ-CP (Điều 38 NĐ169). NĐ125 KHÔNG áp dụng cho vi phạm về thuế đối với hàng xuất nhập khẩu do cơ quan hải quan quản lý thu (Điều 1.1 NĐ125): thuế xuất nhập khẩu dùng nghị định hải quan, không cộng với Điều 16, 17 NĐ125. NĐ 127/2013 (VBHN 10/2016) áp dụng cho hành vi trước 10/12/2020, nhưng thời hiệu tối đa 05 năm (Điều 3 VBHN) nên đã hết từ 10/12/2025; bảng này không gồm văn bản đó.</t>
+          <t>Tiền chậm nộp tiền thuế (tỷ lệ theo Luật Quản lý thuế - văn bản chưa được cung cấp, bảng này không nêu tỷ lệ); truy thu thuế; vi phạm hải quan, bảo hiểm xã hội, lao động; các nghị định xử phạt chuyên ngành khác.</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Điều 38 NĐ169; Điều 1.1 NĐ125; Điều 35 NĐ128; Điều 3 VBHN 10/2016</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Hải quan: chuyển tiếp 01/07/2026</t>
+          <t>Hải quan: văn bản áp dụng và quan hệ với NĐ125</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Hành vi xảy ra và kết thúc trước 01/07/2026 nhưng bị phát hiện hoặc xem xét xử phạt từ 01/07/2026: áp dụng NĐ169 nếu NĐ169 không quy định trách nhiệm pháp lý hoặc quy định nhẹ hơn; nếu NĐ169 nặng hơn thì áp dụng NĐ128 (+ NĐ102). Bảng chọn bản theo ngày hành vi kết thúc; với hành vi trước 01/07/2026 nên xem cả hai bản và chọn bản nhẹ hơn.</t>
+          <t>NĐ 169/2026/NĐ-CP (hiệu lực 01/07/2026) thay thế NĐ 128/2020/NĐ-CP và Điều 2 NĐ 102/2021/NĐ-CP (Điều 38 NĐ169). NĐ125 KHÔNG áp dụng cho vi phạm về thuế đối với hàng xuất nhập khẩu do cơ quan hải quan quản lý thu (Điều 1.1 NĐ125): thuế xuất nhập khẩu dùng nghị định hải quan, không cộng với Điều 16, 17 NĐ125. NĐ 127/2013 (VBHN 10/2016) áp dụng cho hành vi trước 10/12/2020, nhưng thời hiệu tối đa 05 năm (Điều 3 VBHN) nên đã hết từ 10/12/2025; bảng này không gồm văn bản đó.</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Điều 39 NĐ169; Điều 36 NĐ128; Điều 7 NĐ102/2021</t>
+          <t>Điều 38 NĐ169; Điều 1.1 NĐ125; Điều 35 NĐ128; Điều 3 VBHN 10/2016</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Hải quan: mức phạt cá nhân so với tổ chức</t>
+          <t>Hải quan: chuyển tiếp 01/07/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Khung tiền ở Chương II là mức cho TỔ CHỨC; cá nhân bằng 1/2, TRỪ: (1) hành vi xuất cảnh, nhập cảnh (Điều 11 NĐ169; Điều 10 NĐ128) - khung đã là mức của cá nhân; (2) hành vi về quản lý thuế (Điều 10, 15 NĐ169; Điều 9, 14 NĐ128) - cùng mức cho cá nhân và tổ chức. Hộ kinh doanh, hộ gia đình, cộng đồng dân cư áp dụng như cá nhân.</t>
+          <t>Hành vi xảy ra và kết thúc trước 01/07/2026 nhưng bị phát hiện hoặc xem xét xử phạt từ 01/07/2026: áp dụng NĐ169 nếu NĐ169 không quy định trách nhiệm pháp lý hoặc quy định nhẹ hơn; nếu NĐ169 nặng hơn thì áp dụng NĐ128 (+ NĐ102). Bảng chọn bản theo ngày hành vi kết thúc; với hành vi trước 01/07/2026 nên xem cả hai bản và chọn bản nhẹ hơn.</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Điều 6.3 NĐ169; Điều 5.3 NĐ128</t>
+          <t>Điều 39 NĐ169; Điều 36 NĐ128; Điều 7 NĐ102/2021</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Hải quan: mức cụ thể trong khung</t>
+          <t>Hải quan: mức phạt cá nhân so với tổ chức</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Mức phạt cụ thể = mức trung bình của khung. NĐ169 (từ 01/07/2026): 1 tình tiết giảm nhẹ giảm 10%, từ 2 tình tiết giảm nhẹ áp mức tối thiểu; 1 tình tiết tăng nặng tăng 10%, từ 2 tình tiết tăng nặng áp mức tối đa; một tình tiết giảm nhẹ bù trừ một tình tiết tăng nặng. Áp dụng cho Điều 8, 9, 11-14, 16-25 và khoản 1, 2, 4 Điều 26. NĐ128 (+ NĐ102 từ 01/01/2022): mỗi tình tiết ±10% mức trung bình, không vượt khung; áp dụng cho Điều 7, 8, 10-13, 15-24 và khoản 1, 3, 4 Điều 25. Tình tiết giảm nhẹ riêng của hải quan: tang vật có trị giá không quá 50% mức phạt tối thiểu của khung.</t>
+          <t>Khung tiền ở Chương II là mức cho TỔ CHỨC; cá nhân bằng 1/2, TRỪ: (1) hành vi xuất cảnh, nhập cảnh (Điều 11 NĐ169; Điều 10 NĐ128) - khung đã là mức của cá nhân; (2) hành vi về quản lý thuế (Điều 10, 15 NĐ169; Điều 9, 14 NĐ128) - cùng mức cho cá nhân và tổ chức. Hộ kinh doanh, hộ gia đình, cộng đồng dân cư áp dụng như cá nhân.</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Điều 4, Điều 6.3.đ, e NĐ169; Điều 3, Điều 5.3.đ, e NĐ128 (NĐ102/2021 Điều 2.3)</t>
+          <t>Điều 6.3 NĐ169; Điều 5.3 NĐ128</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Hải quan: trốn thuế và khai sai thuế</t>
+          <t>Hải quan: mức cụ thể trong khung</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Trốn thuế (Điều 15 NĐ169; Điều 14 NĐ128): phạt 01 lần số thuế trốn; mỗi tình tiết tăng nặng +0,2 lần, tối đa 03 lần (khác Điều 17 NĐ125). Khai sai dẫn đến thiếu thuế (Điều 10 NĐ169; Điều 9 NĐ128): phạt 10% số thuế khai thiếu nếu tự phát hiện, khai bổ sung muộn; 20% nếu hải quan phát hiện; chỉ xử phạt khi số thuế chênh lệch từ 500.000 đ/tờ khai (cá nhân), 2.000.000 đ/tờ khai (tổ chức). Không xử phạt nếu khai bổ sung trong hạn (60 ngày kể từ ngày thông quan và trước quyết định kiểm tra, thanh tra) - Điều 7.2.a NĐ169.</t>
+          <t>Mức phạt cụ thể = mức trung bình của khung. NĐ169 (từ 01/07/2026): 1 tình tiết giảm nhẹ giảm 10%, từ 2 tình tiết giảm nhẹ áp mức tối thiểu; 1 tình tiết tăng nặng tăng 10%, từ 2 tình tiết tăng nặng áp mức tối đa; một tình tiết giảm nhẹ bù trừ một tình tiết tăng nặng. Áp dụng cho Điều 8, 9, 11-14, 16-25 và khoản 1, 2, 4 Điều 26. NĐ128 (+ NĐ102 từ 01/01/2022): mỗi tình tiết ±10% mức trung bình, không vượt khung; áp dụng cho Điều 7, 8, 10-13, 15-24 và khoản 1, 3, 4 Điều 25. Tình tiết giảm nhẹ riêng của hải quan: tang vật có trị giá không quá 50% mức phạt tối thiểu của khung.</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Điều 10, 15, 7.2.a NĐ169; Điều 9, 14 NĐ128</t>
+          <t>Điều 4, Điều 6.3.đ, e NĐ169; Điều 3, Điều 5.3.đ, e NĐ128 (NĐ102/2021 Điều 2.3)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Hải quan: thời hiệu</t>
+          <t>Hải quan: trốn thuế và khai sai thuế</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Thuế (trốn thuế chưa đến mức hình sự, khai sai dẫn đến thiếu thuế): 05 năm. Hành vi khác: 02 năm. Quá thời hiệu vẫn phải nộp đủ thuế thiếu, thuế trốn và tiền chậm nộp trong 10 năm trở về trước kể từ ngày phát hiện. Hồ sơ do cơ quan tố tụng chuyển đến: thời hiệu kéo dài thêm 01 năm (NĐ169).</t>
+          <t>Trốn thuế (Điều 15 NĐ169; Điều 14 NĐ128): phạt 01 lần số thuế trốn; mỗi tình tiết tăng nặng +0,2 lần, tối đa 03 lần (khác Điều 17 NĐ125). Khai sai dẫn đến thiếu thuế (Điều 10 NĐ169; Điều 9 NĐ128): phạt 10% số thuế khai thiếu nếu tự phát hiện, khai bổ sung muộn; 20% nếu hải quan phát hiện; chỉ xử phạt khi số thuế chênh lệch từ 500.000 đ/tờ khai (cá nhân), 2.000.000 đ/tờ khai (tổ chức). Không xử phạt nếu khai bổ sung trong hạn (60 ngày kể từ ngày thông quan và trước quyết định kiểm tra, thanh tra) - Điều 7.2.a NĐ169.</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Điều 5 NĐ169; Điều 4 NĐ128</t>
+          <t>Điều 10, 15, 7.2.a NĐ169; Điều 9, 14 NĐ128</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>Hải quan: thời hiệu</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Thuế (trốn thuế chưa đến mức hình sự, khai sai dẫn đến thiếu thuế): 05 năm. Hành vi khác: 02 năm. Quá thời hiệu vẫn phải nộp đủ thuế thiếu, thuế trốn và tiền chậm nộp trong 10 năm trở về trước kể từ ngày phát hiện. Hồ sơ do cơ quan tố tụng chuyển đến: thời hiệu kéo dài thêm 01 năm (NĐ169).</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Điều 5 NĐ169; Điều 4 NĐ128</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
           <t>Hải quan: vi phạm nhiều lần, cảnh cáo, hình sự</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>Vi phạm nhiều lần: xử phạt từng hành vi, trừ một số hành vi trên nhiều tờ khai/chứng từ được phát hiện cùng lúc thì phạt một lần và áp dụng tình tiết tăng nặng (Điều 3.1 NĐ169; Điều 2a NĐ128). Cảnh cáo chỉ áp dụng cho cá nhân từ 14 đến dưới 16 tuổi. Hành vi đến mức truy cứu trách nhiệm hình sự không thuộc bảng này (Điều 3.3 NĐ169: ngưỡng 100 triệu đồng với cá nhân, 200 triệu đồng với tổ chức theo trị giá tang vật hoặc số thuế trốn).</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
         <is>
           <t>Điều 3, Điều 6.2 NĐ169; Điều 2a, Điều 5.2 NĐ128</t>
         </is>
@@ -45248,7 +45401,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -45464,7 +45617,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Khoản 4: Vận chuyển ngà voi, sừng tê giác thuộc loại cấm xuất khẩu, cấm nhập khẩu bị xử phạt về hành vi “Vận chuyển lâm sản trái pháp luật” quy định tại Điều 25 Nghị định số 146/2026/NĐ-CP ngày 06 tháng 5 năm 2026 của Chính phủ quy định xử phạt vi phạm hành chính trong lĩnh vực lâm nghiệp; xuất khẩu, nhập khẩu ngà voi, sừng tê giác thuộc loại cấm xuất khẩu, cấm nhập khẩu bị xử phạt về hành vi “tàng trữ, mua bán, xuất khẩu, nhập khẩu, chế biến lâm sản trái pháp luật” quy định tại Điều 26 Nghị định số</t>
+          <t>Khoản 4: Vận chuyển ngà voi, sừng tê giác thuộc loại cấm xuất khẩu, cấm nhập khẩu bị xử phạt về hành vi “Vận chuyển lâm sản trái pháp luật” quy định tại Điều 25 Nghị định số 146/2026/NĐ-CP ngày 06 tháng 5 năm 2026 của Chính phủ quy định xử phạt vi phạm hành chính trong lĩnh vực lâm nghiệp; xuất khẩu, nhập khẩu ngà voi, sừng tê giác thuộc loại cấm xuất khẩu, cấm nhập khẩu bị xử phạt về hành vi “tàng trữ, mua bán, xuất khẩu, nhập khẩu, chế biến lâm sản trái pháp luật” quy định tại Điều 26 Nghị định số 146/2026/NĐ-CP</t>
         </is>
       </c>
     </row>
@@ -45475,11 +45628,11 @@
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Hình thức xử phạt bổ sung (khoản 2): Tịch thu tang vật vi phạm hành chính đối với hành vi vi phạm quy định tại Điều này, trừ tang vật vi phạm bị áp dụng biện pháp khắc phục hậu quả quy định tại điểm a khoản 3 Điều này</t>
+          <t>Khoản 1: Các hành vi vi phạm quy định về xuất khẩu, nhập khẩu hàng hóa theo điều kiện, tiêu chuẩn kỹ thuật, quy chuẩn kỹ thuật gồm: Xuất khẩu, nhập khẩu hàng hóa không đáp ứng điều kiện, tiêu chuẩn kỹ thuật, quy chuẩn kỹ thuật; Xuất khẩu, nhập khẩu hàng hóa phải kiểm tra chuyên ngành mà không có thông báo kết quả kiểm tra chuyên ngành theo quy định của pháp luật</t>
         </is>
       </c>
     </row>
@@ -45494,7 +45647,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Khoản 1: Các hành vi vi phạm quy định về xuất khẩu, nhập khẩu hàng hóa theo điều kiện, tiêu chuẩn kỹ thuật, quy chuẩn kỹ thuật gồm: Xuất khẩu, nhập khẩu hàng hóa không đáp ứng điều kiện, tiêu chuẩn kỹ thuật, quy chuẩn kỹ thuật; Xuất khẩu, nhập khẩu hàng hóa phải kiểm tra chuyên ngành mà không có thông báo kết quả kiểm tra chuyên ngành theo quy định của pháp luật</t>
+          <t>Khoản 2: Nhập khẩu hàng hóa không có chứng từ chứng nhận xuất xứ hàng hóa mà theo quy định phải có chứng từ chứng nhận xuất xứ hàng hóa để xác định hàng hóa không có xuất xứ từ các nước có nguy cơ gây hại đến an toàn xã hội, sức khỏe của cộng đồng hoặc vệ sinh môi trường cần được kiểm soát</t>
         </is>
       </c>
     </row>
@@ -45509,22 +45662,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Khoản 2: Nhập khẩu hàng hóa không có chứng từ chứng nhận xuất xứ hàng hóa mà theo quy định phải có chứng từ chứng nhận xuất xứ hàng hóa để xác định hàng hóa không có xuất xứ từ các nước có nguy cơ gây hại đến an toàn xã hội, sức khỏe của cộng đồng hoặc vệ sinh môi trường cần được kiểm soát</t>
+          <t>Khoản 7: Giấy phép, điều kiện, tiêu chuẩn kỹ thuật, quy chuẩn kỹ thuật nêu tại Điều này là giấy phép, điều kiện, tiêu chuẩn kỹ thuật, quy chuẩn kỹ thuật quy định tại Luật Quản lý ngoại thương số 05/2017/QH14 và các văn bản quy phạm pháp luật khác có quy định về giấy phép, điều kiện, tiêu chuẩn kỹ thuật, quy chuẩn kỹ thuật đối với hàng hóa xuất khẩu, nhập khẩu; điều kiện về chủ thể kinh doanh mà thương nhân phải đáp ứng khi thực hiện hoạt động xuất khẩu, nhập khẩu</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>NĐ 169/2026</t>
+          <t>NĐ 128/2020</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Khoản 7: Giấy phép, điều kiện, tiêu chuẩn kỹ thuật, quy chuẩn kỹ thuật nêu tại Điều này là giấy phép, điều kiện, tiêu chuẩn kỹ thuật, quy chuẩn kỹ thuật quy định tại Luật Quản lý ngoại thương số 05/2017/QH14 và các văn bản quy phạm pháp luật khác có quy định về giấy phép, điều kiện, tiêu chuẩn kỹ thuật, quy chuẩn kỹ thuật đối với hàng hóa xuất khẩu, nhập khẩu; điều kiện về chủ thể kinh doanh mà thương nhân phải đáp ứng khi thực hiện hoạt động xuất khẩu, nhập khẩu</t>
+          <t>Khoản 7: Vi phạm quy định tại điểm b khoản 1, khoản 3, khoản 5 Điều này dẫn đến thiếu số tiền thuế phải nộp hoặc tăng số tiền thuế được miễn, giảm, hoàn, không thu hoặc trốn thuế hoặc vi phạm quy định pháp luật về quản lý hàng hóa xuất khẩu, nhập khẩu thì xử phạt theo các Điều 9, 14, 15, 16, 17, 18, 19, 20, 21, 22 Nghị định này</t>
         </is>
       </c>
     </row>
@@ -45539,7 +45692,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Khoản 7: Vi phạm quy định tại điểm b khoản 1, khoản 3, khoản 5 Điều này dẫn đến thiếu số tiền thuế phải nộp hoặc tăng số tiền thuế được miễn, giảm, hoàn, không thu hoặc trốn thuế hoặc vi phạm quy định pháp luật về quản lý hàng hóa xuất khẩu, nhập khẩu thì xử phạt theo các Điều 9, 14, 15, 16, 17, 18, 19, 20, 21, 22 Nghị định này</t>
+          <t>Khoản 8: Quy định tại Điều này không áp dụng đối với trường hợp vi phạm quy định tại khoản 8 Điều 11 Nghị định này</t>
         </is>
       </c>
     </row>
@@ -45550,11 +45703,11 @@
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Khoản 8: Quy định tại Điều này không áp dụng đối với trường hợp vi phạm quy định tại khoản 8 Điều 11 Nghị định này</t>
+          <t>Khoản 1: Các hành vi khai sai dẫn đến thiếu số tiền thuế phải nộp hoặc tăng số tiền thuế được miễn, giảm, hoàn, không thu gồm: Khai sai về lượng, tên hàng, chủng loại, chất lượng, trị giá hải quan, mã số hàng hóa, thuế suất, mức thuế, xuất xứ, trừ quy định tại khoản 8 Điều 11, điểm b khoản 1 Điều 14 Nghị định này; Khai sai đối tượng không chịu thuế, đối tượng miễn thuế, hàng quản lý theo hạn ngạch thuế quan; Lập và khai không đúng các nội dung trong hồ sơ miễn thuế, hồ sơ xét miễn, giảm thuế, hoàn thuế, không thu thuế, hồ sơ xử lý tiền thuế, tiền phạt nộp thừa; Vi phạm quy định về quản lý nguyên liệu, vật tư, máy móc, thiết bị, sản phẩm gia công, sản xuất xuất khẩu, chế xuất dẫn đến hàng hóa thực tế tồn kho thiếu so với chứng từ kế toán, sổ kế toán, hồ sơ hải quan đối với hàng hóa xuất khẩu, nhập khẩu mà không thuộc trường hợp quy định tại các điểm d, đ, e và điểm g khoản 1 Điều 14 Nghị định này; Vi phạm quy định quản lý hàng hóa trong kho bảo thuế dẫn đến hàng hóa thực tế tồn kho thiếu so với chứng từ, sổ sách kế toán, hồ sơ hải quan đối với hàng hóa xuất khẩu, nhập khẩu mà không thuộc trường hợp quy định tại điểm g khoản 1 Điều 14 Nghị định này; Lập báo cáo quyết toán về lượng nguyên liệu, vật tư, linh kiện nhập khẩu đã sử dụng để sản xuất không đúng với thực tế sử dụng để sản xuất sản phẩm gia công, sản phẩm xuất khẩu; Khai báo hàng hóa nhập khẩu theo loại hình gia công, sản xuất xuất khẩu nhưng không có cơ sở sản xuất hàng gia công, cơ sở sản xuất hàng xuất khẩu trên lãnh thổ nước Cộng hòa xã hội chủ nghĩa Việt Nam; hoặc không có máy móc, thiết bị thuộc quyền sở hữu hoặc quyền sử dụng tại cơ sở sản xuất phù hợp với nguyên liệu, vật tư, linh kiện nhập khẩu để gia công, sản xuất hàng xuất khẩu</t>
         </is>
       </c>
     </row>
@@ -45569,7 +45722,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Khoản 1: Các hành vi khai sai dẫn đến thiếu số tiền thuế phải nộp hoặc tăng số tiền thuế được miễn, giảm, hoàn, không thu gồm: Khai sai về lượng, tên hàng, chủng loại, chất lượng, trị giá hải quan, mã số hàng hóa, thuế suất, mức thuế, xuất xứ, trừ quy định tại khoản 8 Điều 11, điểm b khoản 1 Điều 14 Nghị định này; Khai sai đối tượng không chịu thuế, đối tượng miễn thuế, hàng quản lý theo hạn ngạch thuế quan; Lập và khai không đúng các nội dung trong hồ sơ miễn thuế, hồ sơ xét miễn, giảm thuế, hoàn thuế, không thu thuế, hồ sơ xử lý tiền thuế, tiền phạt nộp thừa; Vi phạm quy định về quản lý nguyên liệu, vật tư, máy móc, thiết bị, sản phẩm gia công, sản xuất xuất khẩu, chế xuất dẫn đến hàng hóa thực tế tồn kho thiếu so với chứng từ kế toán, sổ kế toán, hồ sơ hải quan đối với hàng hóa xuất khẩu, nhập khẩu mà không thuộc trường hợp quy định tại các điểm d, đ, e và điểm g khoản 1 Điều 14 Nghị định này; Vi phạm quy định quản lý hàng hóa trong kho bảo thuế dẫn đến hàng hóa thực tế tồn kho thiếu so với chứng từ, sổ sách kế toán, hồ sơ hải quan đối với hàng hóa xuất khẩu, nhập khẩu mà không thuộc trường hợp quy định tại điểm g khoản 1 Điều 14 Nghị định này; Lập báo cáo quyết toán về lượng nguyên liệu, vật tư, linh kiện nhập khẩu đã sử dụng để sản xuất không đúng với thực tế sử dụng để sản xuất sản phẩm gia công, sản phẩm xuất khẩu; Khai báo hàng hóa nhập khẩu theo loại hình gia công, sản xuất xuất khẩu nhưng không có cơ sở sản xuất hàng gia công, cơ sở sản xuất hàng xuất khẩu trên lãnh thổ nước Cộng hòa xã hội chủ nghĩa Việt Nam; hoặc không có máy móc, thiết bị thuộc quyền sở hữu hoặc quyền sử dụng tại cơ sở sản xuất phù hợp với nguyên liệu, vật tư, linh kiện nhập khẩu để gia công, sản xuất hàng xuất khẩu</t>
+          <t>Khoản 5: Thực hiện xử phạt theo quy định tại các khoản 1, 2 và 3 Điều này chỉ áp dụng trong trường hợp số tiền thuế chênh lệch từ 500.000 đồng/tờ khai hải quan đối với vi phạm do cá nhân thực hiện, từ 2.000.000 đồng/tờ khai hải quan đối với vi phạm do tổ chức thực hiện</t>
         </is>
       </c>
     </row>
@@ -45584,7 +45737,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Khoản 5: Thực hiện xử phạt theo quy định tại các khoản 1, 2 và 3 Điều này chỉ áp dụng trong trường hợp số tiền thuế chênh lệch từ 500.000 đồng/tờ khai hải quan đối với vi phạm do cá nhân thực hiện, từ 2.000.000 đồng/tờ khai hải quan đối với vi phạm do tổ chức thực hiện</t>
+          <t>Khoản 6: Vi phạm quy định tại các khoản 1, 2 và 3 Điều này là hành vi trốn thuế thì xử phạt theo quy định tại Điều 14 Nghị định này</t>
         </is>
       </c>
     </row>
@@ -45599,7 +45752,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Khoản 6: Vi phạm quy định tại các khoản 1, 2 và 3 Điều này là hành vi trốn thuế thì xử phạt theo quy định tại Điều 14 Nghị định này</t>
+          <t>Khoản 7: Quy định tại Điều này không áp dụng đối với các trường hợp vi phạm quy định tại các Điều 15, 16, 17, 18, 19, 20, 21, 22 Nghị định này</t>
         </is>
       </c>
     </row>
@@ -45610,11 +45763,11 @@
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Khoản 7: Quy định tại Điều này không áp dụng đối với các trường hợp vi phạm quy định tại các Điều 15, 16, 17, 18, 19, 20, 21, 22 Nghị định này</t>
+          <t>Khoản 6: Trị giá tang vật vi phạm tại Điều này là trị giá sau khi đã trừ đi trị giá ngoại tệ tiền mặt, đồng Việt Nam bằng tiền mặt, công cụ chuyển nhượng, vàng, kim loại quý khác, đá quý không phải khai hải quan theo quy định của pháp luật</t>
         </is>
       </c>
     </row>
@@ -45625,11 +45778,11 @@
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Khoản 6: Trị giá tang vật vi phạm tại Điều này là trị giá sau khi đã trừ đi trị giá ngoại tệ tiền mặt, đồng Việt Nam bằng tiền mặt, công cụ chuyển nhượng, vàng, kim loại quý khác, đá quý không phải khai hải quan theo quy định của pháp luật</t>
+          <t>Khoản 11: Cá nhân, tổ chức có hành vi vi phạm quy định tại điểm a khoản 7 Điều này để trốn thuế thì bị xử phạt theo quy định tại Điều 14 Nghị định này</t>
         </is>
       </c>
     </row>
@@ -45640,11 +45793,11 @@
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Khoản 11: Cá nhân, tổ chức có hành vi vi phạm quy định tại điểm a khoản 7 Điều này để trốn thuế thì bị xử phạt theo quy định tại Điều 14 Nghị định này</t>
+          <t>Khoản 9: Cá nhân, tổ chức có hành vi vi phạm quy định tại điểm a khoản 4, khoản 5, khoản 6 Điều này mà hàng hóa đã bị tiêu thụ và vi phạm quy định tại các Điều 15, 16, 17, 18, 19, 20, 21, 22 Nghị định này thì ngoài việc bị xử phạt theo điểm a khoản 4, khoản 5, khoản 6 Điều này còn bị xử phạt về hành vi tương ứng quy định tại các Điều 15, 16, 17, 18, 19, 20, 21, 22 Nghị định này</t>
         </is>
       </c>
     </row>
@@ -45655,11 +45808,11 @@
         </is>
       </c>
       <c r="B27" s="2" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Khoản 9: Cá nhân, tổ chức có hành vi vi phạm quy định tại điểm a khoản 4, khoản 5, khoản 6 Điều này mà hàng hóa đã bị tiêu thụ và vi phạm quy định tại các Điều 15, 16, 17, 18, 19, 20, 21, 22 Nghị định này thì ngoài việc bị xử phạt theo điểm a khoản 4, khoản 5, khoản 6 Điều này còn bị xử phạt về hành vi tương ứng quy định tại các Điều 15, 16, 17, 18, 19, 20, 21, 22 Nghị định này</t>
+          <t>Khoản 4: Quy định tại Điều này không áp dụng đối với các trường hợp vi phạm quy định tại các Điều 15, 16, 17, 18, 19, 20, 21, 22 Nghị định này</t>
         </is>
       </c>
     </row>
@@ -45674,7 +45827,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Khoản 4: Quy định tại Điều này không áp dụng đối với các trường hợp vi phạm quy định tại các Điều 15, 16, 17, 18, 19, 20, 21, 22 Nghị định này</t>
+          <t>Khoản 5: Vi phạm quy định tại các điểm c, h khoản 1 Điều này mà không có chứng từ để khai bổ sung thì xử phạt theo quy định tại khoản 8 Điều 11 Nghị định này</t>
         </is>
       </c>
     </row>
@@ -45685,11 +45838,11 @@
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Khoản 5: Vi phạm quy định tại các điểm c, h khoản 1 Điều này mà không có chứng từ để khai bổ sung thì xử phạt theo quy định tại khoản 8 Điều 11 Nghị định này</t>
+          <t>Khoản 2: Mang vào hoặc mang ra khỏi lãnh thổ nước Cộng hòa xã hội chủ nghĩa Việt Nam trái phép ma túy, vũ khí, pháo các loại thuộc danh mục hàng cấm xuất khẩu, cấm nhập khẩu hoặc tạm ngừng xuất khẩu, tạm ngừng nhập khẩu thì xử phạt theo quy định tại Nghị định số 167/2013/NĐ-CP ngày 12 tháng 11 năm 2013 của Chính phủ quy định xử phạt vi phạm hành chính trong lĩnh vực an ninh, trật tự, an toàn xã hội; phòng, chống tệ nạn xã hội; phòng cháy, chữa cháy; phòng, chống bạo lực gia đình</t>
         </is>
       </c>
     </row>
@@ -45704,37 +45857,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Khoản 2: Mang vào hoặc mang ra khỏi lãnh thổ nước Cộng hòa xã hội chủ nghĩa Việt Nam trái phép ma túy, vũ khí, pháo các loại thuộc danh mục hàng cấm xuất khẩu, cấm nhập khẩu hoặc tạm ngừng xuất khẩu, tạm ngừng nhập khẩu thì xử phạt theo quy định tại Nghị định số 167/2013/NĐ-CP ngày 12 tháng 11 năm 2013 của Chính phủ quy định xử phạt vi phạm hành chính trong lĩnh vực an ninh, trật tự, an toàn xã hội; phòng, chống tệ nạn xã hội; phòng cháy, chữa cháy; phòng, chống bạo lực gia đình</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>NĐ 128/2020</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
           <t>Khoản 3: Vận chuyển ngà voi, sừng tê giác thuộc loại cấm xuất khẩu, cấm nhập khẩu bị xử phạt về hành vi “Vận chuyển lâm sản trái pháp luật” quy định tại Điều 22 Nghị định số 35/2019/NĐ-CP ngày 25 tháng 4 năm 2019 của Chính phủ quy định xử phạt vi phạm hành chính trong lĩnh vực lâm nghiệp; xuất khẩu, nhập khẩu ngà voi, sừng tê giác thuộc loại cấm xuất khẩu, cấm nhập khẩu bị xử phạt về hành vi “mua bán lâm sản trái pháp luật” quy định tại Điều 23 Nghị định số 35/2019/NĐ-CP</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>NĐ 128/2020</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>Hình thức xử phạt bổ sung (khoản 2): Tịch thu tang vật vi phạm hành chính đối với hành vi vi phạm quy định tại Điều này, trừ tang vật vi phạm bị áp dụng biện pháp khắc phục hậu quả quy định tại điểm a khoản 3 Điều này</t>
         </is>
       </c>
     </row>

--- a/outputs/penalty_catalog/penalty_catalog.xlsx
+++ b/outputs/penalty_catalog/penalty_catalog.xlsx
@@ -20850,7 +20850,11 @@
           <t>NĐ 169/2026</t>
         </is>
       </c>
-      <c r="U276" s="2" t="inlineStr"/>
+      <c r="U276" s="2" t="inlineStr">
+        <is>
+          <t>Trường hợp vi phạm quy định tại điểm này mà tang vật vi phạm thuộc đối tượng không chịu thuế, miễn thuế, hàng hóa áp dụng thuế suất theo hạn ngạch thuế quan và không vi phạm quy định về chính sách quản lý hàng hóa xuất khẩu, nhập khẩu thì xử phạt theo quy định tại điểm g khoản 1 Điều 15 Nghị định này</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" s="2" t="inlineStr">
@@ -32676,7 +32680,11 @@
           <t>NĐ 128/2020</t>
         </is>
       </c>
-      <c r="U430" s="4" t="inlineStr"/>
+      <c r="U430" s="4" t="inlineStr">
+        <is>
+          <t>Vi phạm quy định tại các điểm b, c, d khoản này mà cá nhân, tổ chức vi phạm không tự nguyện khắc phục hậu quả bằng cách nộp đủ số tiền thuế phải nộp trước thời điểm lập biên bản vi phạm hành chính thì xử phạt theo quy định tại điểm c khoản 1 Điều 14 Nghị định này</t>
+        </is>
+      </c>
     </row>
     <row r="431">
       <c r="A431" s="4" t="inlineStr">
@@ -32751,7 +32759,11 @@
           <t>NĐ 128/2020</t>
         </is>
       </c>
-      <c r="U431" s="4" t="inlineStr"/>
+      <c r="U431" s="4" t="inlineStr">
+        <is>
+          <t>Vi phạm quy định tại các điểm b, c, d khoản này mà cá nhân, tổ chức vi phạm không tự nguyện khắc phục hậu quả bằng cách nộp đủ số tiền thuế phải nộp trước thời điểm lập biên bản vi phạm hành chính thì xử phạt theo quy định tại điểm c khoản 1 Điều 14 Nghị định này</t>
+        </is>
+      </c>
     </row>
     <row r="432">
       <c r="A432" s="4" t="inlineStr">
@@ -32826,7 +32838,11 @@
           <t>NĐ 128/2020</t>
         </is>
       </c>
-      <c r="U432" s="4" t="inlineStr"/>
+      <c r="U432" s="4" t="inlineStr">
+        <is>
+          <t>Vi phạm quy định tại các điểm b, c, d khoản này mà cá nhân, tổ chức vi phạm không tự nguyện khắc phục hậu quả bằng cách nộp đủ số tiền thuế phải nộp trước thời điểm lập biên bản vi phạm hành chính thì xử phạt theo quy định tại điểm c khoản 1 Điều 14 Nghị định này</t>
+        </is>
+      </c>
     </row>
     <row r="433">
       <c r="A433" s="4" t="inlineStr">
@@ -36914,7 +36930,11 @@
           <t>NĐ 128/2020</t>
         </is>
       </c>
-      <c r="U484" s="4" t="inlineStr"/>
+      <c r="U484" s="4" t="inlineStr">
+        <is>
+          <t>Trường hợp vi phạm quy định tại điểm này mà tang vật vi phạm thuộc đối tượng không chịu thuế, miễn thuế, xét miễn thuế, hàng hóa áp dụng thuế suất theo hạn ngạch thuế quan và không vi phạm quy định về chính sách quản lý hàng hóa xuất khẩu, nhập khẩu thì xử phạt theo quy định tại điểm g khoản 1 Điều 14 Nghị định này</t>
+        </is>
+      </c>
     </row>
     <row r="485">
       <c r="A485" s="4" t="inlineStr">
